--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Italy_Seri" displayName="AveragesTable_Italy_Seri" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="H2" t="n">
-        <v>75.40000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>31.8</v>
+        <v>35.17</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="R2" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.6</v>
+        <v>48.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>16</v>
+        <v>18.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CC2" t="n">
         <v>3.4</v>
@@ -1628,40 +1628,40 @@
         <v>3.14</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH2" t="n">
         <v>1.3</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM2" t="n">
         <v>2.07</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO2" t="n">
         <v>1.39</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS2" t="n">
         <v>3.3</v>
@@ -1673,73 +1673,73 @@
         <v>1.35</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB2" t="n">
         <v>1.42</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="DH2" t="n">
-        <v>81.83</v>
+        <v>83.31</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM2" t="n">
-        <v>33.67</v>
+        <v>35.08</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.17</v>
+        <v>12.77</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.17</v>
+        <v>17.31</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.25</v>
+        <v>50.85</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.17</v>
+        <v>17.16</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="3">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="H5" t="n">
-        <v>86.17</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>44.5</v>
+        <v>47.57</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="P5" t="n">
-        <v>15.5</v>
+        <v>14.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>8.67</v>
+        <v>8.43</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.33</v>
+        <v>51.14</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.67</v>
+        <v>10.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.33</v>
+        <v>18.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2759,70 +2759,70 @@
         <v>2.17</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="CA5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CB5" t="n">
         <v>3.11</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>3.09</v>
       </c>
       <c r="CC5" t="n">
         <v>3.41</v>
@@ -2834,7 +2834,7 @@
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG5" t="n">
         <v>2.6</v>
@@ -2852,22 +2852,22 @@
         <v>1.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM5" t="n">
         <v>2.2</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CR5" t="n">
         <v>1.49</v>
@@ -2885,7 +2885,7 @@
         <v>1.94</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX5" t="n">
         <v>1.65</v>
@@ -2903,85 +2903,85 @@
         <v>1.41</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>85.5</v>
+        <v>86.31</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>46</v>
+        <v>47.54</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.84</v>
+        <v>14.54</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.25</v>
+        <v>51.62</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.66</v>
+        <v>13.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.66</v>
+        <v>20.23</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H6" t="n">
-        <v>84.33</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.17</v>
       </c>
-      <c r="M6" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>2.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.67</v>
+        <v>8.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CC6" t="n">
         <v>3.53</v>
@@ -3237,7 +3237,7 @@
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CG6" t="n">
         <v>2.56</v>
@@ -3255,10 +3255,10 @@
         <v>1.69</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.65</v>
@@ -3267,19 +3267,19 @@
         <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CU6" t="n">
         <v>1.35</v>
@@ -3288,10 +3288,10 @@
         <v>1.9</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY6" t="n">
         <v>2.17</v>
@@ -3303,55 +3303,55 @@
         <v>1.67</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="DE6" t="n">
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DH6" t="n">
-        <v>90</v>
+        <v>83.08</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.08</v>
+        <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.08</v>
+        <v>12.15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.08</v>
+        <v>18.38</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>56</v>
+        <v>56.08</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.83</v>
+        <v>13.3</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.17</v>
+        <v>16.69</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>78.40000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>40.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.4</v>
+        <v>16.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,73 +3944,73 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.2</v>
+        <v>48.83</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>9.17</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
         <v>4.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4031,37 +4031,37 @@
         <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH8" t="n">
         <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CM8" t="n">
         <v>2.12</v>
@@ -4070,40 +4070,40 @@
         <v>1.69</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA8" t="n">
         <v>1.72</v>
@@ -4112,52 +4112,52 @@
         <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>78.5</v>
+        <v>80</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.67</v>
+        <v>39.85</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.5</v>
+        <v>16.69</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.58</v>
+        <v>14.08</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.5</v>
+        <v>46.15</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX8" t="n">
-        <v>10</v>
+        <v>10.23</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.41</v>
+        <v>6.61</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.75</v>
+        <v>17.61</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="9">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,49 +6305,49 @@
         <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" t="n">
-        <v>97.8</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>47</v>
+        <v>52.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20.4</v>
+        <v>18.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.2</v>
+        <v>14.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.6</v>
+        <v>51.17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>9.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.4</v>
+        <v>18.83</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.33</v>
+        <v>9.69</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.83</v>
+        <v>5.08</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BR14" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
         <v>1.87</v>
@@ -6446,28 +6446,28 @@
         <v>1.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG14" t="n">
         <v>2.68</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI14" t="n">
         <v>1.85</v>
@@ -6479,7 +6479,7 @@
         <v>1.53</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
@@ -6491,19 +6491,19 @@
         <v>1.33</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
@@ -6515,67 +6515,67 @@
         <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.25</v>
+        <v>92.77</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.08</v>
+        <v>5.23</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.34</v>
+        <v>50.85</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.83</v>
+        <v>15.31</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.25</v>
+        <v>7.69</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.08</v>
+        <v>49.46</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.67</v>
+        <v>13.92</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.17</v>
+        <v>20.23</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,52 +6708,52 @@
         <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>77.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP15" t="n">
         <v>2</v>
       </c>
-      <c r="AL15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>13.4</v>
+        <v>14.83</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.6</v>
+        <v>14.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,61 +6765,61 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.8</v>
+        <v>47.83</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="BC15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BF15" t="n">
         <v>2</v>
       </c>
-      <c r="BD15" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.25</v>
+        <v>10.31</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.33</v>
+        <v>5.54</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6828,19 +6828,19 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU15" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY15" t="n">
         <v>3.55</v>
@@ -6852,19 +6852,19 @@
         <v>3.47</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.8</v>
+        <v>5.97</v>
       </c>
       <c r="CE15" t="n">
         <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CG15" t="n">
         <v>2.69</v>
@@ -6882,31 +6882,31 @@
         <v>1.62</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN15" t="n">
         <v>1.73</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
@@ -6921,64 +6921,64 @@
         <v>1.67</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB15" t="n">
         <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="DH15" t="n">
-        <v>74.58</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>30.08</v>
+        <v>27.77</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.75</v>
+        <v>14.38</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.75</v>
+        <v>14.62</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.67</v>
+        <v>47.31</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.5</v>
+        <v>12.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.58</v>
+        <v>8.23</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.92</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.5</v>
+        <v>18.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.33</v>
+        <v>76.86</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>31</v>
+        <v>32.71</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.67</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45</v>
+        <v>44.86</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.33</v>
+        <v>9.43</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>6.71</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.83</v>
+        <v>17.71</v>
       </c>
       <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>0.92</v>
       </c>
-      <c r="BF16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1</v>
-      </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BP16" t="n">
         <v>3.92</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX16" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY16" t="n">
         <v>3.2</v>
@@ -7258,10 +7258,10 @@
         <v>3.36</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.99</v>
+        <v>4.82</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.52</v>
+        <v>5.37</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
@@ -7279,28 +7279,28 @@
         <v>1.79</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN16" t="n">
         <v>1.67</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CR16" t="n">
         <v>1.47</v>
@@ -7315,10 +7315,10 @@
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX16" t="n">
         <v>1.67</v>
@@ -7333,55 +7333,55 @@
         <v>1.72</v>
       </c>
       <c r="DB16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
         <v>1.39</v>
       </c>
-      <c r="DC16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="DG16" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="DH16" t="n">
-        <v>77.67</v>
+        <v>76.92</v>
       </c>
       <c r="DI16" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.66</v>
+        <v>35.3</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="DO16" t="n">
         <v>1</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.08</v>
+        <v>14.62</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.84</v>
+        <v>14.54</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.08</v>
+        <v>45.93</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.08</v>
+        <v>10.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.75</v>
+        <v>7.07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.66</v>
+        <v>16.69</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="17">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F21" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="H21" t="n">
-        <v>83.83</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="K21" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>44.5</v>
+        <v>47.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>15.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>10.71</v>
       </c>
       <c r="R21" t="n">
-        <v>6.5</v>
+        <v>6.86</v>
       </c>
       <c r="S21" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45</v>
+        <v>45.14</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.17</v>
+        <v>17.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>12</v>
+        <v>12.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.83</v>
+        <v>21.57</v>
       </c>
       <c r="AD21" t="n">
         <v>1.76</v>
       </c>
       <c r="AE21" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,49 +9207,49 @@
         <v>1.67</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BH21" t="n">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="BR21" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS21" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -9258,19 +9258,19 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="CA21" t="n">
         <v>3.04</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CC21" t="n">
         <v>3.35</v>
@@ -9279,49 +9279,49 @@
         <v>3.61</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CH21" t="n">
         <v>1.29</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO21" t="n">
         <v>1.42</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="CR21" t="n">
         <v>1.51</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CT21" t="n">
         <v>2.67</v>
@@ -9330,73 +9330,73 @@
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CW21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CY21" t="n">
         <v>2.1</v>
       </c>
-      <c r="CX21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>2.13</v>
-      </c>
       <c r="CZ21" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="DE21" t="n">
         <v>0.08</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG21" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.08</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="DK21" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.84</v>
+        <v>44.77</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO21" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DP21" t="n">
-        <v>15.75</v>
+        <v>15.69</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12</v>
+        <v>11.77</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.25</v>
+        <v>7.39</v>
       </c>
       <c r="DS21" t="n">
         <v>0.08</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.75</v>
+        <v>46.69</v>
       </c>
       <c r="DW21" t="n">
         <v>0.08</v>
       </c>
       <c r="DX21" t="n">
-        <v>14.67</v>
+        <v>14.93</v>
       </c>
       <c r="DY21" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.16</v>
+        <v>19.69</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1607,7 +1607,7 @@
         <v>2.55</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CA2" t="n">
         <v>3.15</v>
@@ -1667,7 +1667,7 @@
         <v>3.3</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU2" t="n">
         <v>1.35</v>
@@ -1688,7 +1688,7 @@
         <v>2.1</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB2" t="n">
         <v>1.42</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="H3" t="n">
-        <v>79</v>
+        <v>72.17</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>31</v>
+        <v>29.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>14.6</v>
+        <v>14.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="R3" t="n">
-        <v>7.4</v>
+        <v>8.83</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.8</v>
+        <v>45.83</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.6</v>
+        <v>12.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,70 +1953,70 @@
         <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.82</v>
+        <v>8.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC3" t="n">
         <v>3.62</v>
@@ -2031,151 +2031,151 @@
         <v>3.14</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DH3" t="n">
-        <v>78.45</v>
+        <v>75.08</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>31.45</v>
+        <v>30.58</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.91</v>
+        <v>13.83</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.91</v>
+        <v>16.17</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.45</v>
+        <v>8.17</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.82</v>
+        <v>49</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.55</v>
+        <v>11.42</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.36</v>
+        <v>16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>93</v>
+        <v>88.33</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>32.8</v>
+        <v>35.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>12.4</v>
+        <v>12.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.2</v>
+        <v>16.17</v>
       </c>
       <c r="R4" t="n">
-        <v>7.2</v>
+        <v>7.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.4</v>
+        <v>50.83</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.4</v>
+        <v>10.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>17.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN4" t="n">
         <v>1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CC4" t="n">
         <v>3.58</v>
@@ -2428,13 +2428,13 @@
         <v>4.17</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
@@ -2443,37 +2443,37 @@
         <v>1.75</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO4" t="n">
         <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2485,100 +2485,100 @@
         <v>2.04</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DB4" t="n">
         <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.33</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.42</v>
+        <v>32.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.42</v>
+        <v>14.46</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.92</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.91</v>
+        <v>47.53</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.75</v>
+        <v>6.61</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="EA4" t="n">
-        <v>17</v>
+        <v>17.46</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="5">
@@ -2816,7 +2816,7 @@
         <v>2.64</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CA5" t="n">
         <v>3.12</v>
@@ -2870,16 +2870,16 @@
         <v>4.05</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV5" t="n">
         <v>1.94</v>
@@ -2888,25 +2888,25 @@
         <v>1.92</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DE5" t="n">
         <v>0.15</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>88.29000000000001</v>
+        <v>89</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.43</v>
+        <v>45.88</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.43</v>
+        <v>14.62</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.43</v>
+        <v>13.88</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,73 +3541,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.71</v>
+        <v>47.75</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.86</v>
+        <v>11.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.71</v>
+        <v>7.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.71</v>
+        <v>20.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.5</v>
+        <v>7.92</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY7" t="n">
         <v>2.16</v>
@@ -3625,34 +3625,34 @@
         <v>2.15</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.09</v>
+        <v>3.39</v>
       </c>
       <c r="CE7" t="n">
         <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG7" t="n">
         <v>2.55</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK7" t="n">
         <v>1.8</v>
@@ -3661,25 +3661,25 @@
         <v>2.37</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO7" t="n">
         <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CT7" t="n">
         <v>2.7</v>
@@ -3688,10 +3688,10 @@
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX7" t="n">
         <v>1.82</v>
@@ -3703,7 +3703,7 @@
         <v>1.98</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB7" t="n">
         <v>1.42</v>
@@ -3712,82 +3712,82 @@
         <v>2.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.75</v>
+        <v>90.08</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.42</v>
+        <v>48.46</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.25</v>
+        <v>14.77</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.17</v>
+        <v>12.39</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.17</v>
+        <v>7.31</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.75</v>
+        <v>47.77</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.67</v>
+        <v>11.93</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.25</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.33</v>
+        <v>20.3</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="8">
@@ -4031,13 +4031,13 @@
         <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CC8" t="n">
         <v>3.37</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
@@ -4094,25 +4094,25 @@
         <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.17</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
         <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD8" t="n">
         <v>4.52</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.5</v>
@@ -4290,139 +4290,139 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.33</v>
+        <v>75.86</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.67</v>
+        <v>5.29</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.17</v>
+        <v>41.86</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.83</v>
+        <v>14.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44</v>
+        <v>44.71</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.5</v>
+        <v>17.29</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.33</v>
+        <v>11.71</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.17</v>
+        <v>16.43</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.42</v>
+        <v>4.85</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
         <v>2.47</v>
@@ -4434,46 +4434,46 @@
         <v>3.17</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="CE9" t="n">
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH9" t="n">
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP9" t="n">
         <v>2.14</v>
@@ -4485,115 +4485,115 @@
         <v>1.45</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY9" t="n">
         <v>2.02</v>
       </c>
-      <c r="CW9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CZ9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA9" t="n">
         <v>1.8</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.83</v>
+        <v>77.92</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>38.34</v>
+        <v>39.39</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.92</v>
+        <v>17.08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.08</v>
+        <v>15.84</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.16</v>
+        <v>46.38</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.84</v>
+        <v>16.77</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.66</v>
+        <v>11.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.17</v>
+        <v>5.39</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.67</v>
+        <v>17.23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4693,130 +4693,130 @@
         <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>96.83</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.83</v>
+        <v>35.14</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.83</v>
+        <v>18.71</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54</v>
+        <v>52.43</v>
       </c>
       <c r="AZ10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA10" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.36</v>
-      </c>
       <c r="BN10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="BR10" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY10" t="n">
         <v>2.4</v>
@@ -4840,19 +4840,19 @@
         <v>3.1</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH10" t="n">
         <v>1.3</v>
@@ -4861,7 +4861,7 @@
         <v>1.75</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK10" t="n">
         <v>1.66</v>
@@ -4870,133 +4870,133 @@
         <v>2.19</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
         <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS10" t="n">
         <v>3.41</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CU10" t="n">
         <v>1.33</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG10" t="n">
         <v>2.16</v>
       </c>
-      <c r="DA10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>2.09</v>
-      </c>
       <c r="DH10" t="n">
-        <v>91.36</v>
+        <v>89.92</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.63</v>
+        <v>38.42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.45</v>
+        <v>18.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.54</v>
+        <v>13.58</v>
       </c>
       <c r="DR10" t="n">
-        <v>5.82</v>
+        <v>5.84</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.55</v>
+        <v>53.58</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.27</v>
+        <v>8.16</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.09</v>
+        <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="H11" t="n">
-        <v>78.83</v>
+        <v>83.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="K11" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>40</v>
+        <v>42.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.67</v>
+        <v>18.29</v>
       </c>
       <c r="R11" t="n">
-        <v>7.67</v>
+        <v>7.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>64</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.67</v>
+        <v>19.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.83</v>
+        <v>16.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.67</v>
+        <v>10.62</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS11" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CC11" t="n">
         <v>4.06</v>
@@ -5252,52 +5252,52 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.81</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL11" t="n">
         <v>2.39</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV11" t="n">
         <v>2.04</v>
@@ -5306,25 +5306,25 @@
         <v>1.83</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC11" t="n">
         <v>2.06</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
@@ -5333,40 +5333,40 @@
         <v>1.84</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.25</v>
+        <v>88</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.84</v>
+        <v>5.08</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.5</v>
+        <v>41.92</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.34</v>
+        <v>13.31</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19.08</v>
+        <v>18.85</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.25</v>
+        <v>7.08</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.42</v>
+        <v>63.62</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.92</v>
+        <v>16.47</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.42</v>
+        <v>10.54</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.5</v>
+        <v>5.92</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.42</v>
+        <v>17.08</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>99.33</v>
+        <v>104.71</v>
       </c>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M12" t="n">
-        <v>58.17</v>
+        <v>59.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>15.17</v>
+        <v>14.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.83</v>
+        <v>16.14</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T12" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.33</v>
+        <v>54.57</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>16.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.33</v>
+        <v>10.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5580,49 +5580,49 @@
         <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CA12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CB12" t="n">
         <v>3.26</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>3.21</v>
       </c>
       <c r="CC12" t="n">
         <v>2.58</v>
@@ -5655,7 +5655,7 @@
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG12" t="n">
         <v>2.6</v>
@@ -5667,28 +5667,28 @@
         <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
         <v>1.72</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM12" t="n">
         <v>2.05</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
         <v>2.19</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,34 +5697,34 @@
         <v>3.31</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB12" t="n">
         <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
         <v>4.22</v>
@@ -5733,76 +5733,76 @@
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="DH12" t="n">
-        <v>101.33</v>
+        <v>104.07</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>56.08</v>
+        <v>57.07</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.58</v>
+        <v>15.39</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.66</v>
+        <v>15.38</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.16</v>
+        <v>54.31</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>16</v>
+        <v>16.54</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.42</v>
+        <v>11.92</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.34</v>
+        <v>18.85</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="H13" t="n">
-        <v>108.17</v>
+        <v>110.57</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K13" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>56.33</v>
+        <v>56.29</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>15.83</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.17</v>
+        <v>13.43</v>
       </c>
       <c r="R13" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.33</v>
+        <v>55.71</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.83</v>
+        <v>10.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.83</v>
+        <v>16.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
         <v>0.17</v>
@@ -5983,49 +5983,49 @@
         <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT13" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY13" t="n">
         <v>1.77</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
         <v>2.34</v>
@@ -6058,16 +6058,16 @@
         <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CG13" t="n">
         <v>2.63</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.01</v>
@@ -6079,28 +6079,28 @@
         <v>2.27</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN13" t="n">
         <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.99</v>
+        <v>4.06</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
@@ -6109,7 +6109,7 @@
         <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
@@ -6127,52 +6127,52 @@
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
         <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.5</v>
+        <v>101.46</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM13" t="n">
-        <v>48.16</v>
+        <v>48.77</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DP13" t="n">
-        <v>16.58</v>
+        <v>15.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.34</v>
+        <v>13</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.66</v>
+        <v>5.54</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.58</v>
+        <v>54.38</v>
       </c>
       <c r="DW13" t="n">
         <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.33</v>
+        <v>14.31</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.17</v>
+        <v>10.39</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.16</v>
+        <v>3.92</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.42</v>
+        <v>16.84</v>
       </c>
       <c r="EB13" t="n">
         <v>1.54</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6449,13 +6449,13 @@
         <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC14" t="n">
         <v>2.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
@@ -6500,7 +6500,7 @@
         <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT14" t="n">
         <v>2.91</v>
@@ -6533,7 +6533,7 @@
         <v>2.15</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
@@ -7261,7 +7261,7 @@
         <v>4.82</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
@@ -7306,13 +7306,13 @@
         <v>1.47</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV16" t="n">
         <v>1.89</v>
@@ -7321,25 +7321,25 @@
         <v>1.97</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>102.5</v>
+        <v>103.57</v>
       </c>
       <c r="I17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K17" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="L17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>43.83</v>
+        <v>47</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O17" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="P17" t="n">
-        <v>16.67</v>
+        <v>16.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.17</v>
+        <v>14.57</v>
       </c>
       <c r="R17" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.33</v>
+        <v>49.57</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.83</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.83</v>
+        <v>11.29</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="AC17" t="n">
-        <v>17</v>
+        <v>17.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,67 +7595,67 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB17" t="n">
         <v>3.12</v>
@@ -7667,16 +7667,16 @@
         <v>4.1</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI17" t="n">
         <v>1.77</v>
@@ -7685,13 +7685,13 @@
         <v>2</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN17" t="n">
         <v>1.61</v>
@@ -7700,10 +7700,10 @@
         <v>1.42</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7718,31 +7718,31 @@
         <v>1.35</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY17" t="n">
         <v>2.26</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
@@ -7751,73 +7751,73 @@
         <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DH17" t="n">
-        <v>99.75</v>
+        <v>100.54</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.75</v>
+        <v>45.46</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.75</v>
+        <v>15.62</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.25</v>
+        <v>14.46</v>
       </c>
       <c r="DR17" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.42</v>
+        <v>50</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
-        <v>14</v>
+        <v>14.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.25</v>
+        <v>10.54</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.5</v>
+        <v>19.54</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7917,139 +7917,139 @@
         <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.8</v>
+        <v>79.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>16.33</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>40.2</v>
+        <v>39.17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ18" t="n">
         <v>5.08</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY18" t="n">
         <v>1.99</v>
@@ -8061,40 +8061,40 @@
         <v>3.1</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF18" t="n">
         <v>3.2</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH18" t="n">
         <v>1.3</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK18" t="n">
         <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN18" t="n">
         <v>1.71</v>
@@ -8103,91 +8103,91 @@
         <v>1.4</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CU18" t="n">
         <v>1.34</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.57</v>
+        <v>4.51</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.5</v>
+        <v>88.92</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.75</v>
+        <v>40.15</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.5</v>
+        <v>16.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>17.17</v>
+        <v>16.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.42</v>
+        <v>6.61</v>
       </c>
       <c r="DS18" t="n">
         <v>0.08</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.92</v>
+        <v>44.08</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="EA18" t="n">
-        <v>14.66</v>
+        <v>14.84</v>
       </c>
       <c r="EB18" t="n">
         <v>1.15</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8323,55 +8323,55 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>88.83</v>
+        <v>86.86</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.83</v>
+        <v>47</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>19.71</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.33</v>
+        <v>8.57</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -8383,67 +8383,67 @@
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.67</v>
+        <v>10.14</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.83</v>
+        <v>6.43</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.5</v>
+        <v>23.29</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY19" t="n">
         <v>2.51</v>
@@ -8461,55 +8461,55 @@
         <v>2.62</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.18</v>
+        <v>3.47</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="CE19" t="n">
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK19" t="n">
         <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
@@ -8518,16 +8518,16 @@
         <v>3.31</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CX19" t="n">
         <v>1.65</v>
@@ -8548,49 +8548,49 @@
         <v>2.28</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DH19" t="n">
-        <v>93</v>
+        <v>91.62</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM19" t="n">
-        <v>53.58</v>
+        <v>53.15</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO19" t="n">
         <v>2.08</v>
       </c>
       <c r="DP19" t="n">
-        <v>16.92</v>
+        <v>17.46</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.33</v>
+        <v>13.31</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="DS19" t="n">
         <v>0.08</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>34.66</v>
+        <v>34.46</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.84</v>
+        <v>12.38</v>
       </c>
       <c r="DY19" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="EA19" t="n">
-        <v>25.17</v>
+        <v>24.92</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0.33</v>
@@ -8723,139 +8723,139 @@
         <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AI20" t="n">
-        <v>108.33</v>
+        <v>105.14</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>50</v>
+        <v>49.86</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="AR20" t="n">
-        <v>15.5</v>
+        <v>15.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>59.17</v>
+        <v>58.86</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.67</v>
+        <v>14.86</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.33</v>
+        <v>18.71</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.42</v>
+        <v>8.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BQ20" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="BR20" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS20" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT20" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY20" t="n">
         <v>1.87</v>
@@ -8870,19 +8870,19 @@
         <v>3.37</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="CE20" t="n">
         <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH20" t="n">
         <v>1.35</v>
@@ -8894,10 +8894,10 @@
         <v>1.89</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM20" t="n">
         <v>2.26</v>
@@ -8912,19 +8912,19 @@
         <v>2.09</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CR20" t="n">
         <v>1.44</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV20" t="n">
         <v>1.95</v>
@@ -8939,7 +8939,7 @@
         <v>2.04</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA20" t="n">
         <v>1.77</v>
@@ -8948,85 +8948,85 @@
         <v>1.36</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.25</v>
+        <v>104.69</v>
       </c>
       <c r="DI20" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DK20" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DM20" t="n">
-        <v>45.84</v>
+        <v>46.08</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.34</v>
+        <v>14.47</v>
       </c>
       <c r="DQ20" t="n">
-        <v>16.58</v>
+        <v>16.39</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.34</v>
+        <v>61</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX20" t="n">
-        <v>15.67</v>
+        <v>15.7</v>
       </c>
       <c r="DY20" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.66</v>
+        <v>4.85</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.75</v>
+        <v>17.08</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9264,13 +9264,13 @@
         <v>2.3</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CA21" t="n">
         <v>3.04</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CC21" t="n">
         <v>3.35</v>
@@ -9321,7 +9321,7 @@
         <v>1.51</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CT21" t="n">
         <v>2.67</v>
@@ -9333,7 +9333,7 @@
         <v>1.8</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX21" t="n">
         <v>1.69</v>
@@ -9354,7 +9354,7 @@
         <v>2.53</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="DE21" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -4837,7 +4837,7 @@
         <v>3.06</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
         <v>3.17</v>
@@ -4885,43 +4885,43 @@
         <v>4.42</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CS10" t="n">
         <v>3.41</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CU10" t="n">
         <v>1.33</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.57</v>
+        <v>4.61</v>
       </c>
       <c r="DE10" t="n">
         <v>0.16</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>64.29000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.62</v>
+        <v>63.69</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
@@ -7652,13 +7652,13 @@
         <v>2.25</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CA17" t="n">
         <v>3.1</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CC17" t="n">
         <v>3.59</v>
@@ -7709,10 +7709,10 @@
         <v>1.51</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7724,25 +7724,25 @@
         <v>2.02</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
@@ -7974,16 +7974,16 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>39.17</v>
+        <v>39</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.67</v>
+        <v>9.83</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="BC18" t="n">
         <v>3.67</v>
@@ -7992,7 +7992,7 @@
         <v>15</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BF18" t="n">
         <v>2</v>
@@ -8199,16 +8199,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.08</v>
+        <v>44</v>
       </c>
       <c r="DW18" t="n">
         <v>0.39</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.380000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.62</v>
+        <v>5.7</v>
       </c>
       <c r="DZ18" t="n">
         <v>3.77</v>
@@ -8217,7 +8217,7 @@
         <v>14.84</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC18" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>91.8</v>
+        <v>84.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52.6</v>
+        <v>50.17</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
         <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="R7" t="n">
-        <v>6.6</v>
+        <v>7.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.8</v>
+        <v>46.83</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.4</v>
+        <v>10.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.8</v>
+        <v>17.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.92</v>
+        <v>8.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.08</v>
+        <v>4.43</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CC7" t="n">
         <v>3.06</v>
@@ -3637,13 +3637,13 @@
         <v>3.39</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF7" t="n">
         <v>3.15</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3658,10 +3658,10 @@
         <v>1.8</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN7" t="n">
         <v>1.58</v>
@@ -3670,7 +3670,7 @@
         <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CQ7" t="n">
         <v>4.23</v>
@@ -3700,94 +3700,94 @@
         <v>2.28</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DA7" t="n">
         <v>1.59</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>90.08</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.46</v>
+        <v>47.72</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.77</v>
+        <v>14.78</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.39</v>
+        <v>12.08</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.31</v>
+        <v>7.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.77</v>
+        <v>47.36</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.93</v>
+        <v>12.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.460000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.3</v>
+        <v>19.42</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="8">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>103.33</v>
+        <v>105.71</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>14.86</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54</v>
+        <v>54.57</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.67</v>
+        <v>18.57</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.69</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.15</v>
+        <v>5.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY12" t="n">
         <v>1.9</v>
@@ -5640,55 +5640,55 @@
         <v>1.84</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CC12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CG12" t="n">
         <v>2.58</v>
       </c>
-      <c r="CD12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>2.6</v>
-      </c>
       <c r="CH12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM12" t="n">
         <v>2.05</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO12" t="n">
         <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5712,97 +5712,97 @@
         <v>1.74</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.07</v>
+        <v>105.21</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.38</v>
+        <v>5.57</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.07</v>
+        <v>58.86</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.39</v>
+        <v>14.86</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.38</v>
+        <v>15.28</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.08</v>
+        <v>5.22</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.31</v>
+        <v>54.57</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.54</v>
+        <v>16.64</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.92</v>
+        <v>11.93</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.85</v>
+        <v>18.78</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,139 +1469,139 @@
         <v>2.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>86.43000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AL2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>3</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>35</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.77</v>
+        <v>5.93</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
         <v>2.55</v>
@@ -1613,25 +1613,25 @@
         <v>3.15</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CC2" t="n">
         <v>3.4</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI2" t="n">
         <v>1.8</v>
@@ -1640,16 +1640,16 @@
         <v>1.97</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL2" t="n">
         <v>2.23</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO2" t="n">
         <v>1.39</v>
@@ -1658,7 +1658,7 @@
         <v>2.27</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CR2" t="n">
         <v>1.49</v>
@@ -1679,16 +1679,16 @@
         <v>1.98</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB2" t="n">
         <v>1.42</v>
@@ -1697,82 +1697,82 @@
         <v>2.35</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.31</v>
+        <v>82.78</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.08</v>
+        <v>34.28</v>
       </c>
       <c r="DN2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1.15</v>
       </c>
-      <c r="DO2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>50.85</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>11</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1.19</v>
-      </c>
       <c r="EC2" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,16 +1872,16 @@
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>78</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1890,34 +1890,34 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.83</v>
+        <v>31.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.33</v>
+        <v>14.14</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.33</v>
+        <v>14.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.5</v>
+        <v>6.86</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.17</v>
+        <v>51.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.67</v>
+        <v>10.14</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.67</v>
+        <v>8.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.33</v>
+        <v>19.43</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
         <v>2.51</v>
@@ -2013,25 +2013,25 @@
         <v>2.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="CE3" t="n">
         <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
@@ -2046,10 +2046,10 @@
         <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN3" t="n">
         <v>1.72</v>
@@ -2058,61 +2058,61 @@
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
         <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DH3" t="n">
-        <v>75.08</v>
+        <v>75</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,28 +2121,28 @@
         <v>1.92</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.58</v>
+        <v>30.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.83</v>
+        <v>14.23</v>
       </c>
       <c r="DQ3" t="n">
-        <v>16.17</v>
+        <v>15.85</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.17</v>
+        <v>7.77</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2160,22 +2160,22 @@
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.42</v>
+        <v>11.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="EA3" t="n">
-        <v>16</v>
+        <v>16.77</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.17</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>30.43</v>
+        <v>31.25</v>
       </c>
       <c r="AO4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL4" t="n">
         <v>0.57</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>44.71</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.62</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
         <v>1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.38</v>
+        <v>4.79</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.78</v>
@@ -2419,166 +2419,166 @@
         <v>3.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.17</v>
+        <v>3.95</v>
       </c>
       <c r="CE4" t="n">
         <v>1.48</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CP4" t="n">
         <v>2.33</v>
       </c>
-      <c r="CM4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>2.35</v>
-      </c>
       <c r="CQ4" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CR4" t="n">
         <v>1.52</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.54000000000001</v>
+        <v>85.86</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.62</v>
+        <v>32.93</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.46</v>
+        <v>14.93</v>
       </c>
       <c r="DQ4" t="n">
         <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.460000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.53</v>
+        <v>47.28</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.38</v>
+        <v>10.57</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.61</v>
+        <v>6.64</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.46</v>
+        <v>18.28</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,139 +2678,139 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>84.83</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.5</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.67</v>
+        <v>13.29</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.17</v>
+        <v>51.14</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.33</v>
+        <v>11.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>22</v>
+        <v>21.71</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.64</v>
@@ -2819,169 +2819,169 @@
         <v>2.64</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI5" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.31</v>
+        <v>87.64</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.38</v>
+        <v>5.28</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.54</v>
+        <v>46.78</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.54</v>
+        <v>14.36</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.62</v>
+        <v>51.14</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.39</v>
+        <v>12.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.23</v>
+        <v>20.21</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>72.29000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.71</v>
+        <v>5.12</v>
       </c>
       <c r="L6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>34.14</v>
+        <v>34.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="O6" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.14</v>
+        <v>18.75</v>
       </c>
       <c r="R6" t="n">
-        <v>7.86</v>
+        <v>8.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.86</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.14</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.43</v>
+        <v>19.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>2.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.85</v>
+        <v>8.93</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="CA6" t="n">
         <v>3.12</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CC6" t="n">
         <v>3.53</v>
@@ -3234,10 +3234,10 @@
         <v>3.92</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG6" t="n">
         <v>2.56</v>
@@ -3246,13 +3246,13 @@
         <v>1.32</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL6" t="n">
         <v>2.25</v>
@@ -3261,22 +3261,22 @@
         <v>2.1</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP6" t="n">
         <v>2.22</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CT6" t="n">
         <v>2.74</v>
@@ -3288,19 +3288,19 @@
         <v>1.9</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DB6" t="n">
         <v>1.41</v>
@@ -3312,79 +3312,79 @@
         <v>4.26</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.08</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.46</v>
+        <v>4.71</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM6" t="n">
         <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.15</v>
+        <v>11.93</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.38</v>
+        <v>18.21</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>56.08</v>
+        <v>55.43</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.3</v>
+        <v>13.57</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.69</v>
+        <v>16.43</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>78.56999999999999</v>
+        <v>81.12</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="K8" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>39.43</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>16.57</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.14</v>
+        <v>14.75</v>
       </c>
       <c r="R8" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>43.86</v>
+        <v>44.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.14</v>
+        <v>11.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.14</v>
+        <v>18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.380000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CA8" t="n">
         <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CC8" t="n">
         <v>3.37</v>
@@ -4043,10 +4043,10 @@
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH8" t="n">
         <v>1.31</v>
@@ -4061,22 +4061,22 @@
         <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4094,16 +4094,16 @@
         <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY8" t="n">
         <v>2.09</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA8" t="n">
         <v>1.73</v>
@@ -4115,82 +4115,82 @@
         <v>2.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>80</v>
+        <v>81.36</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.85</v>
+        <v>39.57</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DO8" t="n">
         <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.69</v>
+        <v>16.36</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.08</v>
+        <v>14.43</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.69</v>
+        <v>7.43</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.15</v>
+        <v>46.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.23</v>
+        <v>10.64</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.61</v>
+        <v>6.71</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.62</v>
+        <v>3.93</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.61</v>
+        <v>17.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.5</v>
@@ -4290,139 +4290,139 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.86</v>
+        <v>77.12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.86</v>
+        <v>41.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19.29</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.57</v>
+        <v>15.12</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.71</v>
+        <v>45.62</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>17.29</v>
+        <v>16.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.43</v>
+        <v>16.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.08</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>2.47</v>
@@ -4431,70 +4431,70 @@
         <v>2.58</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="CE9" t="n">
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH9" t="n">
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN9" t="n">
         <v>1.75</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CU9" t="n">
         <v>1.38</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW9" t="n">
         <v>1.83</v>
@@ -4515,85 +4515,85 @@
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.92</v>
+        <v>78.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.77</v>
+        <v>5.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>39.39</v>
+        <v>39.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>17.08</v>
+        <v>17.07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.84</v>
+        <v>16.07</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.460000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.38</v>
+        <v>46.78</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.77</v>
+        <v>16.36</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.38</v>
+        <v>11.07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.23</v>
+        <v>17.22</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="n">
-        <v>84.8</v>
+        <v>90.33</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>41.83</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>17.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="R10" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.2</v>
+        <v>56.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.6</v>
+        <v>8.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.4</v>
+        <v>21.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,49 +4774,49 @@
         <v>3.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="BR10" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="CA10" t="n">
         <v>3.06</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC10" t="n">
         <v>3.17</v>
@@ -4849,13 +4849,13 @@
         <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.75</v>
@@ -4867,22 +4867,22 @@
         <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="CR10" t="n">
         <v>1.54</v>
@@ -4903,16 +4903,16 @@
         <v>2.03</v>
       </c>
       <c r="CX10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA10" t="n">
         <v>1.69</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
         <v>1.45</v>
@@ -4924,46 +4924,46 @@
         <v>4.61</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.92</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.42</v>
+        <v>38.23</v>
       </c>
       <c r="DN10" t="n">
         <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.41</v>
+        <v>18</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.58</v>
+        <v>13.69</v>
       </c>
       <c r="DR10" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.58</v>
+        <v>54.23</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.92</v>
+        <v>11.69</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.16</v>
+        <v>7.92</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA10" t="n">
         <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.14</v>
@@ -5099,49 +5099,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.67</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.5</v>
+        <v>19.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.83</v>
+        <v>7.86</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>62.83</v>
+        <v>59</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.17</v>
+        <v>11.71</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.5</v>
+        <v>7.57</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.62</v>
+        <v>10.43</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.85</v>
+        <v>5.93</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>2.57</v>
@@ -5237,28 +5237,28 @@
         <v>2.75</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.06</v>
+        <v>4.34</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.68</v>
+        <v>5</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI11" t="n">
         <v>1.91</v>
@@ -5270,136 +5270,136 @@
         <v>1.71</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW11" t="n">
         <v>1.83</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="DH11" t="n">
-        <v>88</v>
+        <v>84.92</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.08</v>
+        <v>4.78</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.92</v>
+        <v>39.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.31</v>
+        <v>13.14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.85</v>
+        <v>19</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.08</v>
+        <v>7.58</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.69</v>
+        <v>61.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.47</v>
+        <v>15.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.54</v>
+        <v>9.93</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.08</v>
+        <v>17</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.14</v>
@@ -5902,52 +5902,52 @@
         <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AI13" t="n">
-        <v>90.83</v>
+        <v>89.14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>40</v>
+        <v>37.29</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.33</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,73 +5959,73 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.83</v>
+        <v>50.71</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.83</v>
+        <v>14.29</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="BD13" t="n">
-        <v>17</v>
+        <v>16.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.54</v>
+        <v>4.21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.08</v>
+        <v>4.36</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT13" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY13" t="n">
         <v>1.77</v>
@@ -6043,25 +6043,25 @@
         <v>1.79</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
@@ -6070,13 +6070,13 @@
         <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
         <v>1.73</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
@@ -6085,22 +6085,22 @@
         <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS13" t="n">
         <v>3.28</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
@@ -6112,67 +6112,67 @@
         <v>2.06</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB13" t="n">
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.46</v>
+        <v>99.86</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM13" t="n">
-        <v>48.77</v>
+        <v>46.79</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.54</v>
+        <v>15.5</v>
       </c>
       <c r="DQ13" t="n">
         <v>13</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.38</v>
+        <v>53.21</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.31</v>
+        <v>14.08</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.39</v>
+        <v>10.08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.84</v>
+        <v>16.64</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -6230,79 +6230,79 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>91.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K14" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="L14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M14" t="n">
-        <v>49.29</v>
+        <v>47</v>
       </c>
       <c r="N14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>12.57</v>
+        <v>13.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="R14" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="S14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48</v>
+        <v>48.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.57</v>
+        <v>16.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.859999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.71</v>
+        <v>6.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.43</v>
+        <v>20.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6386,70 +6386,70 @@
         <v>2.83</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU14" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC14" t="n">
         <v>2.46</v>
@@ -6461,13 +6461,13 @@
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG14" t="n">
         <v>2.68</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI14" t="n">
         <v>1.85</v>
@@ -6479,31 +6479,31 @@
         <v>1.53</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP14" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
@@ -6512,7 +6512,7 @@
         <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6521,7 +6521,7 @@
         <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA14" t="n">
         <v>1.84</v>
@@ -6530,85 +6530,85 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.77</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.85</v>
+        <v>49.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.31</v>
+        <v>15.43</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.08</v>
+        <v>13.86</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.69</v>
+        <v>7.57</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.46</v>
+        <v>49.86</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.92</v>
+        <v>14.43</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.71</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.23</v>
+        <v>20</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.86</v>
+        <v>3.62</v>
       </c>
       <c r="H15" t="n">
-        <v>72.56999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="K15" t="n">
-        <v>5.43</v>
+        <v>6.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M15" t="n">
-        <v>28.86</v>
+        <v>32.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.86</v>
+        <v>15.62</v>
       </c>
       <c r="R15" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.86</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.14</v>
+        <v>16.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.859999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>20</v>
+        <v>20.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6789,70 +6789,70 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.54</v>
+        <v>3.36</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.31</v>
+        <v>10.79</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.54</v>
+        <v>3.36</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.77</v>
+        <v>5.14</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CB15" t="n">
         <v>3.55</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
         <v>5.04</v>
@@ -6873,31 +6873,31 @@
         <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK15" t="n">
         <v>1.62</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN15" t="n">
         <v>1.73</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP15" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
@@ -6906,79 +6906,79 @@
         <v>3.18</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW15" t="n">
         <v>1.97</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB15" t="n">
         <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD15" t="n">
         <v>3.93</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="DH15" t="n">
-        <v>68.84999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.77</v>
+        <v>30.07</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.38</v>
+        <v>14.42</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.62</v>
+        <v>15.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.31</v>
+        <v>47.93</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.15</v>
+        <v>13</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.23</v>
+        <v>9.07</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.92</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.08</v>
+        <v>18.72</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
+        <v>77.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="L16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M16" t="n">
-        <v>38.33</v>
+        <v>39</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>14.17</v>
+        <v>14.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>14.43</v>
       </c>
       <c r="R16" t="n">
-        <v>9.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.17</v>
+        <v>47.29</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.460000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="BR16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CC16" t="n">
         <v>4.82</v>
@@ -7264,61 +7264,61 @@
         <v>5.43</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO16" t="n">
         <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
@@ -7336,85 +7336,85 @@
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DH16" t="n">
-        <v>76.92</v>
+        <v>77</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.3</v>
+        <v>35.86</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.62</v>
+        <v>14.93</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.54</v>
+        <v>14.72</v>
       </c>
       <c r="DR16" t="n">
         <v>10</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.93</v>
+        <v>46.08</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.07</v>
+        <v>7.14</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.69</v>
+        <v>16.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AI17" t="n">
-        <v>97</v>
+        <v>96.86</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>4.71</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.67</v>
+        <v>45.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.83</v>
+        <v>14.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.33</v>
+        <v>14.86</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.67</v>
+        <v>7.29</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.5</v>
+        <v>51.43</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.17</v>
+        <v>12.57</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BD17" t="n">
-        <v>22</v>
+        <v>21.86</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
         <v>2.25</v>
@@ -7655,19 +7655,19 @@
         <v>2.39</v>
       </c>
       <c r="CA17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CB17" t="n">
         <v>3.1</v>
       </c>
-      <c r="CB17" t="n">
-        <v>3.11</v>
-      </c>
       <c r="CC17" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
         <v>3.25</v>
@@ -7682,7 +7682,7 @@
         <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK17" t="n">
         <v>1.75</v>
@@ -7691,10 +7691,10 @@
         <v>2.34</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO17" t="n">
         <v>1.42</v>
@@ -7703,7 +7703,7 @@
         <v>2.32</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7718,10 +7718,10 @@
         <v>1.35</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX17" t="n">
         <v>1.8</v>
@@ -7736,88 +7736,88 @@
         <v>1.6</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.54</v>
+        <v>100.22</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.61</v>
+        <v>4.92</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.46</v>
+        <v>46.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.62</v>
+        <v>15.5</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.46</v>
+        <v>14.72</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.16</v>
+        <v>13.78</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.54</v>
+        <v>10.29</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.54</v>
+        <v>19.64</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="H18" t="n">
-        <v>96.70999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="K18" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="L18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M18" t="n">
-        <v>44.14</v>
+        <v>42.12</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.29</v>
+        <v>16.88</v>
       </c>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,25 +7893,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.29</v>
+        <v>47.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.71</v>
+        <v>14.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -7998,70 +7998,70 @@
         <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.539999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC18" t="n">
         <v>2.84</v>
@@ -8070,13 +8070,13 @@
         <v>3.28</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF18" t="n">
         <v>3.2</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH18" t="n">
         <v>1.3</v>
@@ -8091,22 +8091,22 @@
         <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO18" t="n">
         <v>1.4</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="CR18" t="n">
         <v>1.51</v>
@@ -8121,10 +8121,10 @@
         <v>1.34</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX18" t="n">
         <v>1.68</v>
@@ -8142,79 +8142,79 @@
         <v>1.45</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.92</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.15</v>
+        <v>39.28</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.46</v>
+        <v>16.57</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.85</v>
+        <v>16.64</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.61</v>
+        <v>6.71</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44</v>
+        <v>43.93</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.7</v>
+        <v>5.79</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="EA18" t="n">
-        <v>14.84</v>
+        <v>14.65</v>
       </c>
       <c r="EB18" t="n">
         <v>1.16</v>
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G19" t="n">
-        <v>3.17</v>
+        <v>3.71</v>
       </c>
       <c r="H19" t="n">
-        <v>97.17</v>
+        <v>102.14</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="P19" t="n">
-        <v>14.83</v>
+        <v>15.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.33</v>
+        <v>14.86</v>
       </c>
       <c r="R19" t="n">
-        <v>8.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>37.33</v>
+        <v>40.57</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>15.71</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.17</v>
+        <v>12</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>26.83</v>
+        <v>26.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.46</v>
+        <v>4.71</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,13 +8452,13 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="CA19" t="n">
         <v>3.14</v>
@@ -8476,10 +8476,10 @@
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8500,7 +8500,7 @@
         <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.37</v>
@@ -8530,16 +8530,16 @@
         <v>1.95</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
@@ -8551,79 +8551,79 @@
         <v>4.19</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.62</v>
+        <v>94.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.46</v>
+        <v>4.85</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM19" t="n">
-        <v>53.15</v>
+        <v>57.64</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.46</v>
+        <v>17.78</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.31</v>
+        <v>13.22</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.69</v>
+        <v>8.43</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>34.46</v>
+        <v>36.29</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.38</v>
+        <v>12.92</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.619999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.92</v>
+        <v>24.86</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>104.17</v>
+        <v>108.71</v>
       </c>
       <c r="I20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.67</v>
+        <v>4.14</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.33</v>
+        <v>-0.14</v>
       </c>
       <c r="M20" t="n">
-        <v>41.67</v>
+        <v>48</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O20" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="P20" t="n">
-        <v>14.67</v>
+        <v>15.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.67</v>
+        <v>16.57</v>
       </c>
       <c r="R20" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S20" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="T20" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V20" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>63.5</v>
+        <v>63.57</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.67</v>
+        <v>18.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.17</v>
+        <v>12.29</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.17</v>
+        <v>14.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF20" t="n">
         <v>0.14</v>
@@ -8804,70 +8804,70 @@
         <v>2.29</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="BR20" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>2.32</v>
@@ -8879,25 +8879,25 @@
         <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM20" t="n">
         <v>2.26</v>
@@ -8906,25 +8906,25 @@
         <v>1.77</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CV20" t="n">
         <v>1.95</v>
@@ -8933,97 +8933,97 @@
         <v>1.91</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="DH20" t="n">
-        <v>104.69</v>
+        <v>106.92</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK20" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM20" t="n">
-        <v>46.08</v>
+        <v>48.93</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.47</v>
+        <v>14.93</v>
       </c>
       <c r="DQ20" t="n">
-        <v>16.39</v>
+        <v>15.93</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.69</v>
+        <v>6.5</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61</v>
+        <v>61.22</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="DY20" t="n">
-        <v>10.85</v>
+        <v>11.43</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.85</v>
+        <v>5.08</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.08</v>
+        <v>16.78</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="EC20" t="n">
         <v>2</v>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0.14</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>80.33</v>
+        <v>82.14</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.17</v>
+        <v>41.86</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15.5</v>
+        <v>15.71</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>12.29</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>48.5</v>
+        <v>49.14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="BB21" t="n">
         <v>10</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.5</v>
+        <v>17.86</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="BH21" t="n">
-        <v>12.38</v>
+        <v>12.21</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.69</v>
+        <v>4.86</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.54</v>
+        <v>7.21</v>
       </c>
       <c r="BR21" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS21" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY21" t="n">
         <v>2.3</v>
@@ -9267,22 +9267,22 @@
         <v>2.36</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB21" t="n">
         <v>3.04</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CG21" t="n">
         <v>2.48</v>
@@ -9294,19 +9294,19 @@
         <v>1.74</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM21" t="n">
         <v>2.09</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO21" t="n">
         <v>1.42</v>
@@ -9318,118 +9318,118 @@
         <v>4.58</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS21" t="n">
         <v>3.36</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU21" t="n">
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="DG21" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.45999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="DK21" t="n">
-        <v>7.23</v>
+        <v>6.86</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.77</v>
+        <v>44.86</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DP21" t="n">
-        <v>15.69</v>
+        <v>15.78</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.77</v>
+        <v>11.5</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.69</v>
+        <v>47.14</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX21" t="n">
-        <v>14.93</v>
+        <v>14.79</v>
       </c>
       <c r="DY21" t="n">
-        <v>11.38</v>
+        <v>11.28</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.69</v>
+        <v>19.72</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.25</v>
+        <v>51.12</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.38</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.07</v>
+        <v>50</v>
       </c>
       <c r="DW2" t="n">
         <v>0.29</v>
@@ -2338,19 +2338,19 @@
         <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="BB4" t="n">
         <v>6.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BD4" t="n">
         <v>19.12</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BF4" t="n">
         <v>3.25</v>
@@ -2563,19 +2563,19 @@
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="DY4" t="n">
         <v>6.64</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="EA4" t="n">
         <v>18.28</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC4" t="n">
         <v>2.79</v>
@@ -6690,19 +6690,19 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.25</v>
+        <v>16.38</v>
       </c>
       <c r="AA15" t="n">
         <v>11.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.12</v>
+        <v>5.25</v>
       </c>
       <c r="AC15" t="n">
         <v>20.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE15" t="n">
         <v>1.12</v>
@@ -6996,19 +6996,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="DY15" t="n">
         <v>9.07</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="EA15" t="n">
         <v>18.72</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC15" t="n">
         <v>1.5</v>
@@ -7899,10 +7899,10 @@
         <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.380000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="AB18" t="n">
         <v>3.88</v>
@@ -7911,7 +7911,7 @@
         <v>14.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -8205,10 +8205,10 @@
         <v>0.36</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.79</v>
+        <v>5.72</v>
       </c>
       <c r="DZ18" t="n">
         <v>3.79</v>
@@ -8296,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>40.57</v>
+        <v>40.71</v>
       </c>
       <c r="Y19" t="n">
         <v>0.29</v>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>36.29</v>
+        <v>36.36</v>
       </c>
       <c r="DW19" t="n">
         <v>0.14</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0.14</v>
       </c>
-      <c r="AG3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>77.43000000000001</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.15</v>
-      </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.69</v>
+        <v>3.86</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>2.51</v>
@@ -2013,40 +2013,40 @@
         <v>2.89</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.15</v>
       </c>
-      <c r="CB3" t="n">
-        <v>3.14</v>
-      </c>
       <c r="CC3" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF3" t="n">
         <v>3.12</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
         <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM3" t="n">
         <v>2.19</v>
@@ -2058,16 +2058,16 @@
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT3" t="n">
         <v>2.76</v>
@@ -2076,10 +2076,10 @@
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX3" t="n">
         <v>1.66</v>
@@ -2103,79 +2103,79 @@
         <v>4.2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>75</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.54</v>
+        <v>30.22</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.23</v>
+        <v>14.14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.85</v>
+        <v>15.93</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49</v>
+        <v>48.28</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.08</v>
+        <v>10.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.77</v>
+        <v>16.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="4">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="H10" t="n">
-        <v>90.33</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>41.83</v>
+        <v>45.86</v>
       </c>
       <c r="N10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="P10" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.5</v>
+        <v>15.14</v>
       </c>
       <c r="R10" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.33</v>
+        <v>57</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>13.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.33</v>
+        <v>20.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,49 +4774,49 @@
         <v>3.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.460000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CC10" t="n">
         <v>3.17</v>
@@ -4849,7 +4849,7 @@
         <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CG10" t="n">
         <v>2.48</v>
@@ -4858,22 +4858,22 @@
         <v>1.29</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK10" t="n">
         <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
@@ -4882,16 +4882,16 @@
         <v>2.34</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS10" t="n">
         <v>3.41</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CU10" t="n">
         <v>1.33</v>
@@ -4906,97 +4906,97 @@
         <v>1.7</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.13</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
         <v>1.45</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DH10" t="n">
-        <v>92.06999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.23</v>
+        <v>40.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="DP10" t="n">
-        <v>18</v>
+        <v>17.92</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="DR10" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.23</v>
+        <v>54.72</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.69</v>
+        <v>12.07</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.92</v>
+        <v>8.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,139 +2678,139 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.70999999999999</v>
+        <v>88.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>46</v>
+        <v>42.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.86</v>
+        <v>13.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.29</v>
+        <v>14.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.71</v>
+        <v>7.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.14</v>
+        <v>50.25</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.57</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.71</v>
+        <v>20.12</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.43</v>
+        <v>9.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="BR5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY5" t="n">
         <v>2.64</v>
@@ -2819,28 +2819,28 @@
         <v>2.64</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI5" t="n">
         <v>1.83</v>
@@ -2849,34 +2849,34 @@
         <v>1.92</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN5" t="n">
         <v>1.76</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2909,79 +2909,79 @@
         <v>4.14</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.64</v>
+        <v>88</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.28</v>
+        <v>5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.78</v>
+        <v>45</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.36</v>
+        <v>14.27</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.14</v>
+        <v>15.53</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.57</v>
+        <v>7.8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.14</v>
+        <v>50.67</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.93</v>
+        <v>12.54</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.07</v>
+        <v>8.73</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.21</v>
+        <v>19.46</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>81.12</v>
+        <v>83</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K8" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>39.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>15.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.75</v>
+        <v>14.44</v>
       </c>
       <c r="R8" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>44.75</v>
+        <v>45.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.75</v>
+        <v>12.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.25</v>
+        <v>7.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>19.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,67 +3968,67 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.359999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.14</v>
+        <v>4.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CB8" t="n">
         <v>3.04</v>
@@ -4052,22 +4052,22 @@
         <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
@@ -4076,7 +4076,7 @@
         <v>2.31</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4097,16 +4097,16 @@
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.44</v>
@@ -4115,49 +4115,49 @@
         <v>2.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>81.36</v>
+        <v>82.47</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.86</v>
+        <v>4.07</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.57</v>
+        <v>39.66</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.36</v>
+        <v>16.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.43</v>
+        <v>14.26</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.5</v>
+        <v>46.93</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.64</v>
+        <v>11.13</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.71</v>
+        <v>7.07</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.57</v>
+        <v>18.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="9">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,52 +6305,52 @@
         <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>96</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN14" t="n">
-        <v>52.67</v>
+        <v>49.43</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18.5</v>
+        <v>17.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>51.17</v>
+        <v>50.57</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>12.43</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.83</v>
+        <v>18.43</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.5</v>
+        <v>9.67</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.93</v>
+        <v>5.13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
         <v>1.85</v>
@@ -6446,40 +6446,40 @@
         <v>1.88</v>
       </c>
       <c r="CA14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CB14" t="n">
         <v>3.39</v>
       </c>
-      <c r="CB14" t="n">
-        <v>3.42</v>
-      </c>
       <c r="CC14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
@@ -6488,13 +6488,13 @@
         <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP14" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6515,100 +6515,100 @@
         <v>1.89</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.43000000000001</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.43</v>
+        <v>48.13</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.43</v>
+        <v>15.2</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.86</v>
+        <v>13.87</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.57</v>
+        <v>7.34</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.86</v>
+        <v>49.67</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.43</v>
+        <v>14.47</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>20</v>
+        <v>19.74</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="H17" t="n">
-        <v>103.57</v>
+        <v>103.25</v>
       </c>
       <c r="I17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="K17" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="L17" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>47</v>
+        <v>46.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O17" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>16.29</v>
+        <v>16.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.57</v>
+        <v>14.25</v>
       </c>
       <c r="R17" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.57</v>
+        <v>50.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
         <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.43</v>
+        <v>16.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,67 +7595,67 @@
         <v>2.57</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.859999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.71</v>
+        <v>3.87</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB17" t="n">
         <v>3.1</v>
@@ -7670,10 +7670,10 @@
         <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7682,19 +7682,19 @@
         <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO17" t="n">
         <v>1.42</v>
@@ -7703,16 +7703,16 @@
         <v>2.32</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7739,85 +7739,85 @@
         <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.22</v>
+        <v>100.27</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.22</v>
+        <v>45.87</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.5</v>
+        <v>15.87</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.72</v>
+        <v>14.53</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.5</v>
+        <v>50.87</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.78</v>
+        <v>13.87</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.29</v>
+        <v>10.14</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.64</v>
+        <v>18.87</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="H2" t="n">
-        <v>79.67</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>35.17</v>
+        <v>32.43</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>7.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="T2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.5</v>
+        <v>45.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.83</v>
+        <v>9.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.17</v>
+        <v>17.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,70 +1550,70 @@
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ2" t="n">
         <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.93</v>
+        <v>6.13</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.72</v>
+        <v>3.01</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CC2" t="n">
         <v>3.4</v>
@@ -1625,10 +1625,10 @@
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CH2" t="n">
         <v>1.31</v>
@@ -1637,109 +1637,109 @@
         <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL2" t="n">
         <v>2.23</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.78</v>
+        <v>81</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.28</v>
+        <v>33.06</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.71</v>
+        <v>12.87</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.64</v>
+        <v>17.87</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DS2" t="n">
         <v>0.07000000000000001</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50</v>
+        <v>48.53</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.64</v>
+        <v>10.07</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.35</v>
+        <v>6.86</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.15</v>
+        <v>16.87</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>72.17</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="K3" t="n">
-        <v>3.83</v>
+        <v>4.57</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>29.33</v>
+        <v>35.14</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="P3" t="n">
-        <v>14.33</v>
+        <v>14.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>15.71</v>
       </c>
       <c r="R3" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.83</v>
+        <v>48.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.67</v>
+        <v>14.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,70 +1953,70 @@
         <v>1.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.16</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.15</v>
       </c>
       <c r="CC3" t="n">
         <v>3.68</v>
@@ -2025,10 +2025,10 @@
         <v>4.59</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG3" t="n">
         <v>2.51</v>
@@ -2043,43 +2043,43 @@
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL3" t="n">
         <v>2.15</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
         <v>1.66</v>
@@ -2094,55 +2094,55 @@
         <v>1.73</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DH3" t="n">
-        <v>73.56999999999999</v>
+        <v>75.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.22</v>
+        <v>32.87</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.14</v>
+        <v>14.33</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.93</v>
+        <v>15.4</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.28</v>
+        <v>49.46</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="DY3" t="n">
         <v>8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.36</v>
+        <v>16.54</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>88.33</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>35.17</v>
+        <v>32.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P4" t="n">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.17</v>
+        <v>16.29</v>
       </c>
       <c r="R4" t="n">
-        <v>7.33</v>
+        <v>7.71</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.83</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.67</v>
+        <v>10.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.17</v>
+        <v>16.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2359,46 +2359,46 @@
         <v>2.07</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.93</v>
+        <v>9.67</v>
       </c>
       <c r="BI4" t="n">
         <v>2.07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT4" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="CA4" t="n">
         <v>3.12</v>
@@ -2428,19 +2428,19 @@
         <v>3.95</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.97</v>
@@ -2458,13 +2458,13 @@
         <v>1.67</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="CR4" t="n">
         <v>1.52</v>
@@ -2482,7 +2482,7 @@
         <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
         <v>1.71</v>
@@ -2497,88 +2497,88 @@
         <v>1.69</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="DE4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.86</v>
+        <v>86.47</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
         <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.93</v>
+        <v>32</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.93</v>
+        <v>14.47</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>15.13</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.28</v>
+        <v>47.6</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.5</v>
+        <v>10.34</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.64</v>
+        <v>6.54</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.28</v>
+        <v>18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.25</v>
+        <v>50.12</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.67</v>
+        <v>50.6</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>95.67</v>
+        <v>94</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.33</v>
+        <v>40.71</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.17</v>
+        <v>11.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.67</v>
+        <v>58.29</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.33</v>
+        <v>11.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="BC6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>3.86</v>
-      </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.5</v>
@@ -3222,25 +3222,25 @@
         <v>2.75</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.53</v>
+        <v>3.83</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.92</v>
+        <v>4.23</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CH6" t="n">
         <v>1.32</v>
@@ -3255,7 +3255,7 @@
         <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM6" t="n">
         <v>2.1</v>
@@ -3264,13 +3264,13 @@
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3285,106 +3285,106 @@
         <v>1.35</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX6" t="n">
         <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="DE6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.93000000000001</v>
+        <v>83</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.71</v>
+        <v>4.53</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM6" t="n">
-        <v>37</v>
+        <v>37.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.93</v>
+        <v>11.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.21</v>
+        <v>17.93</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.140000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.43</v>
+        <v>55.47</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.57</v>
+        <v>13.2</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.35</v>
+        <v>9.07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.43</v>
+        <v>16.2</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>89</v>
+        <v>89.78</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AL7" t="n">
         <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.88</v>
+        <v>45.22</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.62</v>
+        <v>14.89</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.88</v>
+        <v>13.22</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,73 +3541,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.75</v>
+        <v>47.78</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.38</v>
+        <v>11.78</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.25</v>
+        <v>7.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.62</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.43</v>
+        <v>8.27</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.27</v>
@@ -3625,55 +3625,55 @@
         <v>2.32</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
         <v>3.12</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.96</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL7" t="n">
         <v>2.36</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP7" t="n">
         <v>2.31</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.23</v>
+        <v>4.28</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
@@ -3688,106 +3688,106 @@
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>87.06999999999999</v>
+        <v>87.67</v>
       </c>
       <c r="DI7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.72</v>
+        <v>47.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.78</v>
+        <v>14.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.08</v>
+        <v>11.8</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.36</v>
+        <v>47.4</v>
       </c>
       <c r="DW7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.07</v>
+        <v>12.27</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.720000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.42</v>
+        <v>19.13</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>80.33</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="K9" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M9" t="n">
-        <v>36.5</v>
+        <v>38.29</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O9" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="P9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.33</v>
+        <v>16.86</v>
       </c>
       <c r="R9" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.33</v>
+        <v>48.43</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.17</v>
+        <v>16.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.17</v>
+        <v>18.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC9" t="n">
         <v>3.3</v>
@@ -4464,19 +4464,19 @@
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO9" t="n">
         <v>1.34</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.74</v>
@@ -4485,7 +4485,7 @@
         <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CT9" t="n">
         <v>2.89</v>
@@ -4497,7 +4497,7 @@
         <v>2.05</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4506,7 +4506,7 @@
         <v>2.02</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA9" t="n">
         <v>1.8</v>
@@ -4518,82 +4518,82 @@
         <v>2.15</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.5</v>
+        <v>80.47</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>39.57</v>
+        <v>40.2</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP9" t="n">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.07</v>
+        <v>15.93</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.78</v>
+        <v>46.93</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.36</v>
+        <v>16.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.22</v>
+        <v>17.34</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.14</v>
@@ -4693,130 +4693,130 @@
         <v>2.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>93.56999999999999</v>
+        <v>91.38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.14</v>
+        <v>33.62</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.71</v>
+        <v>18.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.29</v>
+        <v>7.12</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.43</v>
+        <v>52.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.14</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.71</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BO10" t="n">
         <v>1.07</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.64</v>
+        <v>4.47</v>
       </c>
       <c r="BR10" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
         <v>2.48</v>
@@ -4834,169 +4834,169 @@
         <v>2.64</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CB10" t="n">
         <v>3.1</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CE10" t="n">
         <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG10" t="n">
         <v>2.48</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK10" t="n">
         <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DA10" t="n">
         <v>1.7</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.59</v>
+        <v>4.51</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.93000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.5</v>
+        <v>39.33</v>
       </c>
       <c r="DN10" t="n">
         <v>0.93</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.92</v>
+        <v>17.66</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.64</v>
+        <v>13.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>5.71</v>
+        <v>6.2</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.72</v>
+        <v>54.47</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.57</v>
+        <v>3.33</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.43</v>
+        <v>20.07</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G11" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>83.14</v>
+        <v>88.38</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>42.71</v>
+        <v>45.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.29</v>
+        <v>18.25</v>
       </c>
       <c r="R11" t="n">
-        <v>7.29</v>
+        <v>6.88</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="T11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>64.43000000000001</v>
+        <v>65.88</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.29</v>
+        <v>19.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.29</v>
+        <v>12.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.29</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
         <v>2.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.43</v>
+        <v>10.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CC11" t="n">
         <v>4.34</v>
@@ -5252,22 +5252,22 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH11" t="n">
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL11" t="n">
         <v>2.38</v>
@@ -5282,25 +5282,25 @@
         <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT11" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW11" t="n">
         <v>1.83</v>
@@ -5312,10 +5312,10 @@
         <v>2.14</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
@@ -5324,82 +5324,82 @@
         <v>2.04</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="DH11" t="n">
-        <v>84.92</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.78</v>
+        <v>5.13</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.86</v>
+        <v>41.67</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.14</v>
+        <v>13.07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19</v>
+        <v>18.93</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.58</v>
+        <v>7.34</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.72</v>
+        <v>62.67</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.5</v>
+        <v>15.66</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.93</v>
+        <v>10.07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="EA11" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="H12" t="n">
-        <v>104.71</v>
+        <v>102.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="K12" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>59.71</v>
+        <v>61.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="S12" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="V12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>54.57</v>
+        <v>53.25</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.14</v>
+        <v>16.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.57</v>
+        <v>10.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="AC12" t="n">
         <v>19</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
         <v>0.14</v>
@@ -5580,49 +5580,49 @@
         <v>2.43</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.43</v>
+        <v>5.47</v>
       </c>
       <c r="BR12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="CC12" t="n">
         <v>2.55</v>
@@ -5655,40 +5655,40 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM12" t="n">
         <v>2.05</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO12" t="n">
         <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5721,88 +5721,88 @@
         <v>1.65</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="DE12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="DH12" t="n">
-        <v>105.21</v>
+        <v>103.86</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.86</v>
+        <v>59.73</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.86</v>
+        <v>14.87</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.28</v>
+        <v>14.73</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.22</v>
+        <v>5.06</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.57</v>
+        <v>53.87</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.64</v>
+        <v>16.8</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.78</v>
+        <v>18.8</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>110.57</v>
+        <v>112.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>6.29</v>
+        <v>5.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M13" t="n">
-        <v>56.29</v>
+        <v>55.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.43</v>
+        <v>14.38</v>
       </c>
       <c r="R13" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="S13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>55.71</v>
+        <v>56.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.29</v>
+        <v>9.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.71</v>
+        <v>16.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5986,22 +5986,22 @@
         <v>2.07</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.57</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI13" t="n">
         <v>2.07</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
         <v>1</v>
@@ -6010,22 +6010,22 @@
         <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.36</v>
+        <v>4.13</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT13" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CC13" t="n">
         <v>2.31</v>
@@ -6058,7 +6058,7 @@
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG13" t="n">
         <v>2.6</v>
@@ -6067,7 +6067,7 @@
         <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.02</v>
@@ -6076,25 +6076,25 @@
         <v>1.73</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS13" t="n">
         <v>3.28</v>
@@ -6106,73 +6106,73 @@
         <v>1.35</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB13" t="n">
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
         <v>1.14</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.86</v>
+        <v>101.47</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.79</v>
+        <v>47</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13</v>
+        <v>13.54</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.21</v>
+        <v>53.86</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.08</v>
+        <v>13.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.64</v>
+        <v>16.74</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6708,52 +6708,52 @@
         <v>1.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>64.5</v>
+        <v>66.86</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.5</v>
+        <v>27.29</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.83</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.33</v>
+        <v>14.71</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.83</v>
+        <v>45.86</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.83</v>
+        <v>15.57</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.79</v>
+        <v>10.73</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY15" t="n">
         <v>3.48</v>
@@ -6849,16 +6849,16 @@
         <v>3.94</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.04</v>
+        <v>4.85</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.97</v>
+        <v>5.69</v>
       </c>
       <c r="CE15" t="n">
         <v>1.43</v>
@@ -6876,19 +6876,19 @@
         <v>1.79</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
         <v>2.18</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO15" t="n">
         <v>1.35</v>
@@ -6897,7 +6897,7 @@
         <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
@@ -6906,16 +6906,16 @@
         <v>3.18</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CX15" t="n">
         <v>1.66</v>
@@ -6930,88 +6930,88 @@
         <v>1.74</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="DE15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>47</v>
+      </c>
+      <c r="DW15" t="n">
         <v>0.14</v>
       </c>
-      <c r="DF15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>71.93000000000001</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>5</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DX15" t="n">
-        <v>13.08</v>
+        <v>13.27</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.07</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.72</v>
+        <v>18.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>76.86</v>
+        <v>73</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>32.71</v>
+        <v>31</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.86</v>
+        <v>42.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.71</v>
+        <v>16.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.210000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.36</v>
+        <v>5.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>3.21</v>
@@ -7252,40 +7252,40 @@
         <v>3.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.43</v>
+        <v>5.17</v>
       </c>
       <c r="CE16" t="n">
         <v>1.44</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM16" t="n">
         <v>2.13</v>
@@ -7294,19 +7294,19 @@
         <v>1.68</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CT16" t="n">
         <v>2.83</v>
@@ -7315,73 +7315,73 @@
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="DH16" t="n">
-        <v>77</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.86</v>
+        <v>34.73</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.93</v>
+        <v>15.14</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.72</v>
+        <v>14.53</v>
       </c>
       <c r="DR16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DS16" t="n">
         <v>0.07000000000000001</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.08</v>
+        <v>44.6</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.86</v>
+        <v>16.4</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="17">
@@ -7436,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
         <v>2.88</v>
@@ -7448,7 +7448,7 @@
         <v>0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="K17" t="n">
         <v>5.38</v>
@@ -7490,10 +7490,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.38</v>
+        <v>50.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>15</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DG17" t="n">
         <v>2.8</v>
@@ -7760,7 +7760,7 @@
         <v>0.47</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="DK17" t="n">
         <v>5.07</v>
@@ -7796,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.87</v>
+        <v>50.93</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
         <v>13.87</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7917,139 +7917,139 @@
         <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>79.83</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN18" t="n">
-        <v>35.5</v>
+        <v>36.71</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.33</v>
+        <v>16.71</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>39</v>
+        <v>40.86</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.83</v>
+        <v>10.43</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>15</v>
+        <v>16.86</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.710000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.07</v>
+        <v>5.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY18" t="n">
         <v>2.04</v>
@@ -8058,43 +8058,43 @@
         <v>2.13</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="CE18" t="n">
         <v>1.48</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH18" t="n">
         <v>1.3</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN18" t="n">
         <v>1.72</v>
@@ -8106,7 +8106,7 @@
         <v>2.33</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="CR18" t="n">
         <v>1.51</v>
@@ -8121,73 +8121,73 @@
         <v>1.34</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC18" t="n">
         <v>2.41</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.06999999999999</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.28</v>
+        <v>39.6</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.57</v>
+        <v>16.67</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.64</v>
+        <v>16.8</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.71</v>
+        <v>6.74</v>
       </c>
       <c r="DS18" t="n">
         <v>0.07000000000000001</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.93</v>
+        <v>44.47</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.72</v>
+        <v>6.07</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="EA18" t="n">
-        <v>14.65</v>
+        <v>15.54</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8323,127 +8323,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>86.86</v>
+        <v>87.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>47</v>
+        <v>47.12</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.71</v>
+        <v>19.88</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.57</v>
+        <v>7.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>32</v>
+        <v>32.62</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.43</v>
+        <v>6.88</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.29</v>
+        <v>22.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BH19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.71</v>
+        <v>4.47</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
         <v>2.46</v>
@@ -8461,22 +8461,22 @@
         <v>2.54</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.02</v>
+        <v>4.32</v>
       </c>
       <c r="CE19" t="n">
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG19" t="n">
         <v>2.6</v>
@@ -8485,49 +8485,49 @@
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK19" t="n">
         <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM19" t="n">
         <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
         <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS19" t="n">
         <v>3.31</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.64</v>
@@ -8536,94 +8536,94 @@
         <v>2.05</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DE19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.5</v>
+        <v>94.53</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.85</v>
+        <v>4.53</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM19" t="n">
-        <v>57.64</v>
+        <v>57</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.78</v>
+        <v>18</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.22</v>
+        <v>13.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.43</v>
+        <v>8.07</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>36.36</v>
+        <v>36.4</v>
       </c>
       <c r="DW19" t="n">
         <v>0.14</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.220000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.86</v>
+        <v>24.33</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0.29</v>
@@ -8723,139 +8723,139 @@
         <v>1.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="AI20" t="n">
-        <v>105.14</v>
+        <v>108.25</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.29</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN20" t="n">
-        <v>49.86</v>
+        <v>53</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.29</v>
+        <v>15.12</v>
       </c>
       <c r="AR20" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>58.86</v>
+        <v>60.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.86</v>
+        <v>16.25</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.57</v>
+        <v>11.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.29</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.71</v>
+        <v>18.88</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.789999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS20" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT20" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY20" t="n">
         <v>1.82</v>
@@ -8864,25 +8864,25 @@
         <v>1.83</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="CE20" t="n">
         <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH20" t="n">
         <v>1.36</v>
@@ -8897,7 +8897,7 @@
         <v>1.57</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM20" t="n">
         <v>2.26</v>
@@ -8906,10 +8906,10 @@
         <v>1.77</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ20" t="n">
         <v>3.6</v>
@@ -8918,115 +8918,115 @@
         <v>1.43</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.26</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB20" t="n">
         <v>1.35</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.92</v>
+        <v>108.46</v>
       </c>
       <c r="DI20" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.22</v>
+        <v>4.6</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM20" t="n">
-        <v>48.93</v>
+        <v>50.67</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.93</v>
+        <v>15.33</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.93</v>
+        <v>15.87</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.22</v>
+        <v>61.93</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX20" t="n">
-        <v>16.5</v>
+        <v>17.13</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.43</v>
+        <v>11.74</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.08</v>
+        <v>5.4</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.78</v>
+        <v>17</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="H21" t="n">
-        <v>84.29000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J21" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>8.140000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>47.86</v>
+        <v>48.88</v>
       </c>
       <c r="N21" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O21" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>15.86</v>
+        <v>16.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.71</v>
+        <v>11.62</v>
       </c>
       <c r="R21" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="S21" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T21" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45.14</v>
+        <v>45.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.29</v>
+        <v>15.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>12.57</v>
+        <v>11.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.57</v>
+        <v>22</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,67 +9207,67 @@
         <v>1.86</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BH21" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS21" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB21" t="n">
         <v>3.04</v>
@@ -9282,40 +9282,40 @@
         <v>1.5</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH21" t="n">
         <v>1.29</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL21" t="n">
         <v>2.21</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO21" t="n">
         <v>1.42</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="CR21" t="n">
         <v>1.5</v>
@@ -9330,106 +9330,106 @@
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CY21" t="n">
         <v>2.07</v>
       </c>
-      <c r="CX21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>2.09</v>
-      </c>
       <c r="CZ21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DB21" t="n">
         <v>1.47</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.22</v>
+        <v>82.87</v>
       </c>
       <c r="DI21" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.86</v>
+        <v>6.73</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.86</v>
+        <v>45.6</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DP21" t="n">
-        <v>15.78</v>
+        <v>16</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.5</v>
+        <v>11.93</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.36</v>
+        <v>7.27</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.14</v>
+        <v>47.2</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX21" t="n">
-        <v>14.79</v>
+        <v>14.2</v>
       </c>
       <c r="DY21" t="n">
-        <v>11.28</v>
+        <v>10.74</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.72</v>
+        <v>20.07</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -9084,7 +9084,7 @@
         <v>11.62</v>
       </c>
       <c r="R21" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="S21" t="n">
         <v>0.88</v>
@@ -9396,7 +9396,7 @@
         <v>11.93</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.27</v>
+        <v>7.2</v>
       </c>
       <c r="DS21" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.12</v>
+        <v>84.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.62</v>
+        <v>32.78</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ2" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BV2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>86.67</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY2" t="n">
         <v>2.81</v>
@@ -1610,43 +1610,43 @@
         <v>3.01</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="CE2" t="n">
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.96</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN2" t="n">
         <v>1.69</v>
@@ -1655,22 +1655,22 @@
         <v>1.38</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV2" t="n">
         <v>1.9</v>
@@ -1679,100 +1679,100 @@
         <v>1.96</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DH2" t="n">
-        <v>81</v>
+        <v>80.81</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM2" t="n">
-        <v>33.06</v>
+        <v>32.63</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.87</v>
+        <v>13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.87</v>
+        <v>17.56</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.66</v>
+        <v>9.44</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.53</v>
+        <v>48.25</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.07</v>
+        <v>9.81</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.86</v>
+        <v>6.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.87</v>
+        <v>17.57</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.29</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>74.62</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>30.88</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.13</v>
-      </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY3" t="n">
         <v>2.44</v>
@@ -2013,25 +2013,25 @@
         <v>2.77</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.59</v>
+        <v>4.63</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
@@ -2046,7 +2046,7 @@
         <v>1.62</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM3" t="n">
         <v>2.2</v>
@@ -2070,7 +2070,7 @@
         <v>3.22</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2085,7 +2085,7 @@
         <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.19</v>
@@ -2100,82 +2100,82 @@
         <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>75.06</v>
+        <v>77.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>32.87</v>
+        <v>34.81</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.33</v>
+        <v>14.37</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.4</v>
+        <v>15.31</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.33</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.46</v>
+        <v>50.68</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.67</v>
+        <v>10.88</v>
       </c>
       <c r="DY3" t="n">
-        <v>8</v>
+        <v>8.19</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.54</v>
+        <v>16.88</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>84</v>
+        <v>85.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN4" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BN4" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.87</v>
+        <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY4" t="n">
         <v>2.84</v>
@@ -2419,13 +2419,13 @@
         <v>3.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
@@ -2434,25 +2434,25 @@
         <v>3.19</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN4" t="n">
         <v>1.67</v>
@@ -2461,10 +2461,10 @@
         <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CR4" t="n">
         <v>1.52</v>
@@ -2473,7 +2473,7 @@
         <v>3.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CU4" t="n">
         <v>1.34</v>
@@ -2485,7 +2485,7 @@
         <v>2.03</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY4" t="n">
         <v>2.14</v>
@@ -2500,22 +2500,22 @@
         <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.47</v>
+        <v>87.12</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
@@ -2524,61 +2524,61 @@
         <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>32</v>
+        <v>31.63</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.47</v>
+        <v>14.31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.13</v>
+        <v>14.82</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.869999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.6</v>
+        <v>48.25</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.34</v>
+        <v>10.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.54</v>
+        <v>6.44</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>18</v>
+        <v>17.87</v>
       </c>
       <c r="EB4" t="n">
         <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>87.56999999999999</v>
+        <v>87.75</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>47.57</v>
+        <v>47.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
-        <v>14.86</v>
+        <v>14.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="R5" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>51.14</v>
+        <v>50.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.29</v>
+        <v>14.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.71</v>
+        <v>18.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.25</v>
@@ -2759,67 +2759,67 @@
         <v>2.38</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.33</v>
+        <v>9.44</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="BR5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB5" t="n">
         <v>3.14</v>
@@ -2834,10 +2834,10 @@
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH5" t="n">
         <v>1.33</v>
@@ -2852,31 +2852,31 @@
         <v>1.58</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO5" t="n">
         <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2888,100 +2888,100 @@
         <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
         <v>1.39</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
         <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>88</v>
+        <v>88.06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DK5" t="n">
         <v>5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>45</v>
+        <v>44.94</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.27</v>
+        <v>14.18</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.53</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.6</v>
+        <v>50.31</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.54</v>
+        <v>12.69</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.73</v>
+        <v>8.81</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.46</v>
+        <v>19.44</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>73.38</v>
+        <v>77.67</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>34.5</v>
+        <v>35.89</v>
       </c>
       <c r="N6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>11.75</v>
+        <v>11.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.75</v>
+        <v>18.33</v>
       </c>
       <c r="R6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53</v>
+        <v>53.33</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.5</v>
+        <v>18.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,70 +3162,70 @@
         <v>2.14</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9</v>
+        <v>8.81</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CC6" t="n">
         <v>3.83</v>
@@ -3237,154 +3237,154 @@
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG6" t="n">
         <v>2.59</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CM6" t="n">
         <v>2.1</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO6" t="n">
         <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB6" t="n">
         <v>1.4</v>
       </c>
       <c r="DC6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>84.81</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>38</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DO6" t="n">
         <v>2.31</v>
       </c>
-      <c r="DD6" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>83</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>2.33</v>
-      </c>
       <c r="DP6" t="n">
-        <v>11.6</v>
+        <v>11.69</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.93</v>
+        <v>17.75</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.47</v>
+        <v>55.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.2</v>
+        <v>13.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.07</v>
+        <v>9.19</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,79 +3406,79 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="n">
-        <v>84.5</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="K7" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>50.17</v>
+        <v>50.71</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.83</v>
+        <v>47.29</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.67</v>
+        <v>10.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.83</v>
+        <v>17.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.27</v>
+        <v>8.31</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU7" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CC7" t="n">
         <v>2.98</v>
@@ -3640,10 +3640,10 @@
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3658,7 +3658,7 @@
         <v>1.79</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM7" t="n">
         <v>1.94</v>
@@ -3667,31 +3667,31 @@
         <v>1.59</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX7" t="n">
         <v>1.81</v>
@@ -3706,88 +3706,88 @@
         <v>1.6</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="DH7" t="n">
-        <v>87.67</v>
+        <v>88.44</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.2</v>
+        <v>47.62</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.93</v>
+        <v>15.06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.47</v>
+        <v>7.56</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.4</v>
+        <v>47.57</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.27</v>
+        <v>12.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.869999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.13</v>
+        <v>18.81</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.67</v>
+        <v>81.14</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.33</v>
+        <v>39.71</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.83</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.83</v>
+        <v>48.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>17.57</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4034,16 +4034,16 @@
         <v>3.04</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CG8" t="n">
         <v>2.51</v>
@@ -4052,7 +4052,7 @@
         <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.96</v>
@@ -4064,19 +4064,19 @@
         <v>2.14</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN8" t="n">
         <v>1.71</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
         <v>2.31</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4100,7 +4100,7 @@
         <v>1.65</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.2</v>
@@ -4115,82 +4115,82 @@
         <v>2.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>82.47</v>
+        <v>82.19</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.66</v>
+        <v>39.43</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.2</v>
+        <v>16.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.26</v>
+        <v>14.62</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.93</v>
+        <v>47</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.13</v>
+        <v>11.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.07</v>
+        <v>7.19</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.07</v>
+        <v>3.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.33</v>
+        <v>18.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.43</v>
@@ -4290,139 +4290,139 @@
         <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.12</v>
+        <v>77.11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.88</v>
+        <v>40.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19</v>
+        <v>18.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.62</v>
+        <v>45.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.12</v>
+        <v>10.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.470000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY9" t="n">
         <v>2.4</v>
@@ -4431,169 +4431,169 @@
         <v>2.55</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CO9" t="n">
         <v>1.34</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.27</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.47</v>
+        <v>80.25</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.2</v>
+        <v>39.63</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.93</v>
+        <v>15.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.93</v>
+        <v>46.88</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.47</v>
+        <v>16.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>11</v>
+        <v>10.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.47</v>
+        <v>5.63</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.34</v>
+        <v>17.56</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
-        <v>96.29000000000001</v>
+        <v>95.25</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>45.86</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="P10" t="n">
-        <v>17.14</v>
+        <v>17.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.14</v>
+        <v>15.5</v>
       </c>
       <c r="R10" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57</v>
+        <v>56.38</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.57</v>
+        <v>12.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,49 +4774,49 @@
         <v>3.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.73</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,16 +4825,16 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB10" t="n">
         <v>3.1</v>
@@ -4852,37 +4852,37 @@
         <v>3.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH10" t="n">
         <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.98</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL10" t="n">
         <v>2.19</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="CR10" t="n">
         <v>1.52</v>
@@ -4900,7 +4900,7 @@
         <v>1.85</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX10" t="n">
         <v>1.69</v>
@@ -4909,10 +4909,10 @@
         <v>2.12</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
@@ -4921,49 +4921,49 @@
         <v>2.41</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.67</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.33</v>
+        <v>39.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.66</v>
+        <v>17.81</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.47</v>
+        <v>13.75</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.47</v>
+        <v>54.32</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.93</v>
+        <v>11.69</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.6</v>
+        <v>8.25</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="EB10" t="n">
         <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>86.70999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>37</v>
+        <v>37.88</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.14</v>
+        <v>12.38</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.71</v>
+        <v>19.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59</v>
+        <v>57.88</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.71</v>
+        <v>16.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>2.49</v>
@@ -5237,16 +5237,16 @@
         <v>2.71</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="CD11" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5255,43 +5255,43 @@
         <v>2.86</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH11" t="n">
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
         <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM11" t="n">
         <v>2.04</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
         <v>2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CT11" t="n">
         <v>2.99</v>
@@ -5300,7 +5300,7 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW11" t="n">
         <v>1.83</v>
@@ -5324,82 +5324,82 @@
         <v>2.04</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DG11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.59999999999999</v>
+        <v>86.94</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.67</v>
+        <v>41.82</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.07</v>
+        <v>12.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.93</v>
+        <v>18.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.34</v>
+        <v>7.19</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.67</v>
+        <v>61.88</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.66</v>
+        <v>15.62</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.6</v>
+        <v>5.69</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.8</v>
+        <v>16.38</v>
       </c>
       <c r="EB11" t="n">
         <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>105.71</v>
+        <v>101.88</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.57</v>
+        <v>6.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>58</v>
+        <v>57.38</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.86</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.43</v>
+        <v>14.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54.57</v>
+        <v>52.88</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>17.14</v>
+        <v>18.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.29</v>
+        <v>13.88</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.86</v>
+        <v>4.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.57</v>
+        <v>17.88</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.47</v>
+        <v>5.69</v>
       </c>
       <c r="BR12" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY12" t="n">
         <v>1.85</v>
@@ -5640,28 +5640,28 @@
         <v>1.81</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
         <v>2.55</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG12" t="n">
         <v>2.61</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
         <v>1.79</v>
@@ -5673,19 +5673,19 @@
         <v>1.72</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ12" t="n">
         <v>4</v>
@@ -5694,10 +5694,10 @@
         <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5709,100 +5709,100 @@
         <v>1.99</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
         <v>2.3</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>103.86</v>
+        <v>102.06</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.73</v>
+        <v>5.94</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>59.73</v>
+        <v>59.32</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.87</v>
+        <v>15.44</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.73</v>
+        <v>14.56</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.87</v>
+        <v>53.06</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="DY12" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.8</v>
+        <v>5.12</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.8</v>
+        <v>18.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.12</v>
@@ -5902,130 +5902,130 @@
         <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.43</v>
       </c>
-      <c r="AH13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>89.14</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1</v>
       </c>
-      <c r="BO13" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY13" t="n">
         <v>1.74</v>
@@ -6043,16 +6043,16 @@
         <v>1.76</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
@@ -6061,22 +6061,22 @@
         <v>3.15</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>2.02</v>
@@ -6091,7 +6091,7 @@
         <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
@@ -6100,25 +6100,25 @@
         <v>3.28</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DA13" t="n">
         <v>1.63</v>
@@ -6127,52 +6127,52 @@
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.47</v>
+        <v>100.75</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DM13" t="n">
-        <v>47</v>
+        <v>46.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.46</v>
+        <v>15.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.54</v>
+        <v>13.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.86</v>
+        <v>53.18</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.87</v>
+        <v>13.62</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.07</v>
+        <v>3.88</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.74</v>
+        <v>16.31</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6227,82 +6227,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H14" t="n">
-        <v>91.5</v>
+        <v>90.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M14" t="n">
-        <v>47</v>
+        <v>44.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.88</v>
+        <v>48.22</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.25</v>
+        <v>16.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.88</v>
+        <v>20.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
         <v>0.29</v>
@@ -6386,70 +6386,70 @@
         <v>2.71</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.67</v>
+        <v>9.44</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>1.85</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CA14" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CC14" t="n">
         <v>2.44</v>
@@ -6470,16 +6470,16 @@
         <v>1.35</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK14" t="n">
         <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
@@ -6503,7 +6503,7 @@
         <v>3.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
@@ -6512,70 +6512,70 @@
         <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DG14" t="n">
         <v>2.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.73999999999999</v>
+        <v>92.88</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.13</v>
+        <v>46.75</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO14" t="n">
         <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.87</v>
+        <v>14.13</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.34</v>
+        <v>7.31</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.67</v>
+        <v>49.25</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.47</v>
+        <v>14.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.74</v>
+        <v>19.63</v>
       </c>
       <c r="EB14" t="n">
         <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="H15" t="n">
-        <v>77.5</v>
+        <v>78.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="K15" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M15" t="n">
-        <v>32.75</v>
+        <v>34.44</v>
       </c>
       <c r="N15" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="P15" t="n">
-        <v>14.12</v>
+        <v>14.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.62</v>
+        <v>15.67</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48</v>
+        <v>48.67</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.38</v>
+        <v>16.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.88</v>
+        <v>20.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0.29</v>
@@ -6789,70 +6789,70 @@
         <v>2.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.73</v>
+        <v>10.81</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CC15" t="n">
         <v>4.85</v>
@@ -6864,154 +6864,154 @@
         <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CH15" t="n">
         <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX15" t="n">
         <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.2</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
         <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DF15" t="n">
         <v>1.13</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="DH15" t="n">
-        <v>72.53</v>
+        <v>73.31</v>
       </c>
       <c r="DI15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="DW15" t="n">
         <v>0.13</v>
       </c>
-      <c r="DJ15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>14.06</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>47</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DX15" t="n">
-        <v>13.27</v>
+        <v>13.69</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.06</v>
+        <v>4.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.4</v>
+        <v>18.38</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7033,79 +7033,79 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G16" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>77.14</v>
+        <v>79</v>
       </c>
       <c r="I16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>40.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>14.86</v>
+        <v>14.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.43</v>
+        <v>14.12</v>
       </c>
       <c r="R16" t="n">
-        <v>9.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.29</v>
+        <v>46.62</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.14</v>
+        <v>12.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
         <v>16</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -7192,70 +7192,70 @@
         <v>2.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.470000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU16" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="CA16" t="n">
         <v>3.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CC16" t="n">
         <v>4.72</v>
@@ -7264,28 +7264,28 @@
         <v>5.17</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI16" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK16" t="n">
         <v>1.67</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM16" t="n">
         <v>2.13</v>
@@ -7297,19 +7297,19 @@
         <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7318,7 +7318,7 @@
         <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
@@ -7333,88 +7333,88 @@
         <v>1.73</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.93000000000001</v>
+        <v>76</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.33</v>
+        <v>3.56</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.73</v>
+        <v>35.56</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.14</v>
+        <v>14.82</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.53</v>
+        <v>14.37</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.6</v>
+        <v>44.44</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.6</v>
+        <v>10.75</v>
       </c>
       <c r="DY16" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.4</v>
+        <v>16.38</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>96.86</v>
+        <v>97.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>45.43</v>
+        <v>44.62</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.71</v>
+        <v>15.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.86</v>
+        <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.43</v>
+        <v>52.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.57</v>
+        <v>11.88</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.86</v>
+        <v>22.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.93</v>
+        <v>4.81</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY17" t="n">
         <v>2.24</v>
@@ -7655,25 +7655,25 @@
         <v>2.37</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="CD17" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7685,34 +7685,34 @@
         <v>1.98</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL17" t="n">
         <v>2.31</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO17" t="n">
         <v>1.42</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7724,100 +7724,100 @@
         <v>2.01</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="EB17" t="n">
         <v>1.44</v>
       </c>
-      <c r="DC17" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DD17" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>100.27</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DK17" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="DL17" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DM17" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DO17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DP17" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="DQ17" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="DR17" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="DS17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DT17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV17" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="DW17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DX17" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="DY17" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="DZ17" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="EA17" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="EB17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="EC17" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H18" t="n">
-        <v>94.25</v>
+        <v>94.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J18" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M18" t="n">
-        <v>42.12</v>
+        <v>42.56</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="P18" t="n">
-        <v>16.25</v>
+        <v>15.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.88</v>
+        <v>17.67</v>
       </c>
       <c r="R18" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.62</v>
+        <v>48.89</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.38</v>
+        <v>14.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF18" t="n">
         <v>0.14</v>
@@ -7998,70 +7998,70 @@
         <v>2.29</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.2</v>
+        <v>5.44</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU18" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="CA18" t="n">
         <v>3.08</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CC18" t="n">
         <v>2.89</v>
@@ -8076,7 +8076,7 @@
         <v>3.22</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH18" t="n">
         <v>1.3</v>
@@ -8091,10 +8091,10 @@
         <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN18" t="n">
         <v>1.72</v>
@@ -8106,13 +8106,13 @@
         <v>2.33</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CR18" t="n">
         <v>1.51</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CT18" t="n">
         <v>2.65</v>
@@ -8127,16 +8127,16 @@
         <v>2.04</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.2</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB18" t="n">
         <v>1.44</v>
@@ -8148,79 +8148,79 @@
         <v>4.47</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.45999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.27</v>
+        <v>4.18</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="DN18" t="n">
         <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.67</v>
+        <v>16.38</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.8</v>
+        <v>17.25</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.74</v>
+        <v>6.75</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.47</v>
+        <v>45.38</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.54</v>
+        <v>15.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>102.14</v>
+        <v>99.38</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J19" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="K19" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>68.29000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="O19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="R19" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>26.43</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.6</v>
+        <v>8.44</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,13 +8452,13 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>2.46</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>2.54</v>
       </c>
       <c r="CA19" t="n">
         <v>3.2</v>
@@ -8479,7 +8479,7 @@
         <v>3.07</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8488,19 +8488,19 @@
         <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK19" t="n">
         <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CM19" t="n">
         <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.37</v>
@@ -8509,16 +8509,16 @@
         <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
@@ -8527,19 +8527,19 @@
         <v>1.9</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
@@ -8548,49 +8548,49 @@
         <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.53</v>
+        <v>93.63</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM19" t="n">
-        <v>57</v>
+        <v>55.68</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP19" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.33</v>
+        <v>13.44</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.07</v>
+        <v>8.32</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>36.4</v>
+        <v>36.06</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.93</v>
+        <v>12.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.33</v>
+        <v>24.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="n">
-        <v>108.71</v>
+        <v>106.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K20" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="M20" t="n">
-        <v>48</v>
+        <v>46.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="P20" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.57</v>
+        <v>16.38</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>63.57</v>
+        <v>62.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.14</v>
+        <v>17.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.86</v>
+        <v>15.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8804,70 +8804,70 @@
         <v>2.38</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH20" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>2.24</v>
@@ -8879,16 +8879,16 @@
         <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CH20" t="n">
         <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.88</v>
@@ -8900,16 +8900,16 @@
         <v>2.12</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ20" t="n">
         <v>3.6</v>
@@ -8918,10 +8918,10 @@
         <v>1.43</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
@@ -8933,16 +8933,16 @@
         <v>1.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB20" t="n">
         <v>1.35</v>
@@ -8954,79 +8954,79 @@
         <v>3.76</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH20" t="n">
-        <v>108.46</v>
+        <v>107.18</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM20" t="n">
-        <v>50.67</v>
+        <v>49.88</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.33</v>
+        <v>15.18</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.87</v>
+        <v>15.82</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.93</v>
+        <v>61.62</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.13</v>
+        <v>17</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.74</v>
+        <v>11.62</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="EA20" t="n">
         <v>17</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0.12</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.14</v>
+        <v>82.88</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF21" t="n">
         <v>2</v>
       </c>
-      <c r="AL21" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>41.86</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>49.14</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BG21" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="n">
-        <v>12.13</v>
+        <v>12.06</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="BR21" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS21" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV21" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY21" t="n">
         <v>2.32</v>
@@ -9267,169 +9267,169 @@
         <v>2.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB21" t="n">
         <v>3.04</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="CE21" t="n">
         <v>1.5</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CH21" t="n">
         <v>1.29</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CL21" t="n">
         <v>2.21</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="CR21" t="n">
         <v>1.5</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CU21" t="n">
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY21" t="n">
         <v>2.06</v>
       </c>
-      <c r="CX21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>2.07</v>
-      </c>
       <c r="CZ21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.87</v>
+        <v>83.19</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.73</v>
+        <v>6.68</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DM21" t="n">
-        <v>45.6</v>
+        <v>45.63</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DP21" t="n">
-        <v>16</v>
+        <v>15.93</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.2</v>
+        <v>47.62</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>14.2</v>
+        <v>13.94</v>
       </c>
       <c r="DY21" t="n">
-        <v>10.74</v>
+        <v>10.57</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -3469,16 +3469,16 @@
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.86</v>
+        <v>10.71</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="AC7" t="n">
         <v>17.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3775,10 +3775,10 @@
         <v>12.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="EA7" t="n">
         <v>18.81</v>
@@ -6257,7 +6257,7 @@
         <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
@@ -6569,7 +6569,7 @@
         <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="DQ14" t="n">
         <v>14.13</v>
@@ -7547,7 +7547,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.12</v>
+        <v>15.38</v>
       </c>
       <c r="AR17" t="n">
         <v>14.5</v>
@@ -7778,7 +7778,7 @@
         <v>2.12</v>
       </c>
       <c r="DP17" t="n">
-        <v>16</v>
+        <v>16.13</v>
       </c>
       <c r="DQ17" t="n">
         <v>14.38</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>76.29000000000001</v>
+        <v>74.75</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>32.43</v>
+        <v>33.62</v>
       </c>
       <c r="N2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="R2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.57</v>
+        <v>46.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>6</v>
+        <v>5.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.43</v>
+        <v>17.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2.44</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.69</v>
+        <v>9.59</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.94</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CC2" t="n">
         <v>3.45</v>
@@ -1622,13 +1622,13 @@
         <v>4.02</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH2" t="n">
         <v>1.32</v>
@@ -1637,109 +1637,109 @@
         <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU2" t="n">
         <v>1.37</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW2" t="n">
         <v>1.96</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DB2" t="n">
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DH2" t="n">
-        <v>80.81</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM2" t="n">
-        <v>32.63</v>
+        <v>33.18</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.56</v>
+        <v>17.82</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.25</v>
+        <v>48.53</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.81</v>
+        <v>9.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.69</v>
+        <v>6.47</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.13</v>
+        <v>3.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.57</v>
+        <v>17.41</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>75.56999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>35.14</v>
+        <v>35.38</v>
       </c>
       <c r="N3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>14.71</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.71</v>
+        <v>15.38</v>
       </c>
       <c r="R3" t="n">
-        <v>9.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.71</v>
+        <v>47.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.43</v>
+        <v>14.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
         <v>1.06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.16</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
         <v>3.66</v>
@@ -2031,7 +2031,7 @@
         <v>3.1</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
@@ -2043,13 +2043,13 @@
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN3" t="n">
         <v>1.73</v>
@@ -2070,7 +2070,7 @@
         <v>3.22</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2079,19 +2079,19 @@
         <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
@@ -2100,73 +2100,73 @@
         <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.5</v>
+        <v>76.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>34.81</v>
+        <v>34.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.37</v>
+        <v>14.53</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.31</v>
+        <v>15.18</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.119999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.68</v>
+        <v>49.88</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.88</v>
+        <v>10.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.19</v>
+        <v>8.06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="EA3" t="n">
         <v>16.88</v>
@@ -2175,7 +2175,7 @@
         <v>1.13</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>89.29000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>32.86</v>
+        <v>33.62</v>
       </c>
       <c r="N4" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="P4" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.29</v>
+        <v>16.5</v>
       </c>
       <c r="R4" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51</v>
+        <v>52.62</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.29</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.71</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2359,22 +2359,22 @@
         <v>2.12</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.81</v>
+        <v>9.65</v>
       </c>
       <c r="BI4" t="n">
         <v>2.12</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
         <v>1.12</v>
@@ -2386,19 +2386,19 @@
         <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY4" t="n">
         <v>2.84</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC4" t="n">
         <v>3.4</v>
@@ -2428,13 +2428,13 @@
         <v>3.94</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
@@ -2443,28 +2443,28 @@
         <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK4" t="n">
         <v>1.68</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CM4" t="n">
         <v>2.1</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO4" t="n">
         <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.52</v>
@@ -2482,19 +2482,19 @@
         <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
         <v>1.7</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB4" t="n">
         <v>1.45</v>
@@ -2509,76 +2509,76 @@
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.12</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.63</v>
+        <v>32.06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.31</v>
+        <v>14.3</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.82</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.25</v>
+        <v>49.17</v>
       </c>
       <c r="DW4" t="n">
         <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.31</v>
+        <v>10.41</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.44</v>
+        <v>6.65</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.87</v>
+        <v>18.18</v>
       </c>
       <c r="EB4" t="n">
         <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.38</v>
+        <v>88.56</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>42.75</v>
+        <v>43.78</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.75</v>
+        <v>13.56</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.25</v>
+        <v>6.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.12</v>
+        <v>50</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>10.78</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.12</v>
+        <v>18.89</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.44</v>
+        <v>9.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="BR5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU5" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
         <v>2.62</v>
@@ -2819,28 +2819,28 @@
         <v>2.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.02</v>
+        <v>4.27</v>
       </c>
       <c r="CE5" t="n">
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CG5" t="n">
         <v>2.61</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI5" t="n">
         <v>1.83</v>
@@ -2852,7 +2852,7 @@
         <v>1.58</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM5" t="n">
         <v>2.24</v>
@@ -2861,31 +2861,31 @@
         <v>1.77</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CR5" t="n">
         <v>1.47</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX5" t="n">
         <v>1.62</v>
@@ -2903,85 +2903,85 @@
         <v>1.39</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.06</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.94</v>
+        <v>45.35</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.18</v>
+        <v>14.06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>15.29</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.88</v>
+        <v>7.53</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.31</v>
+        <v>50.24</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.69</v>
+        <v>12.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.81</v>
+        <v>8.59</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.44</v>
+        <v>18.82</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI6" t="n">
-        <v>94</v>
+        <v>95.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.71</v>
+        <v>43.25</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.29</v>
+        <v>58.88</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.71</v>
+        <v>11.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="BD6" t="n">
-        <v>12.43</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.81</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
         <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BQ6" t="n">
         <v>3.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>2.44</v>
@@ -3222,16 +3222,16 @@
         <v>2.64</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.83</v>
+        <v>3.66</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="CE6" t="n">
         <v>1.45</v>
@@ -3240,7 +3240,7 @@
         <v>3.12</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH6" t="n">
         <v>1.33</v>
@@ -3252,13 +3252,13 @@
         <v>1.94</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL6" t="n">
         <v>2.28</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN6" t="n">
         <v>1.66</v>
@@ -3270,7 +3270,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3291,13 +3291,13 @@
         <v>1.96</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA6" t="n">
         <v>1.69</v>
@@ -3306,85 +3306,85 @@
         <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.81</v>
+        <v>86.06</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM6" t="n">
-        <v>38</v>
+        <v>39.35</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.69</v>
+        <v>11.82</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.5</v>
+        <v>55.94</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.25</v>
+        <v>13.17</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.19</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.06</v>
       </c>
       <c r="EA6" t="n">
-        <v>16</v>
+        <v>16.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,79 +3406,79 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>86.70999999999999</v>
+        <v>89.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K7" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>50.71</v>
+        <v>48.62</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>15.29</v>
+        <v>14.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.289999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.29</v>
+        <v>46.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.71</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.29</v>
+        <v>17.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.31</v>
+        <v>8.18</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CA7" t="n">
         <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC7" t="n">
         <v>2.98</v>
@@ -3640,10 +3640,10 @@
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3658,13 +3658,13 @@
         <v>1.79</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM7" t="n">
         <v>1.94</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO7" t="n">
         <v>1.39</v>
@@ -3682,7 +3682,7 @@
         <v>3.3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
@@ -3694,13 +3694,13 @@
         <v>1.98</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY7" t="n">
         <v>2.27</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA7" t="n">
         <v>1.6</v>
@@ -3718,73 +3718,73 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>88.44</v>
+        <v>89.47</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.63</v>
+        <v>4.41</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.62</v>
+        <v>46.82</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.06</v>
+        <v>14.71</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.5</v>
+        <v>11.41</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.56</v>
+        <v>7.41</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.57</v>
+        <v>47.3</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.75</v>
+        <v>12.47</v>
       </c>
       <c r="DY7" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.81</v>
+        <v>18.64</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC7" t="n">
         <v>1.94</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="H9" t="n">
-        <v>84.29000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M9" t="n">
-        <v>38.29</v>
+        <v>39.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.86</v>
+        <v>16.12</v>
       </c>
       <c r="R9" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.43</v>
+        <v>48.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.43</v>
+        <v>17.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.86</v>
+        <v>11.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.29</v>
+        <v>18.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,70 +4371,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.619999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.62</v>
+        <v>4.82</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CC9" t="n">
         <v>3.13</v>
@@ -4461,40 +4461,40 @@
         <v>1.83</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL9" t="n">
         <v>2.1</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW9" t="n">
         <v>1.81</v>
@@ -4515,85 +4515,85 @@
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.25</v>
+        <v>80.06</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>39.63</v>
+        <v>40</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.63</v>
+        <v>16.59</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.88</v>
+        <v>15.59</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.88</v>
+        <v>46.95</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.19</v>
+        <v>16.53</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.56</v>
+        <v>10.76</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.63</v>
+        <v>5.77</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.56</v>
+        <v>17.76</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.12</v>
@@ -4693,130 +4693,130 @@
         <v>2.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
-        <v>91.38</v>
+        <v>91.22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.62</v>
+        <v>34.67</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.12</v>
+        <v>17.22</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.12</v>
+        <v>6.78</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.25</v>
+        <v>52.78</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.22</v>
       </c>
       <c r="BC10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF10" t="n">
         <v>3</v>
       </c>
-      <c r="BD10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="BG10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.12</v>
       </c>
-      <c r="BF10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="BR10" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY10" t="n">
         <v>2.49</v>
@@ -4834,28 +4834,28 @@
         <v>2.6</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CE10" t="n">
         <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.75</v>
@@ -4864,22 +4864,22 @@
         <v>1.98</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
         <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
         <v>4.36</v>
@@ -4903,16 +4903,16 @@
         <v>2.01</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
@@ -4921,49 +4921,49 @@
         <v>2.41</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.31999999999999</v>
+        <v>93.12</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.31</v>
+        <v>39.53</v>
       </c>
       <c r="DN10" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.81</v>
+        <v>17.35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.75</v>
+        <v>13.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.32</v>
+        <v>54.47</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.69</v>
+        <v>11.53</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.25</v>
+        <v>8.06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.06</v>
+        <v>19.76</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="11">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H12" t="n">
-        <v>102.25</v>
+        <v>99.44</v>
       </c>
       <c r="I12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M12" t="n">
-        <v>61.25</v>
+        <v>59.78</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P12" t="n">
-        <v>14.88</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="R12" t="n">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="S12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="V12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.25</v>
+        <v>51.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.5</v>
+        <v>15.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.88</v>
+        <v>10.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5580,49 +5580,49 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BO12" t="n">
         <v>0.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.69</v>
+        <v>5.65</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CC12" t="n">
         <v>2.55</v>
@@ -5658,37 +5658,37 @@
         <v>3.09</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH12" t="n">
         <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO12" t="n">
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,112 +5697,112 @@
         <v>3.32</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX12" t="n">
         <v>1.73</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
         <v>2.3</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DH12" t="n">
-        <v>102.06</v>
+        <v>100.59</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>59.32</v>
+        <v>58.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.44</v>
+        <v>14.94</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.56</v>
+        <v>14.41</v>
       </c>
       <c r="DR12" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.06</v>
+        <v>52.24</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>17.5</v>
+        <v>17.06</v>
       </c>
       <c r="DY12" t="n">
-        <v>12.38</v>
+        <v>12.12</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.44</v>
+        <v>18.83</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F13" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>112.25</v>
+        <v>111</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K13" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>55.5</v>
+        <v>53.67</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P13" t="n">
-        <v>14.12</v>
+        <v>13.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.38</v>
+        <v>14.11</v>
       </c>
       <c r="R13" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.62</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.75</v>
+        <v>4.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.88</v>
+        <v>16.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5983,70 +5983,70 @@
         <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.19</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1.06</v>
       </c>
-      <c r="BO13" t="n">
-        <v>1</v>
-      </c>
       <c r="BP13" t="n">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>1.74</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CA13" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CC13" t="n">
         <v>2.41</v>
@@ -6058,13 +6058,13 @@
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CG13" t="n">
         <v>2.59</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
         <v>1.76</v>
@@ -6073,37 +6073,37 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV13" t="n">
         <v>1.83</v>
@@ -6112,67 +6112,67 @@
         <v>2.05</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.75</v>
+        <v>100.76</v>
       </c>
       <c r="DI13" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.88</v>
+        <v>46.41</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.5</v>
+        <v>13.41</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.18</v>
+        <v>53.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.62</v>
+        <v>13.71</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.75</v>
+        <v>9.35</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.31</v>
+        <v>16</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI14" t="n">
-        <v>96.29000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.43</v>
+        <v>46.88</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.57</v>
+        <v>18.12</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.57</v>
+        <v>50.12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.43</v>
+        <v>12.62</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.43</v>
+        <v>17.88</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.44</v>
+        <v>9.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BO14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV14" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
         <v>1.82</v>
@@ -6446,31 +6446,31 @@
         <v>1.85</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CH14" t="n">
         <v>1.35</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.88</v>
@@ -6479,7 +6479,7 @@
         <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
@@ -6494,7 +6494,7 @@
         <v>2.1</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CR14" t="n">
         <v>1.44</v>
@@ -6503,28 +6503,28 @@
         <v>3.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.36</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
@@ -6533,82 +6533,82 @@
         <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.88</v>
+        <v>92.23</v>
       </c>
       <c r="DI14" t="n">
         <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.75</v>
+        <v>45.71</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.12</v>
+        <v>15.53</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.13</v>
+        <v>14.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.31</v>
+        <v>7.12</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.25</v>
+        <v>49.11</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.5</v>
+        <v>14.47</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.869999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.63</v>
+        <v>19.3</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>78.33</v>
+        <v>81.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>34.44</v>
+        <v>37.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>14.22</v>
+        <v>14.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.67</v>
+        <v>15.8</v>
       </c>
       <c r="R15" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.67</v>
+        <v>49.4</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.78</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.11</v>
+        <v>10.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.67</v>
+        <v>6.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.56</v>
+        <v>19.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.29</v>
@@ -6789,70 +6789,70 @@
         <v>2.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.81</v>
+        <v>10.94</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.25</v>
+        <v>5.41</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.04</v>
+        <v>3.88</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CC15" t="n">
         <v>4.85</v>
@@ -6867,22 +6867,22 @@
         <v>3</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH15" t="n">
         <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK15" t="n">
         <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
         <v>2.22</v>
@@ -6894,10 +6894,10 @@
         <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
@@ -6912,22 +6912,22 @@
         <v>1.39</v>
       </c>
       <c r="CV15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW15" t="n">
         <v>1.93</v>
       </c>
-      <c r="CW15" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CX15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY15" t="n">
         <v>2.05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.36</v>
@@ -6936,49 +6936,49 @@
         <v>2.14</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>73.31</v>
+        <v>75.47</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.06</v>
+        <v>5.24</v>
       </c>
       <c r="DL15" t="n">
         <v>0.18</v>
       </c>
       <c r="DM15" t="n">
-        <v>31.31</v>
+        <v>33.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DP15" t="n">
         <v>14.12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.25</v>
+        <v>15.35</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.44</v>
+        <v>7.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.44</v>
+        <v>47.94</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.69</v>
+        <v>14</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.31</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.38</v>
+        <v>4.7</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.38</v>
+        <v>18</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>73</v>
+        <v>74.11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>31</v>
+        <v>31.11</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.38</v>
+        <v>15.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.62</v>
+        <v>14.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.880000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.25</v>
+        <v>42.44</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.75</v>
+        <v>16.89</v>
       </c>
       <c r="BE16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="BR16" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY16" t="n">
         <v>3.1</v>
@@ -7252,16 +7252,16 @@
         <v>3.36</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.72</v>
+        <v>4.52</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.17</v>
+        <v>4.97</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
@@ -7270,7 +7270,7 @@
         <v>3.08</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
@@ -7279,13 +7279,13 @@
         <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CM16" t="n">
         <v>2.13</v>
@@ -7318,19 +7318,19 @@
         <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.38</v>
@@ -7345,43 +7345,43 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DG16" t="n">
         <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>76</v>
+        <v>76.41</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="DL16" t="n">
         <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.56</v>
+        <v>35.35</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.82</v>
+        <v>14.94</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.37</v>
+        <v>14.35</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.630000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="DS16" t="n">
         <v>0.06</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.44</v>
+        <v>44.41</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.75</v>
+        <v>10.59</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.12</v>
+        <v>6.94</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.38</v>
+        <v>16.47</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>97.25</v>
+        <v>97.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.62</v>
+        <v>44.89</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.38</v>
+        <v>15.67</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.12</v>
+        <v>50.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD17" t="n">
-        <v>22.62</v>
+        <v>21.78</v>
       </c>
       <c r="BE17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN17" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.31</v>
       </c>
       <c r="BO17" t="n">
         <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY17" t="n">
         <v>2.24</v>
@@ -7655,25 +7655,25 @@
         <v>2.37</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.22</v>
+        <v>4.03</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7682,37 +7682,37 @@
         <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO17" t="n">
         <v>1.42</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS17" t="n">
         <v>3.29</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7721,19 +7721,19 @@
         <v>1.86</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB17" t="n">
         <v>1.43</v>
@@ -7748,76 +7748,76 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.25</v>
+        <v>100.12</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.44</v>
+        <v>45.53</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.13</v>
+        <v>16.24</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.38</v>
+        <v>14.35</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.31</v>
+        <v>50.41</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.44</v>
+        <v>13.35</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.44</v>
+        <v>19.18</v>
       </c>
       <c r="EB17" t="n">
         <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7917,139 +7917,139 @@
         <v>2.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="AI18" t="n">
-        <v>79.70999999999999</v>
+        <v>83.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>36.71</v>
+        <v>37.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.14</v>
+        <v>16.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.71</v>
+        <v>16.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.29</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN18" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT18" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY18" t="n">
         <v>2.13</v>
@@ -8058,73 +8058,73 @@
         <v>2.3</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="CE18" t="n">
         <v>1.48</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CH18" t="n">
         <v>1.3</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO18" t="n">
         <v>1.4</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX18" t="n">
         <v>1.66</v>
@@ -8139,55 +8139,55 @@
         <v>1.75</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.81</v>
+        <v>88.94</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.18</v>
+        <v>4.53</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>40</v>
+        <v>40.18</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.38</v>
+        <v>16.06</v>
       </c>
       <c r="DQ18" t="n">
-        <v>17.25</v>
+        <v>17.18</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.75</v>
+        <v>7.12</v>
       </c>
       <c r="DS18" t="n">
         <v>0.06</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.38</v>
+        <v>45.77</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.630000000000001</v>
+        <v>10</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.94</v>
+        <v>6.18</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.69</v>
+        <v>3.83</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.75</v>
+        <v>15.88</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8323,103 +8323,103 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>87.88</v>
+        <v>94</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.12</v>
+        <v>50.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.88</v>
+        <v>19.56</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>12.56</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>32.62</v>
+        <v>35.22</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.5</v>
+        <v>23.44</v>
       </c>
       <c r="BE19" t="n">
         <v>1.26</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG19" t="n">
         <v>2.12</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.44</v>
+        <v>8.24</v>
       </c>
       <c r="BI19" t="n">
         <v>2.12</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN19" t="n">
         <v>1.06</v>
@@ -8428,22 +8428,22 @@
         <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="BR19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY19" t="n">
         <v>2.42</v>
@@ -8461,31 +8461,31 @@
         <v>2.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="CE19" t="n">
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.94</v>
@@ -8497,7 +8497,7 @@
         <v>2.24</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN19" t="n">
         <v>1.76</v>
@@ -8509,16 +8509,16 @@
         <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
@@ -8530,67 +8530,67 @@
         <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.63</v>
+        <v>96.53</v>
       </c>
       <c r="DI19" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.68</v>
+        <v>57.06</v>
       </c>
       <c r="DN19" t="n">
         <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.75</v>
+        <v>17.71</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.44</v>
+        <v>13.65</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.32</v>
+        <v>8.35</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8602,25 +8602,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>36.06</v>
+        <v>37.23</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.62</v>
+        <v>12.35</v>
       </c>
       <c r="DY19" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.5</v>
+        <v>24.88</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
         <v>2.06</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0.25</v>
@@ -8723,139 +8723,139 @@
         <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AI20" t="n">
-        <v>108.25</v>
+        <v>111.11</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN20" t="n">
-        <v>53</v>
+        <v>52.89</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15.12</v>
+        <v>14.78</v>
       </c>
       <c r="AR20" t="n">
-        <v>15.25</v>
+        <v>14.33</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.5</v>
+        <v>60.56</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.25</v>
+        <v>16.44</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.25</v>
+        <v>11.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.88</v>
+        <v>18.33</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.94</v>
+        <v>9</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL20" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO20" t="n">
         <v>1.12</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BR20" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU20" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY20" t="n">
         <v>1.89</v>
@@ -8864,16 +8864,16 @@
         <v>1.88</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CE20" t="n">
         <v>1.43</v>
@@ -8888,7 +8888,7 @@
         <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.88</v>
@@ -8897,13 +8897,13 @@
         <v>1.57</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM20" t="n">
         <v>2.25</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO20" t="n">
         <v>1.33</v>
@@ -8918,19 +8918,19 @@
         <v>1.43</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX20" t="n">
         <v>1.62</v>
@@ -8948,85 +8948,85 @@
         <v>1.35</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="DE20" t="n">
         <v>0.18</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="DG20" t="n">
         <v>2</v>
       </c>
       <c r="DH20" t="n">
-        <v>107.18</v>
+        <v>108.76</v>
       </c>
       <c r="DI20" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.88</v>
+        <v>50</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.18</v>
+        <v>15</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.82</v>
+        <v>15.29</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.62</v>
+        <v>61.59</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>17</v>
+        <v>17.06</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.62</v>
+        <v>11.53</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="EA20" t="n">
-        <v>17</v>
+        <v>16.82</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>83.5</v>
+        <v>83.89</v>
       </c>
       <c r="I21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="K21" t="n">
-        <v>7.75</v>
+        <v>7.11</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M21" t="n">
-        <v>48.88</v>
+        <v>47.22</v>
       </c>
       <c r="N21" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="P21" t="n">
-        <v>16.25</v>
+        <v>16.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.62</v>
+        <v>12.22</v>
       </c>
       <c r="R21" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45.5</v>
+        <v>45.33</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.88</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.38</v>
+        <v>10.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>22</v>
+        <v>22.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BH21" t="n">
-        <v>12.06</v>
+        <v>11.65</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.75</v>
+        <v>4.59</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.19</v>
+        <v>6.94</v>
       </c>
       <c r="BR21" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS21" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU21" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV21" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="BZ21" t="n">
         <v>2.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CC21" t="n">
         <v>3.25</v>
@@ -9279,16 +9279,16 @@
         <v>3.65</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF21" t="n">
         <v>3.32</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI21" t="n">
         <v>1.76</v>
@@ -9300,13 +9300,13 @@
         <v>1.65</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
@@ -9315,13 +9315,13 @@
         <v>2.37</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="CR21" t="n">
         <v>1.5</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CT21" t="n">
         <v>2.7</v>
@@ -9330,106 +9330,106 @@
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DB21" t="n">
         <v>1.46</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.19</v>
+        <v>83.41</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.68</v>
+        <v>6.41</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM21" t="n">
-        <v>45.63</v>
+        <v>44.94</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="DP21" t="n">
-        <v>15.93</v>
+        <v>16</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.62</v>
+        <v>47.41</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.94</v>
+        <v>13.59</v>
       </c>
       <c r="DY21" t="n">
-        <v>10.57</v>
+        <v>10.18</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.06</v>
+        <v>20.35</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,46 +3890,46 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.14</v>
+        <v>83.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.71</v>
+        <v>40.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.86</v>
+        <v>15.12</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.71</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.71</v>
+        <v>47.88</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.57</v>
+        <v>17.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.56</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4034,49 +4034,49 @@
         <v>3.04</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.54</v>
+        <v>3.47</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH8" t="n">
         <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
         <v>2.14</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO8" t="n">
         <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4091,73 +4091,73 @@
         <v>1.34</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>82.19</v>
+        <v>83.12</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.43</v>
+        <v>39.7</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.31</v>
+        <v>16.24</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.62</v>
+        <v>14.76</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47</v>
+        <v>46.71</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.06</v>
+        <v>10.76</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="H11" t="n">
-        <v>88.38</v>
+        <v>91.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>45.75</v>
+        <v>47.89</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>13.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.25</v>
+        <v>17.89</v>
       </c>
       <c r="R11" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="S11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>65.88</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.88</v>
+        <v>6.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>16</v>
+        <v>16.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.5</v>
+        <v>10.41</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.76</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC11" t="n">
         <v>4.44</v>
@@ -5249,7 +5249,7 @@
         <v>5.01</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF11" t="n">
         <v>2.86</v>
@@ -5261,28 +5261,28 @@
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
         <v>2.04</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ11" t="n">
         <v>3.4</v>
@@ -5300,22 +5300,22 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW11" t="n">
         <v>1.83</v>
       </c>
       <c r="CX11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA11" t="n">
         <v>1.71</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.69</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
@@ -5330,76 +5330,76 @@
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.94</v>
+        <v>88.47</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DO11" t="n">
         <v>2.18</v>
       </c>
-      <c r="DK11" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2.06</v>
-      </c>
       <c r="DP11" t="n">
-        <v>12.69</v>
+        <v>12.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.75</v>
+        <v>18.53</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.88</v>
+        <v>61.65</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.62</v>
+        <v>15.59</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.94</v>
+        <v>10.06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.69</v>
+        <v>5.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.38</v>
+        <v>16.71</v>
       </c>
       <c r="EB11" t="n">
         <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.67</v>
+        <v>51.56</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.24</v>
+        <v>52.18</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
@@ -5884,19 +5884,19 @@
         <v>0.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.67</v>
+        <v>13.78</v>
       </c>
       <c r="AA13" t="n">
         <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="AC13" t="n">
         <v>16.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>1.44</v>
@@ -6190,19 +6190,19 @@
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.71</v>
+        <v>13.77</v>
       </c>
       <c r="DY13" t="n">
         <v>9.35</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="EA13" t="n">
         <v>16</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC13" t="n">
         <v>2.06</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.78</v>
+        <v>6.89</v>
       </c>
       <c r="BC19" t="n">
         <v>3.44</v>
@@ -8608,10 +8608,10 @@
         <v>0.18</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.35</v>
+        <v>12.41</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.82</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ19" t="n">
         <v>3.52</v>
@@ -8780,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.56</v>
+        <v>60.67</v>
       </c>
       <c r="AZ20" t="n">
         <v>0.11</v>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.59</v>
+        <v>61.65</v>
       </c>
       <c r="DW20" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1469,49 +1469,49 @@
         <v>2.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.33</v>
+        <v>88.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>32.78</v>
+        <v>34.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.78</v>
+        <v>13.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.22</v>
+        <v>17.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.33</v>
+        <v>51.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.22</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.67</v>
+        <v>18.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.94</v>
+        <v>5.78</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>3</v>
@@ -1610,82 +1610,82 @@
         <v>3.23</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF2" t="n">
         <v>3.1</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CH2" t="n">
         <v>1.32</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CN2" t="n">
         <v>1.7</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP2" t="n">
         <v>2.22</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
         <v>1.91</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA2" t="n">
         <v>1.73</v>
@@ -1694,85 +1694,85 @@
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="DE2" t="n">
         <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>79.81999999999999</v>
+        <v>82.39</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM2" t="n">
-        <v>33.18</v>
+        <v>34.22</v>
       </c>
       <c r="DN2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.12</v>
+        <v>13.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.82</v>
+        <v>18.11</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.53</v>
+        <v>49.17</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.41</v>
+        <v>18.11</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="H3" t="n">
-        <v>72.75</v>
+        <v>76.11</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K3" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>35.38</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>15.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.38</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.25</v>
+        <v>46.44</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.88</v>
+        <v>11.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.75</v>
+        <v>15.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL3" t="n">
         <v>1.06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.16</v>
       </c>
       <c r="CC3" t="n">
         <v>3.66</v>
@@ -2028,7 +2028,7 @@
         <v>1.46</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG3" t="n">
         <v>2.54</v>
@@ -2046,10 +2046,10 @@
         <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN3" t="n">
         <v>1.73</v>
@@ -2061,16 +2061,16 @@
         <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2082,100 +2082,100 @@
         <v>1.94</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DH3" t="n">
-        <v>76.06</v>
+        <v>77.56</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DM3" t="n">
-        <v>34.95</v>
+        <v>34.78</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.53</v>
+        <v>15</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.18</v>
+        <v>15.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.88</v>
+        <v>7.83</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.88</v>
+        <v>49.33</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.77</v>
+        <v>10.73</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.88</v>
+        <v>16.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>85.44</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.89</v>
+        <v>4.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>30.67</v>
+        <v>32.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,52 +2332,52 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>46.11</v>
+        <v>47.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.33</v>
+        <v>10.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.78</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.65</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
@@ -2386,19 +2386,19 @@
         <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>2.84</v>
@@ -2416,28 +2416,28 @@
         <v>3.1</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.94</v>
+        <v>4.17</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI4" t="n">
         <v>1.76</v>
@@ -2446,34 +2446,34 @@
         <v>1.97</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO4" t="n">
         <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CU4" t="n">
         <v>1.34</v>
@@ -2482,103 +2482,103 @@
         <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.29000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.82</v>
+        <v>4.06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.06</v>
+        <v>33</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.3</v>
+        <v>14.11</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>14.83</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.17</v>
+        <v>49.72</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.41</v>
+        <v>10.44</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.65</v>
+        <v>6.56</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.18</v>
+        <v>18.61</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>87</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P5" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>87.75</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M5" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.5</v>
+        <v>50.67</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.38</v>
+        <v>14.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>10.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.75</v>
+        <v>18.89</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF5" t="n">
         <v>0.22</v>
@@ -2759,70 +2759,70 @@
         <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.65</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.12</v>
+        <v>5.28</v>
       </c>
       <c r="BR5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="CA5" t="n">
         <v>3.16</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CC5" t="n">
         <v>3.95</v>
@@ -2831,157 +2831,157 @@
         <v>4.27</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH5" t="n">
         <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL5" t="n">
         <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO5" t="n">
         <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.18000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.18</v>
+        <v>5.28</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.35</v>
+        <v>45.72</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP5" t="n">
         <v>14.06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.53</v>
+        <v>7.61</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.24</v>
+        <v>50.34</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.47</v>
+        <v>12.78</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.59</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.82</v>
+        <v>18.89</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>77.67</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>35.89</v>
+        <v>35.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>11.89</v>
+        <v>11.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.33</v>
+        <v>18.5</v>
       </c>
       <c r="R6" t="n">
         <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.33</v>
+        <v>52.3</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.22</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.78</v>
+        <v>17.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="BQ6" t="n">
         <v>3.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CC6" t="n">
         <v>3.66</v>
@@ -3240,10 +3240,10 @@
         <v>3.12</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI6" t="n">
         <v>1.83</v>
@@ -3255,10 +3255,10 @@
         <v>1.69</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN6" t="n">
         <v>1.66</v>
@@ -3270,7 +3270,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3291,67 +3291,67 @@
         <v>1.96</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB6" t="n">
         <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.06</v>
+        <v>85.17</v>
       </c>
       <c r="DI6" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.35</v>
+        <v>38.89</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.82</v>
+        <v>11.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.7</v>
+        <v>17.83</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.94</v>
+        <v>7.95</v>
       </c>
       <c r="DS6" t="n">
         <v>0.11</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.94</v>
+        <v>55.22</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.17</v>
+        <v>13.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.119999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.06</v>
+        <v>15.72</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>89.78</v>
+        <v>91</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.22</v>
+        <v>46.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.89</v>
+        <v>15.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.22</v>
+        <v>12.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.78</v>
+        <v>48.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.78</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.67</v>
+        <v>7.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.18</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.18</v>
@@ -3625,13 +3625,13 @@
         <v>2.25</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CD7" t="n">
         <v>3.26</v>
@@ -3652,13 +3652,13 @@
         <v>1.78</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK7" t="n">
         <v>1.79</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM7" t="n">
         <v>1.94</v>
@@ -3670,10 +3670,10 @@
         <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.49</v>
@@ -3682,28 +3682,28 @@
         <v>3.3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX7" t="n">
         <v>1.82</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.99</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB7" t="n">
         <v>1.42</v>
@@ -3712,79 +3712,79 @@
         <v>2.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.47</v>
+        <v>90.16</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.82</v>
+        <v>47.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.71</v>
+        <v>15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.41</v>
+        <v>11.17</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.3</v>
+        <v>47.83</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.710000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.64</v>
+        <v>18.72</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
         <v>1.94</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>83</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>39.22</v>
+        <v>38.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>15.78</v>
+        <v>15.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.44</v>
+        <v>14.5</v>
       </c>
       <c r="R8" t="n">
-        <v>7.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>45.67</v>
+        <v>45.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.44</v>
+        <v>12.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.22</v>
+        <v>19.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CC8" t="n">
         <v>3.24</v>
@@ -4043,121 +4043,121 @@
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG8" t="n">
         <v>2.52</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN8" t="n">
         <v>1.72</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CX8" t="n">
         <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>83.12</v>
+        <v>81.94</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.7</v>
+        <v>39.39</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>16.24</v>
+        <v>16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.76</v>
+        <v>14.78</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.35</v>
+        <v>7.72</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.71</v>
+        <v>46.61</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.76</v>
+        <v>10.89</v>
       </c>
       <c r="DY8" t="n">
         <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.53</v>
+        <v>18.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.38</v>
@@ -4290,139 +4290,139 @@
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.11</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.67</v>
+        <v>42.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.67</v>
+        <v>18.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.11</v>
+        <v>14.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.67</v>
+        <v>46.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.94</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.41</v>
+        <v>4.22</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.36</v>
@@ -4437,34 +4437,34 @@
         <v>3.21</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH9" t="n">
         <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK9" t="n">
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
         <v>2.23</v>
@@ -4476,91 +4476,91 @@
         <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CU9" t="n">
         <v>1.4</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
         <v>2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA9" t="n">
         <v>1.82</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.06</v>
+        <v>80.17</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.18</v>
+        <v>4.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>40</v>
+        <v>41.22</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.59</v>
+        <v>16.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.59</v>
+        <v>15.39</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.65</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.11</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.95</v>
+        <v>47.39</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.53</v>
+        <v>16.44</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.76</v>
+        <v>10.83</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.76</v>
+        <v>18.28</v>
       </c>
       <c r="EB9" t="n">
         <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="H10" t="n">
-        <v>95.25</v>
+        <v>92.44</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="K10" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>43.33</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="R10" t="n">
-        <v>5.38</v>
+        <v>6.11</v>
       </c>
       <c r="S10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="T10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.38</v>
+        <v>55.11</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.12</v>
+        <v>20.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4774,49 +4774,49 @@
         <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BR10" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CA10" t="n">
         <v>3.09</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC10" t="n">
         <v>3.31</v>
@@ -4846,13 +4846,13 @@
         <v>3.56</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH10" t="n">
         <v>1.29</v>
@@ -4864,16 +4864,16 @@
         <v>1.98</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
@@ -4882,16 +4882,16 @@
         <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CS10" t="n">
         <v>3.37</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CU10" t="n">
         <v>1.34</v>
@@ -4900,70 +4900,70 @@
         <v>1.85</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.12</v>
+        <v>91.83</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.53</v>
+        <v>39</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.35</v>
+        <v>17.44</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.47</v>
+        <v>13.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.47</v>
+        <v>53.94</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.53</v>
+        <v>11.44</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.06</v>
+        <v>8</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.76</v>
+        <v>20.11</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI11" t="n">
-        <v>85.5</v>
+        <v>87.89</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>37.88</v>
+        <v>38.67</v>
       </c>
       <c r="AO11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>57.88</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BK11" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY11" t="n">
         <v>2.5</v>
@@ -5237,19 +5237,19 @@
         <v>2.7</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CB11" t="n">
         <v>3.37</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.01</v>
+        <v>4.91</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF11" t="n">
         <v>2.86</v>
@@ -5261,22 +5261,22 @@
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
@@ -5285,121 +5285,121 @@
         <v>1.99</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.47</v>
+        <v>89.5</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK11" t="n">
         <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.18</v>
+        <v>43.28</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.94</v>
+        <v>13.27</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.53</v>
+        <v>18.28</v>
       </c>
       <c r="DR11" t="n">
-        <v>7</v>
+        <v>7.28</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.65</v>
+        <v>60.89</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.59</v>
+        <v>15.12</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.06</v>
+        <v>9.83</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.53</v>
+        <v>5.28</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.71</v>
+        <v>16.89</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>99.44</v>
+        <v>99.8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>59.78</v>
+        <v>59.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.67</v>
+        <v>14.6</v>
       </c>
       <c r="R12" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="S12" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.56</v>
+        <v>51.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.78</v>
+        <v>15.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.56</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.67</v>
+        <v>19.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5580,49 +5580,49 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CC12" t="n">
         <v>2.55</v>
@@ -5655,10 +5655,10 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH12" t="n">
         <v>1.33</v>
@@ -5673,7 +5673,7 @@
         <v>1.71</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CM12" t="n">
         <v>2.06</v>
@@ -5685,10 +5685,10 @@
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,7 +5697,7 @@
         <v>3.32</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5715,7 +5715,7 @@
         <v>2.16</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA12" t="n">
         <v>1.67</v>
@@ -5724,85 +5724,85 @@
         <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="DH12" t="n">
-        <v>100.59</v>
+        <v>100.72</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.88</v>
+        <v>5.84</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.65</v>
+        <v>58.45</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DP12" t="n">
         <v>14.94</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.41</v>
+        <v>14.39</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.18</v>
+        <v>52.17</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>17.06</v>
+        <v>16.78</v>
       </c>
       <c r="DY12" t="n">
-        <v>12.12</v>
+        <v>11.72</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.83</v>
+        <v>18.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.22</v>
@@ -5902,52 +5902,52 @@
         <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AI13" t="n">
-        <v>89.25</v>
+        <v>88.44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.25</v>
+        <v>37.89</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16.88</v>
+        <v>16.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.62</v>
+        <v>12.89</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.75</v>
+        <v>49.56</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.75</v>
+        <v>14.89</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO13" t="n">
         <v>1.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>1.72</v>
@@ -6043,28 +6043,28 @@
         <v>1.74</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI13" t="n">
         <v>1.76</v>
@@ -6076,7 +6076,7 @@
         <v>1.71</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>2.03</v>
@@ -6085,13 +6085,13 @@
         <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
@@ -6100,7 +6100,7 @@
         <v>3.26</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
@@ -6127,52 +6127,52 @@
         <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
         <v>1.06</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.76</v>
+        <v>99.72</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.36</v>
+        <v>5.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.41</v>
+        <v>45.78</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.3</v>
+        <v>15.28</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.41</v>
+        <v>13.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.06</v>
+        <v>52.78</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>16</v>
+        <v>15.56</v>
       </c>
       <c r="EB13" t="n">
         <v>1.52</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6227,82 +6227,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>90.22</v>
+        <v>91.7</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>44.67</v>
+        <v>44.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>13.22</v>
+        <v>13.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.22</v>
+        <v>47.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.11</v>
+        <v>15.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.56</v>
+        <v>20.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6386,70 +6386,70 @@
         <v>2.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.35</v>
+        <v>9.44</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CC14" t="n">
         <v>2.37</v>
@@ -6470,37 +6470,37 @@
         <v>1.35</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK14" t="n">
         <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM14" t="n">
         <v>2.38</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT14" t="n">
         <v>2.93</v>
@@ -6512,16 +6512,16 @@
         <v>1.95</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA14" t="n">
         <v>1.85</v>
@@ -6530,52 +6530,52 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="DG14" t="n">
         <v>2.11</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.23</v>
+        <v>92.94</v>
       </c>
       <c r="DI14" t="n">
         <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.71</v>
+        <v>45.72</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.53</v>
+        <v>15.33</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.12</v>
+        <v>13.94</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.12</v>
+        <v>6.95</v>
       </c>
       <c r="DS14" t="n">
         <v>0.11</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.11</v>
+        <v>48.66</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.47</v>
+        <v>14.28</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC14" t="n">
         <v>2.06</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6708,139 +6708,139 @@
         <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>66.86</v>
+        <v>68</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AL15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="BC15" t="n">
         <v>3</v>
       </c>
-      <c r="AM15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.71</v>
-      </c>
       <c r="BD15" t="n">
-        <v>15.57</v>
+        <v>17.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.94</v>
+        <v>11.17</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.53</v>
+        <v>5.83</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT15" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY15" t="n">
         <v>3.46</v>
@@ -6852,19 +6852,19 @@
         <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.69</v>
+        <v>5.52</v>
       </c>
       <c r="CE15" t="n">
         <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG15" t="n">
         <v>2.7</v>
@@ -6873,31 +6873,31 @@
         <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CO15" t="n">
         <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
@@ -6912,73 +6912,73 @@
         <v>1.39</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>75.47</v>
+        <v>75.5</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM15" t="n">
-        <v>33.47</v>
+        <v>33.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.12</v>
+        <v>14.06</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.35</v>
+        <v>15.33</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.35</v>
+        <v>7.39</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.94</v>
+        <v>48.16</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="EA15" t="n">
-        <v>18</v>
+        <v>18.61</v>
       </c>
       <c r="EB15" t="n">
         <v>1.41</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>74.11</v>
+        <v>75.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.11</v>
+        <v>30.2</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.56</v>
+        <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.56</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.44</v>
+        <v>42.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.22</v>
+        <v>5.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.89</v>
+        <v>17.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.53</v>
+        <v>5.17</v>
       </c>
       <c r="BR16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>3.1</v>
@@ -7252,25 +7252,25 @@
         <v>3.36</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.97</v>
+        <v>5</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
@@ -7279,13 +7279,13 @@
         <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CM16" t="n">
         <v>2.13</v>
@@ -7300,7 +7300,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
@@ -7321,7 +7321,7 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
         <v>2.08</v>
@@ -7330,7 +7330,7 @@
         <v>2.19</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB16" t="n">
         <v>1.38</v>
@@ -7345,76 +7345,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DH16" t="n">
-        <v>76.41</v>
+        <v>77.17</v>
       </c>
       <c r="DI16" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.35</v>
+        <v>34.61</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.94</v>
+        <v>15.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.35</v>
+        <v>14.61</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.41</v>
+        <v>44.44</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.59</v>
+        <v>10.33</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.94</v>
+        <v>6.72</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.47</v>
+        <v>16.72</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7436,61 +7436,61 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>103.25</v>
+        <v>102.22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="K17" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>46.25</v>
+        <v>47.44</v>
       </c>
       <c r="N17" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="P17" t="n">
-        <v>16.88</v>
+        <v>17.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.25</v>
+        <v>15.33</v>
       </c>
       <c r="R17" t="n">
-        <v>7.25</v>
+        <v>6.89</v>
       </c>
       <c r="S17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7499,19 +7499,19 @@
         <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.88</v>
+        <v>10.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.25</v>
+        <v>16.89</v>
       </c>
       <c r="AD17" t="n">
         <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,67 +7595,67 @@
         <v>2.22</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB17" t="n">
         <v>3.13</v>
@@ -7667,13 +7667,13 @@
         <v>4.03</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7682,16 +7682,16 @@
         <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK17" t="n">
         <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN17" t="n">
         <v>1.65</v>
@@ -7700,10 +7700,10 @@
         <v>1.42</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7724,13 +7724,13 @@
         <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA17" t="n">
         <v>1.62</v>
@@ -7742,82 +7742,82 @@
         <v>2.39</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.12</v>
+        <v>99.78</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.53</v>
+        <v>46.16</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.35</v>
+        <v>14.88</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.41</v>
+        <v>50.66</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.35</v>
+        <v>13.44</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.710000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.18</v>
+        <v>19.33</v>
       </c>
       <c r="EB17" t="n">
         <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>94.11</v>
+        <v>93.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>42.56</v>
+        <v>44.6</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>15.78</v>
+        <v>15.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.67</v>
+        <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.89</v>
+        <v>48.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.89</v>
+        <v>16.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0.12</v>
@@ -7998,70 +7998,70 @@
         <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.24</v>
+        <v>10.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CC18" t="n">
         <v>2.97</v>
@@ -8070,43 +8070,43 @@
         <v>3.38</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="CR18" t="n">
         <v>1.5</v>
@@ -8121,106 +8121,106 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.94</v>
+        <v>88.72</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.53</v>
+        <v>4.78</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.18</v>
+        <v>41.44</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.06</v>
+        <v>16</v>
       </c>
       <c r="DQ18" t="n">
-        <v>17.18</v>
+        <v>16.94</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.77</v>
+        <v>45.89</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DX18" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.88</v>
+        <v>16.83</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8323,127 +8323,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>94</v>
+        <v>95.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>50.67</v>
+        <v>52.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.56</v>
+        <v>19.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.56</v>
+        <v>13.2</v>
       </c>
       <c r="AS19" t="n">
         <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>35.22</v>
+        <v>37.2</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.33</v>
+        <v>10.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.89</v>
+        <v>7.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.44</v>
+        <v>23.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.24</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BO19" t="n">
         <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT19" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY19" t="n">
         <v>2.42</v>
@@ -8461,25 +8461,25 @@
         <v>2.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8488,109 +8488,109 @@
         <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
         <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS19" t="n">
         <v>3.31</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.53</v>
+        <v>97.11</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM19" t="n">
-        <v>57.06</v>
+        <v>57.67</v>
       </c>
       <c r="DN19" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.71</v>
+        <v>17.66</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.65</v>
+        <v>13.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.35</v>
+        <v>8.33</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>37.23</v>
+        <v>38.22</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.41</v>
+        <v>12.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.88</v>
+        <v>24.78</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F20" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="H20" t="n">
-        <v>106.12</v>
+        <v>105.89</v>
       </c>
       <c r="I20" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J20" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K20" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>46.75</v>
+        <v>46.44</v>
       </c>
       <c r="N20" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O20" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="P20" t="n">
-        <v>15.25</v>
+        <v>15.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.38</v>
+        <v>16.67</v>
       </c>
       <c r="R20" t="n">
-        <v>7.25</v>
+        <v>6.78</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>62.75</v>
+        <v>63.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.75</v>
+        <v>17.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.12</v>
+        <v>14.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8804,70 +8804,70 @@
         <v>2.44</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BH20" t="n">
         <v>9</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BR20" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS20" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU20" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="CC20" t="n">
         <v>2.33</v>
@@ -8882,25 +8882,25 @@
         <v>2.97</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH20" t="n">
         <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK20" t="n">
         <v>1.57</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN20" t="n">
         <v>1.77</v>
@@ -8909,124 +8909,124 @@
         <v>1.33</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CR20" t="n">
         <v>1.43</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX20" t="n">
         <v>1.62</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB20" t="n">
         <v>1.35</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="DG20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH20" t="n">
-        <v>108.76</v>
+        <v>108.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM20" t="n">
-        <v>50</v>
+        <v>49.66</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DP20" t="n">
-        <v>15</v>
+        <v>15.06</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.23</v>
+        <v>6.06</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.65</v>
+        <v>61.89</v>
       </c>
       <c r="DW20" t="n">
         <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.06</v>
+        <v>16.88</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.53</v>
+        <v>11.44</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.82</v>
+        <v>16.5</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0.11</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.88</v>
+        <v>83.22</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.38</v>
+        <v>42.33</v>
       </c>
       <c r="AO21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM21" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BN21" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.94</v>
+        <v>6.89</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS21" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT21" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY21" t="n">
         <v>2.31</v>
@@ -9267,136 +9267,136 @@
         <v>2.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.65</v>
+        <v>4.01</v>
       </c>
       <c r="CE21" t="n">
         <v>1.49</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ21" t="n">
         <v>2.01</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW21" t="n">
         <v>2.04</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA21" t="n">
         <v>1.8</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.41</v>
+        <v>83.56</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.41</v>
+        <v>6.34</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.94</v>
+        <v>44.78</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="DP21" t="n">
-        <v>16</v>
+        <v>16.16</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.18</v>
+        <v>7.28</v>
       </c>
       <c r="DS21" t="n">
         <v>0.11</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.41</v>
+        <v>46.66</v>
       </c>
       <c r="DW21" t="n">
         <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.59</v>
+        <v>13.28</v>
       </c>
       <c r="DY21" t="n">
-        <v>10.18</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.35</v>
+        <v>20.38</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -7117,7 +7117,7 @@
         <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
         <v>75.7</v>
@@ -7132,7 +7132,7 @@
         <v>3.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN16" t="n">
         <v>30.2</v>
@@ -7141,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -7174,19 +7174,19 @@
         <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BB16" t="n">
         <v>5.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
         <v>17.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="BF16" t="n">
         <v>2.5</v>
@@ -7219,10 +7219,10 @@
         <v>1.39</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.17</v>
+        <v>5.44</v>
       </c>
       <c r="BR16" t="n">
         <v>83.33</v>
@@ -7348,7 +7348,7 @@
         <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
         <v>77.17</v>
@@ -7363,7 +7363,7 @@
         <v>3.67</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="DM16" t="n">
         <v>34.61</v>
@@ -7372,7 +7372,7 @@
         <v>0.83</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DP16" t="n">
         <v>15.5</v>
@@ -7399,13 +7399,13 @@
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.33</v>
+        <v>10.39</v>
       </c>
       <c r="DY16" t="n">
         <v>6.72</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="EA16" t="n">
         <v>16.72</v>
@@ -7439,7 +7439,7 @@
         <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
         <v>102.22</v>
@@ -7454,7 +7454,7 @@
         <v>5.33</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
         <v>47.44</v>
@@ -7463,13 +7463,13 @@
         <v>0.89</v>
       </c>
       <c r="O17" t="n">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="P17" t="n">
         <v>17.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.33</v>
+        <v>15.44</v>
       </c>
       <c r="R17" t="n">
         <v>6.89</v>
@@ -7622,10 +7622,10 @@
         <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.61</v>
+        <v>3.94</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.33</v>
+        <v>4.61</v>
       </c>
       <c r="BR17" t="n">
         <v>94.44</v>
@@ -7751,7 +7751,7 @@
         <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="DH17" t="n">
         <v>99.78</v>
@@ -7766,7 +7766,7 @@
         <v>4.83</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
         <v>46.16</v>
@@ -7775,13 +7775,13 @@
         <v>1.11</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="DP17" t="n">
         <v>16.39</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.88</v>
+        <v>14.94</v>
       </c>
       <c r="DR17" t="n">
         <v>7.06</v>
@@ -8392,7 +8392,7 @@
         <v>3.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="BE19" t="n">
         <v>1.3</v>
@@ -8617,7 +8617,7 @@
         <v>3.55</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.78</v>
+        <v>24.83</v>
       </c>
       <c r="EB19" t="n">
         <v>1.46</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1391,7 +1391,7 @@
         <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
         <v>3.25</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
@@ -1466,13 +1466,13 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
         <v>1.6</v>
@@ -1547,7 +1547,7 @@
         <v>1.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG2" t="n">
         <v>2.83</v>
@@ -1703,7 +1703,7 @@
         <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="DG2" t="n">
         <v>2.33</v>
@@ -1715,7 +1715,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="DK2" t="n">
         <v>3.56</v>
@@ -1772,7 +1772,7 @@
         <v>1.13</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -2197,7 +2197,7 @@
         <v>0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>3.75</v>
@@ -2272,13 +2272,13 @@
         <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -2290,7 +2290,7 @@
         <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AL4" t="n">
         <v>4.3</v>
@@ -2353,7 +2353,7 @@
         <v>1.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
         <v>2.06</v>
@@ -2509,7 +2509,7 @@
         <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="DG4" t="n">
         <v>2</v>
@@ -2521,7 +2521,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="DK4" t="n">
         <v>4.06</v>
@@ -2578,7 +2578,7 @@
         <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="5">
@@ -6257,7 +6257,7 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="Q14" t="n">
         <v>13.7</v>
@@ -6569,7 +6569,7 @@
         <v>2.78</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.33</v>
+        <v>15.22</v>
       </c>
       <c r="DQ14" t="n">
         <v>13.94</v>
@@ -6741,7 +6741,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.88</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
         <v>14.75</v>
@@ -6972,7 +6972,7 @@
         <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.06</v>
+        <v>14.33</v>
       </c>
       <c r="DQ15" t="n">
         <v>15.33</v>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -7108,7 +7108,7 @@
         <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>30.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP16" t="n">
         <v>1.4</v>
@@ -7171,7 +7171,7 @@
         <v>42.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="BA16" t="n">
         <v>8.9</v>
@@ -7189,7 +7189,7 @@
         <v>0.99</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BG16" t="n">
         <v>2.61</v>
@@ -7345,7 +7345,7 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
         <v>2</v>
@@ -7357,7 +7357,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK16" t="n">
         <v>3.67</v>
@@ -7369,7 +7369,7 @@
         <v>34.61</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DO16" t="n">
         <v>1.67</v>
@@ -7396,7 +7396,7 @@
         <v>44.44</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
         <v>10.39</v>
@@ -7414,7 +7414,7 @@
         <v>1.16</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="17">
@@ -7436,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="G17" t="n">
         <v>2.78</v>
@@ -7448,7 +7448,7 @@
         <v>0.33</v>
       </c>
       <c r="J17" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>5.33</v>
@@ -7460,7 +7460,7 @@
         <v>47.44</v>
       </c>
       <c r="N17" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="O17" t="n">
         <v>2.56</v>
@@ -7511,7 +7511,7 @@
         <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.67</v>
+        <v>15.44</v>
       </c>
       <c r="AR17" t="n">
         <v>14.44</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
         <v>2.55</v>
@@ -7760,7 +7760,7 @@
         <v>0.33</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="DK17" t="n">
         <v>4.83</v>
@@ -7772,13 +7772,13 @@
         <v>46.16</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="DO17" t="n">
         <v>2.28</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.39</v>
+        <v>16.28</v>
       </c>
       <c r="DQ17" t="n">
         <v>14.94</v>
@@ -7817,7 +7817,7 @@
         <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="18">
@@ -7869,7 +7869,7 @@
         <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="Q18" t="n">
         <v>17.2</v>
@@ -8181,7 +8181,7 @@
         <v>2.17</v>
       </c>
       <c r="DP18" t="n">
-        <v>16</v>
+        <v>15.89</v>
       </c>
       <c r="DQ18" t="n">
         <v>16.94</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
         <v>1.7</v>
@@ -8335,7 +8335,7 @@
         <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
         <v>3.7</v>
@@ -8398,7 +8398,7 @@
         <v>1.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BG19" t="n">
         <v>2.06</v>
@@ -8554,7 +8554,7 @@
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DG19" t="n">
         <v>2.5</v>
@@ -8566,7 +8566,7 @@
         <v>0.17</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="DK19" t="n">
         <v>4.45</v>
@@ -8623,7 +8623,7 @@
         <v>1.46</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>74.75</v>
+        <v>76.33</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>33.62</v>
+        <v>34.33</v>
       </c>
       <c r="N2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.5</v>
+        <v>18.33</v>
       </c>
       <c r="R2" t="n">
-        <v>8.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="T2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.5</v>
+        <v>46.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.12</v>
+        <v>17.89</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>2.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.89</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.78</v>
+        <v>5.63</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY2" t="n">
         <v>3</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC2" t="n">
         <v>3.42</v>
@@ -1625,10 +1625,10 @@
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH2" t="n">
         <v>1.32</v>
@@ -1643,31 +1643,31 @@
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN2" t="n">
         <v>1.7</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
@@ -1685,7 +1685,7 @@
         <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA2" t="n">
         <v>1.73</v>
@@ -1694,52 +1694,52 @@
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.39</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.22</v>
+        <v>34.52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.56</v>
+        <v>13.63</v>
       </c>
       <c r="DQ2" t="n">
-        <v>18.11</v>
+        <v>18.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.17</v>
+        <v>49.16</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX2" t="n">
-        <v>10</v>
+        <v>9.84</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.5</v>
+        <v>6.37</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.11</v>
+        <v>18.42</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1.11</v>
       </c>
-      <c r="AH3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>79</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18.78</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP3" t="n">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY3" t="n">
         <v>2.51</v>
@@ -2019,16 +2019,16 @@
         <v>3.15</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
         <v>2.54</v>
@@ -2043,16 +2043,16 @@
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL3" t="n">
         <v>2.14</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
@@ -2061,7 +2061,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
@@ -2079,7 +2079,7 @@
         <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
         <v>1.66</v>
@@ -2094,88 +2094,88 @@
         <v>1.73</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
         <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DG3" t="n">
         <v>2.11</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.56</v>
+        <v>79.63</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>34.78</v>
+        <v>35.26</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DP3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.33</v>
+        <v>49.58</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.73</v>
+        <v>10.69</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.94</v>
+        <v>7.84</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.94</v>
+        <v>17.47</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>87</v>
+        <v>87.3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>47.67</v>
+        <v>48.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>14.56</v>
+        <v>13.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="R5" t="n">
-        <v>8.56</v>
+        <v>8.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.67</v>
+        <v>50.2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.78</v>
+        <v>14.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.89</v>
+        <v>18.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.22</v>
@@ -2759,67 +2759,67 @@
         <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
         <v>1.11</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV5" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB5" t="n">
         <v>3.2</v>
@@ -2834,7 +2834,7 @@
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CG5" t="n">
         <v>2.62</v>
@@ -2843,7 +2843,7 @@
         <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.9</v>
@@ -2855,7 +2855,7 @@
         <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN5" t="n">
         <v>1.78</v>
@@ -2867,7 +2867,7 @@
         <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
@@ -2885,7 +2885,7 @@
         <v>1.96</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
         <v>1.61</v>
@@ -2912,76 +2912,76 @@
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.78</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.72</v>
+        <v>46.37</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.06</v>
+        <v>13.74</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>15.37</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.61</v>
+        <v>7.84</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.34</v>
+        <v>50.11</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.78</v>
+        <v>12.95</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.89</v>
+        <v>18.58</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,76 +3081,76 @@
         <v>2.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" t="n">
-        <v>95.5</v>
+        <v>90.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.25</v>
+        <v>42.22</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>17.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.88</v>
+        <v>57.44</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.75</v>
+        <v>11.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BD6" t="n">
         <v>13</v>
@@ -3159,61 +3159,61 @@
         <v>1.33</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.94</v>
+        <v>4.74</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY6" t="n">
         <v>2.46</v>
@@ -3222,43 +3222,43 @@
         <v>2.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CD6" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CE6" t="n">
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN6" t="n">
         <v>1.66</v>
@@ -3267,10 +3267,10 @@
         <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3285,106 +3285,106 @@
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="DG6" t="n">
         <v>2.05</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.17</v>
+        <v>83.42</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.89</v>
+        <v>38.63</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.56</v>
+        <v>11.68</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.83</v>
+        <v>17.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.95</v>
+        <v>7.9</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.22</v>
+        <v>54.73</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.22</v>
+        <v>13.21</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.72</v>
+        <v>15.58</v>
       </c>
       <c r="EB6" t="n">
         <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="7">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>83.38</v>
+        <v>84.44</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="K9" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L9" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>39.25</v>
+        <v>42.33</v>
       </c>
       <c r="N9" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="P9" t="n">
-        <v>14.25</v>
+        <v>14.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.12</v>
+        <v>15.78</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.38</v>
+        <v>49</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.12</v>
+        <v>17.11</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.25</v>
+        <v>11.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.62</v>
+        <v>18.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,70 +4371,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CC9" t="n">
         <v>3.07</v>
@@ -4446,16 +4446,16 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH9" t="n">
         <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.82</v>
@@ -4464,7 +4464,7 @@
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
         <v>2.23</v>
@@ -4473,13 +4473,13 @@
         <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4494,106 +4494,106 @@
         <v>1.4</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
         <v>1.61</v>
       </c>
       <c r="CY9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.28</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.17</v>
+        <v>80.84</v>
       </c>
       <c r="DI9" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="DK9" t="n">
         <v>4.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.22</v>
+        <v>42.58</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.5</v>
+        <v>16.63</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.39</v>
+        <v>15.26</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.39</v>
+        <v>47.74</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.44</v>
+        <v>16.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.83</v>
+        <v>10.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.28</v>
+        <v>18.16</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>92.44</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>43.33</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>17.67</v>
+        <v>17.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.67</v>
+        <v>15.4</v>
       </c>
       <c r="R10" t="n">
-        <v>6.11</v>
+        <v>6.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.11</v>
+        <v>55.1</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.56</v>
+        <v>13.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.779999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.78</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4774,49 +4774,49 @@
         <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.17</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BO10" t="n">
         <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BR10" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT10" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>2.47</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>2.56</v>
-      </c>
       <c r="CA10" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CC10" t="n">
         <v>3.31</v>
@@ -4846,16 +4846,16 @@
         <v>3.56</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI10" t="n">
         <v>1.75</v>
@@ -4867,40 +4867,40 @@
         <v>1.67</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV10" t="n">
         <v>1.85</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX10" t="n">
         <v>1.71</v>
@@ -4915,88 +4915,88 @@
         <v>1.69</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG10" t="n">
         <v>2.05</v>
       </c>
-      <c r="DG10" t="n">
-        <v>1.94</v>
-      </c>
       <c r="DH10" t="n">
-        <v>91.83</v>
+        <v>91.58</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM10" t="n">
-        <v>39</v>
+        <v>39.05</v>
       </c>
       <c r="DN10" t="n">
         <v>0.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.44</v>
+        <v>17.16</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.67</v>
+        <v>13.63</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.44</v>
+        <v>6.63</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.94</v>
+        <v>54</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.44</v>
+        <v>11.79</v>
       </c>
       <c r="DY10" t="n">
-        <v>8</v>
+        <v>8.26</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.11</v>
+        <v>20.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="11">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.22</v>
@@ -5902,52 +5902,52 @@
         <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.44</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.89</v>
+        <v>39.7</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16.67</v>
+        <v>16.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.56</v>
+        <v>50.7</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.78</v>
+        <v>14</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.56</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.89</v>
+        <v>15.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT13" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY13" t="n">
         <v>1.72</v>
@@ -6043,22 +6043,22 @@
         <v>1.74</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG13" t="n">
         <v>2.58</v>
@@ -6073,16 +6073,16 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
@@ -6091,19 +6091,19 @@
         <v>2.23</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV13" t="n">
         <v>1.83</v>
@@ -6112,67 +6112,67 @@
         <v>2.05</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC13" t="n">
         <v>2.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="DE13" t="n">
         <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.72</v>
+        <v>100.95</v>
       </c>
       <c r="DI13" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.28</v>
+        <v>5.42</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.78</v>
+        <v>46.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.28</v>
+        <v>15.16</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.5</v>
+        <v>13.53</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.67</v>
+        <v>5.79</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.78</v>
+        <v>53.21</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.78</v>
+        <v>13.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.279999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.56</v>
+        <v>15.89</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6708,52 +6708,52 @@
         <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
-        <v>68</v>
+        <v>68.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.75</v>
+        <v>14.44</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.62</v>
+        <v>46.44</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.12</v>
+        <v>10.67</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.12</v>
+        <v>7.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.25</v>
+        <v>17.44</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.17</v>
+        <v>11.37</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.83</v>
+        <v>5.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY15" t="n">
         <v>3.46</v>
@@ -6849,31 +6849,31 @@
         <v>3.88</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.74</v>
+        <v>4.86</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.91</v>
@@ -6882,31 +6882,31 @@
         <v>1.59</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN15" t="n">
         <v>1.78</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU15" t="n">
         <v>1.39</v>
@@ -6936,49 +6936,49 @@
         <v>2.12</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH15" t="n">
-        <v>75.5</v>
+        <v>75.42</v>
       </c>
       <c r="DI15" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM15" t="n">
-        <v>33.5</v>
+        <v>33.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.33</v>
+        <v>14.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.33</v>
+        <v>15.16</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.16</v>
+        <v>48</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.61</v>
+        <v>18.63</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
-        <v>79</v>
+        <v>79.44</v>
       </c>
       <c r="I16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M16" t="n">
-        <v>40.12</v>
+        <v>40</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P16" t="n">
-        <v>14.25</v>
+        <v>13.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.12</v>
+        <v>13.78</v>
       </c>
       <c r="R16" t="n">
-        <v>9.380000000000001</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>46.62</v>
+        <v>45.56</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>16</v>
+        <v>15.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CC16" t="n">
         <v>4.46</v>
@@ -7267,7 +7267,7 @@
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG16" t="n">
         <v>2.62</v>
@@ -7282,25 +7282,25 @@
         <v>1.93</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO16" t="n">
         <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
@@ -7318,70 +7318,70 @@
         <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH16" t="n">
-        <v>77.17</v>
+        <v>77.47</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.61</v>
+        <v>34.84</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.5</v>
+        <v>15.21</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.61</v>
+        <v>14.42</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.84</v>
+        <v>10.11</v>
       </c>
       <c r="DS16" t="n">
         <v>0.05</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.44</v>
+        <v>44.05</v>
       </c>
       <c r="DW16" t="n">
         <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.39</v>
+        <v>10.52</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.72</v>
+        <v>16.31</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>97.33</v>
+        <v>98</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.89</v>
+        <v>46.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.44</v>
+        <v>15.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.22</v>
+        <v>6.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.33</v>
+        <v>50.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.89</v>
+        <v>12.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.67</v>
+        <v>9.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.78</v>
+        <v>21.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.56</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO17" t="n">
         <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY17" t="n">
         <v>2.21</v>
@@ -7655,40 +7655,40 @@
         <v>2.31</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB17" t="n">
         <v>3.13</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.03</v>
+        <v>3.89</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
         <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK17" t="n">
         <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
         <v>2.05</v>
@@ -7697,7 +7697,7 @@
         <v>1.65</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP17" t="n">
         <v>2.29</v>
@@ -7709,7 +7709,7 @@
         <v>1.51</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CT17" t="n">
         <v>2.67</v>
@@ -7724,16 +7724,16 @@
         <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB17" t="n">
         <v>1.43</v>
@@ -7742,82 +7742,82 @@
         <v>2.39</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DH17" t="n">
-        <v>99.78</v>
+        <v>100</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.83</v>
+        <v>4.68</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.16</v>
+        <v>47.05</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.28</v>
+        <v>16.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.94</v>
+        <v>14.89</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.06</v>
+        <v>6.9</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.66</v>
+        <v>50.68</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.44</v>
+        <v>13.89</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.779999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.33</v>
+        <v>19.21</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.2</v>
@@ -7917,139 +7917,139 @@
         <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.12</v>
+        <v>88.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>37.5</v>
+        <v>38.89</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.38</v>
+        <v>15.78</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.62</v>
+        <v>16.22</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>42.25</v>
+        <v>44.44</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.25</v>
+        <v>7.44</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BD18" t="n">
-        <v>17</v>
+        <v>19.22</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.5</v>
+        <v>10.32</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP18" t="n">
         <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.44</v>
+        <v>5.26</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY18" t="n">
         <v>2.11</v>
@@ -8058,16 +8058,16 @@
         <v>2.26</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="CE18" t="n">
         <v>1.47</v>
@@ -8076,7 +8076,7 @@
         <v>3.18</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH18" t="n">
         <v>1.31</v>
@@ -8091,13 +8091,13 @@
         <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO18" t="n">
         <v>1.39</v>
@@ -8106,7 +8106,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CR18" t="n">
         <v>1.5</v>
@@ -8121,70 +8121,70 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW18" t="n">
         <v>2</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB18" t="n">
         <v>1.42</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="DE18" t="n">
         <v>0.16</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.72</v>
+        <v>91.05</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.44</v>
+        <v>41.9</v>
       </c>
       <c r="DN18" t="n">
         <v>0.95</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.94</v>
+        <v>16.74</v>
       </c>
       <c r="DR18" t="n">
         <v>7</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.89</v>
+        <v>46.73</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.11</v>
+        <v>10.21</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.17</v>
+        <v>6.31</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.83</v>
+        <v>17.89</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="H19" t="n">
-        <v>99.38</v>
+        <v>98.89</v>
       </c>
       <c r="I19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J19" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M19" t="n">
-        <v>64.25</v>
+        <v>63.33</v>
       </c>
       <c r="N19" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P19" t="n">
-        <v>15.62</v>
+        <v>15.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.88</v>
+        <v>14.44</v>
       </c>
       <c r="R19" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="S19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>39.5</v>
+        <v>39.33</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.75</v>
+        <v>14.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>26.5</v>
+        <v>25.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN19" t="n">
         <v>1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,19 +8452,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC19" t="n">
         <v>3.76</v>
@@ -8479,7 +8479,7 @@
         <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8494,13 +8494,13 @@
         <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
@@ -8509,7 +8509,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
@@ -8530,100 +8530,100 @@
         <v>1.97</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="DH19" t="n">
-        <v>97.11</v>
+        <v>97</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.45</v>
+        <v>4.37</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>57.67</v>
+        <v>57.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO19" t="n">
         <v>1.95</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.66</v>
+        <v>17.42</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.95</v>
+        <v>13.79</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.33</v>
+        <v>8.32</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>38.22</v>
+        <v>38.21</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.5</v>
+        <v>12.37</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.94</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.83</v>
+        <v>24.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>0.22</v>
@@ -8723,139 +8723,139 @@
         <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>111.11</v>
+        <v>112.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.89</v>
+        <v>54.1</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>14.33</v>
+        <v>13.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.67</v>
+        <v>60.9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.44</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.33</v>
+        <v>18.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BH20" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="BR20" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS20" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU20" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY20" t="n">
         <v>1.85</v>
@@ -8864,22 +8864,22 @@
         <v>1.84</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="CE20" t="n">
         <v>1.43</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG20" t="n">
         <v>2.74</v>
@@ -8903,7 +8903,7 @@
         <v>2.26</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO20" t="n">
         <v>1.33</v>
@@ -8912,7 +8912,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CR20" t="n">
         <v>1.43</v>
@@ -8927,19 +8927,19 @@
         <v>1.4</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA20" t="n">
         <v>1.79</v>
@@ -8951,82 +8951,82 @@
         <v>2.12</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="DE20" t="n">
         <v>0.16</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DH20" t="n">
-        <v>108.5</v>
+        <v>109.37</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.66</v>
+        <v>50.47</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.06</v>
+        <v>14.84</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.89</v>
+        <v>61.95</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX20" t="n">
-        <v>16.88</v>
+        <v>16.63</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.44</v>
+        <v>11.21</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.5</v>
+        <v>16.53</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H21" t="n">
-        <v>83.89</v>
+        <v>82.8</v>
       </c>
       <c r="I21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="K21" t="n">
-        <v>7.11</v>
+        <v>6.8</v>
       </c>
       <c r="L21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M21" t="n">
-        <v>47.22</v>
+        <v>46.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>16.33</v>
+        <v>16.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
       <c r="R21" t="n">
-        <v>6.56</v>
+        <v>6.9</v>
       </c>
       <c r="S21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45.33</v>
+        <v>44.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.56</v>
+        <v>10.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>22.33</v>
+        <v>21.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.22</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.5</v>
+        <v>11.53</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.89</v>
+        <v>6.74</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS21" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU21" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="CA21" t="n">
         <v>3.11</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CC21" t="n">
         <v>3.52</v>
@@ -9285,7 +9285,7 @@
         <v>3.3</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
@@ -9303,7 +9303,7 @@
         <v>2.19</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN21" t="n">
         <v>1.71</v>
@@ -9312,19 +9312,19 @@
         <v>1.41</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
@@ -9345,91 +9345,91 @@
         <v>2.27</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB21" t="n">
         <v>1.45</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DD21" t="n">
         <v>4.66</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.56</v>
+        <v>83</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.34</v>
+        <v>6.21</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.78</v>
+        <v>44.47</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.16</v>
+        <v>16.05</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.28</v>
+        <v>7.42</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.66</v>
+        <v>46.26</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.28</v>
+        <v>13.21</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.890000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.38</v>
+        <v>20.16</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1935,10 +1935,10 @@
         <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>1.9</v>
@@ -1947,7 +1947,7 @@
         <v>19.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF3" t="n">
         <v>1.7</v>
@@ -2160,10 +2160,10 @@
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.69</v>
+        <v>10.74</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.84</v>
+        <v>7.9</v>
       </c>
       <c r="DZ3" t="n">
         <v>2.84</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>88.89</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>33.62</v>
+        <v>32.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.5</v>
+        <v>16.11</v>
       </c>
       <c r="R4" t="n">
-        <v>7.25</v>
+        <v>7.89</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.62</v>
+        <v>50.78</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.75</v>
+        <v>6.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.5</v>
+        <v>17.56</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.720000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.06</v>
+        <v>5.21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CC4" t="n">
         <v>3.69</v>
@@ -2431,7 +2431,7 @@
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CG4" t="n">
         <v>2.54</v>
@@ -2440,13 +2440,13 @@
         <v>1.3</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL4" t="n">
         <v>2.26</v>
@@ -2455,16 +2455,16 @@
         <v>2.12</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO4" t="n">
         <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
@@ -2473,7 +2473,7 @@
         <v>3.35</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CU4" t="n">
         <v>1.34</v>
@@ -2485,16 +2485,16 @@
         <v>2.03</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
@@ -2503,7 +2503,7 @@
         <v>2.42</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="DE4" t="n">
         <v>0.05</v>
@@ -2512,73 +2512,73 @@
         <v>2.11</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.5</v>
+        <v>87.42</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>33</v>
+        <v>32.63</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.11</v>
+        <v>13.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.83</v>
+        <v>14.74</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.74</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.72</v>
+        <v>49</v>
       </c>
       <c r="DW4" t="n">
         <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.44</v>
+        <v>10.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.56</v>
+        <v>6.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.61</v>
+        <v>18.58</v>
       </c>
       <c r="EB4" t="n">
         <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="5">
@@ -3117,7 +3117,7 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.33</v>
+        <v>17.22</v>
       </c>
       <c r="AS6" t="n">
         <v>7.78</v>
@@ -3348,7 +3348,7 @@
         <v>11.68</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.95</v>
+        <v>17.89</v>
       </c>
       <c r="DR6" t="n">
         <v>7.9</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,79 +3406,79 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="H7" t="n">
-        <v>89.12</v>
+        <v>94.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>4.88</v>
+        <v>5.67</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>48.62</v>
+        <v>52.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P7" t="n">
-        <v>14.5</v>
+        <v>13.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.380000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="R7" t="n">
-        <v>7.25</v>
+        <v>7.11</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.75</v>
+        <v>48.78</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.25</v>
+        <v>13.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.12</v>
+        <v>17.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>1.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.109999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.14</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.13</v>
       </c>
       <c r="CC7" t="n">
         <v>2.97</v>
@@ -3643,28 +3643,28 @@
         <v>3.16</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.95</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CO7" t="n">
         <v>1.39</v>
@@ -3673,16 +3673,16 @@
         <v>2.28</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS7" t="n">
         <v>3.3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
@@ -3694,100 +3694,100 @@
         <v>1.97</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DB7" t="n">
         <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="DH7" t="n">
-        <v>90.16</v>
+        <v>92.53</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.45</v>
+        <v>4.84</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.5</v>
+        <v>49.31</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>15</v>
+        <v>14.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.17</v>
+        <v>11.1</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.5</v>
+        <v>7.42</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.83</v>
+        <v>48.74</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.28</v>
+        <v>12.53</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.67</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.72</v>
+        <v>18.84</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,46 +3890,46 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.25</v>
+        <v>80.78</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.25</v>
+        <v>38.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.75</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.12</v>
+        <v>14.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>7.78</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.88</v>
+        <v>46.44</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.75</v>
+        <v>16.56</v>
       </c>
       <c r="BE8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL8" t="n">
         <v>1.05</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL8" t="n">
+      <c r="BM8" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.11</v>
       </c>
-      <c r="BM8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.67</v>
+        <v>4.95</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY8" t="n">
         <v>2.56</v>
@@ -4028,22 +4028,22 @@
         <v>2.78</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.47</v>
+        <v>3.61</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG8" t="n">
         <v>2.52</v>
@@ -4067,7 +4067,7 @@
         <v>2.15</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO8" t="n">
         <v>1.39</v>
@@ -4085,7 +4085,7 @@
         <v>3.32</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CU8" t="n">
         <v>1.35</v>
@@ -4097,7 +4097,7 @@
         <v>1.95</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY8" t="n">
         <v>2.05</v>
@@ -4112,67 +4112,67 @@
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DH8" t="n">
-        <v>81.94</v>
+        <v>80.84</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DK8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.39</v>
+        <v>38.79</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP8" t="n">
-        <v>16</v>
+        <v>15.68</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.78</v>
+        <v>14.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.72</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.61</v>
+        <v>46</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
         <v>10.89</v>
@@ -4181,16 +4181,16 @@
         <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -4245,7 +4245,7 @@
         <v>14.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.78</v>
+        <v>15.89</v>
       </c>
       <c r="R9" t="n">
         <v>8.779999999999999</v>
@@ -4557,7 +4557,7 @@
         <v>16.63</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="DR9" t="n">
         <v>8.789999999999999</v>
@@ -4903,16 +4903,16 @@
         <v>2.01</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
         <v>1.43</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>91.11</v>
+        <v>93.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="K11" t="n">
-        <v>6.44</v>
+        <v>6.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>47.89</v>
+        <v>46.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>13.44</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>17.89</v>
+        <v>17.9</v>
       </c>
       <c r="R11" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.67</v>
+        <v>17.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.22</v>
+        <v>11.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.44</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.67</v>
+        <v>17.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.89</v>
+        <v>5.79</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT11" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
         <v>4.35</v>
@@ -5252,28 +5252,28 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG11" t="n">
         <v>2.75</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI11" t="n">
         <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN11" t="n">
         <v>1.67</v>
@@ -5282,91 +5282,91 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.5</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.28</v>
+        <v>42.63</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.27</v>
+        <v>12.95</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.28</v>
+        <v>7.32</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.89</v>
+        <v>61.05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.12</v>
+        <v>14.69</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.83</v>
+        <v>9.58</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.28</v>
+        <v>5.1</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>101.88</v>
+        <v>106.56</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.88</v>
+        <v>7.44</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.38</v>
+        <v>60.22</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.12</v>
+        <v>13.78</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52.88</v>
+        <v>54.11</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.88</v>
+        <v>15.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.88</v>
+        <v>18.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.390000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO12" t="n">
         <v>0.89</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.89</v>
+        <v>4.11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY12" t="n">
         <v>1.96</v>
@@ -5640,22 +5640,22 @@
         <v>2.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CB12" t="n">
         <v>3.23</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG12" t="n">
         <v>2.6</v>
@@ -5664,31 +5664,31 @@
         <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO12" t="n">
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5697,28 +5697,28 @@
         <v>3.32</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW12" t="n">
         <v>1.98</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY12" t="n">
         <v>2.16</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB12" t="n">
         <v>1.4</v>
@@ -5730,79 +5730,79 @@
         <v>4.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DH12" t="n">
-        <v>100.72</v>
+        <v>103</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.84</v>
+        <v>6.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.45</v>
+        <v>59.74</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.94</v>
+        <v>14.84</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.39</v>
+        <v>14.21</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.17</v>
+        <v>52.79</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.78</v>
+        <v>17.58</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.72</v>
+        <v>12.47</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.67</v>
+        <v>18.89</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>94.5</v>
+        <v>94.89</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.88</v>
+        <v>46.89</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18.12</v>
+        <v>18.11</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.25</v>
+        <v>13.44</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.12</v>
+        <v>48.56</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.62</v>
+        <v>13.22</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.88</v>
+        <v>17.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY14" t="n">
         <v>1.79</v>
@@ -6449,76 +6449,76 @@
         <v>3.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI14" t="n">
         <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL14" t="n">
         <v>2.01</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
         <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.37</v>
@@ -6530,85 +6530,85 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.94</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.72</v>
+        <v>45.79</v>
       </c>
       <c r="DN14" t="n">
         <v>0.89</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.22</v>
+        <v>15.37</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.94</v>
+        <v>13.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.95</v>
+        <v>6.89</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.66</v>
+        <v>48</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.28</v>
+        <v>14.47</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.83</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.5</v>
+        <v>19.42</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="15">
@@ -6918,16 +6918,16 @@
         <v>1.92</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB15" t="n">
         <v>1.35</v>
@@ -7577,10 +7577,10 @@
         <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC17" t="n">
         <v>3.4</v>
@@ -7802,10 +7802,10 @@
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.89</v>
+        <v>13.84</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.16</v>
+        <v>10.11</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.74</v>
@@ -7953,7 +7953,7 @@
         <v>15.78</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.22</v>
+        <v>16.33</v>
       </c>
       <c r="AS18" t="n">
         <v>7.89</v>
@@ -8184,7 +8184,7 @@
         <v>15.63</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.74</v>
+        <v>16.79</v>
       </c>
       <c r="DR18" t="n">
         <v>7</v>
@@ -8272,7 +8272,7 @@
         <v>1.89</v>
       </c>
       <c r="P19" t="n">
-        <v>15.33</v>
+        <v>15.44</v>
       </c>
       <c r="Q19" t="n">
         <v>14.44</v>
@@ -8584,7 +8584,7 @@
         <v>1.95</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.42</v>
+        <v>17.47</v>
       </c>
       <c r="DQ19" t="n">
         <v>13.79</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -7436,79 +7436,79 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>102.22</v>
+        <v>101.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.33</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="M17" t="n">
-        <v>47.44</v>
+        <v>45.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>17.11</v>
+        <v>17.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.44</v>
+        <v>16.9</v>
       </c>
       <c r="R17" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.89</v>
+        <v>10.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.89</v>
+        <v>17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7595,70 +7595,70 @@
         <v>2.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.470000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS17" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CC17" t="n">
         <v>3.45</v>
@@ -7673,34 +7673,34 @@
         <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO17" t="n">
         <v>1.41</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
         <v>4.22</v>
@@ -7712,7 +7712,7 @@
         <v>3.3</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7724,100 +7724,100 @@
         <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.68</v>
+        <v>4.9</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.05</v>
+        <v>46.15</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.32</v>
+        <v>16.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>14.89</v>
+        <v>15.65</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.68</v>
+        <v>50.35</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.84</v>
+        <v>13.65</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.21</v>
+        <v>19.15</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="18">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>0.1</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>83.22</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.56</v>
+        <v>5.1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.33</v>
+        <v>41.4</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.78</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.220000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.44</v>
+        <v>18.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.53</v>
+        <v>11.45</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.74</v>
+        <v>6.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS21" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT21" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU21" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY21" t="n">
         <v>2.48</v>
@@ -9267,16 +9267,16 @@
         <v>2.61</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB21" t="n">
         <v>3.11</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CD21" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="CE21" t="n">
         <v>1.49</v>
@@ -9285,7 +9285,7 @@
         <v>3.3</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
@@ -9297,25 +9297,25 @@
         <v>2.01</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL21" t="n">
         <v>2.19</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
@@ -9324,7 +9324,7 @@
         <v>3.32</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
@@ -9333,16 +9333,16 @@
         <v>1.83</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA21" t="n">
         <v>1.81</v>
@@ -9351,85 +9351,85 @@
         <v>1.45</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="DE21" t="n">
         <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="DH21" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="DK21" t="n">
-        <v>6.21</v>
+        <v>5.95</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM21" t="n">
-        <v>44.47</v>
+        <v>43.9</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.05</v>
+        <v>16.75</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.47</v>
+        <v>13.1</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.42</v>
+        <v>7.35</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.26</v>
+        <v>46.75</v>
       </c>
       <c r="DW21" t="n">
         <v>0.1</v>
       </c>
       <c r="DX21" t="n">
-        <v>13.21</v>
+        <v>12.9</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.789999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.16</v>
+        <v>20.25</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>76.33</v>
+        <v>80.2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>34.33</v>
+        <v>34.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="P2" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.33</v>
+        <v>17.6</v>
       </c>
       <c r="R2" t="n">
-        <v>9.44</v>
+        <v>9.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.78</v>
+        <v>47.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.56</v>
+        <v>9.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.44</v>
+        <v>5.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.89</v>
+        <v>17.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,67 +1550,67 @@
         <v>2.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB2" t="n">
         <v>3.19</v>
@@ -1625,7 +1625,7 @@
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG2" t="n">
         <v>2.56</v>
@@ -1634,10 +1634,10 @@
         <v>1.32</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK2" t="n">
         <v>1.66</v>
@@ -1646,100 +1646,100 @@
         <v>2.2</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="CR2" t="n">
         <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX2" t="n">
         <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DG2" t="n">
         <v>2.3</v>
       </c>
-      <c r="DD2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DH2" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="DI2" t="n">
         <v>0.1</v>
       </c>
-      <c r="DF2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>82.73999999999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.11</v>
-      </c>
       <c r="DJ2" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.52</v>
+        <v>34.75</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.63</v>
+        <v>13.65</v>
       </c>
       <c r="DQ2" t="n">
-        <v>18.05</v>
+        <v>17.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.52</v>
+        <v>9.35</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.16</v>
+        <v>49.6</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.37</v>
+        <v>6.45</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.42</v>
+        <v>18.4</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>76.11</v>
+        <v>79.3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>15.89</v>
+        <v>16.3</v>
       </c>
       <c r="Q3" t="n">
         <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.67</v>
+        <v>11.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.11</v>
+        <v>15.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,70 +1953,70 @@
         <v>1.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.42</v>
+        <v>8.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="BR3" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CC3" t="n">
         <v>3.63</v>
@@ -2025,31 +2025,31 @@
         <v>4.58</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL3" t="n">
         <v>2.14</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN3" t="n">
         <v>1.74</v>
@@ -2058,10 +2058,10 @@
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
@@ -2076,10 +2076,10 @@
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX3" t="n">
         <v>1.66</v>
@@ -2106,43 +2106,43 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>79.63</v>
+        <v>81.05</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="DL3" t="n">
         <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>35.26</v>
+        <v>35.75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.9</v>
+        <v>15.15</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.11</v>
+        <v>15.15</v>
       </c>
       <c r="DR3" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="DS3" t="n">
         <v>0.1</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.58</v>
+        <v>49.95</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.74</v>
+        <v>10.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.47</v>
+        <v>17.6</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>88.89</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>32.78</v>
+        <v>35.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.11</v>
+        <v>16.5</v>
       </c>
       <c r="R4" t="n">
-        <v>7.89</v>
+        <v>8.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.78</v>
+        <v>51.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.22</v>
+        <v>11.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.22</v>
+        <v>6.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.56</v>
+        <v>17.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT4" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="CA4" t="n">
         <v>3.15</v>
@@ -2431,19 +2431,19 @@
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CH4" t="n">
         <v>1.3</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK4" t="n">
         <v>1.66</v>
@@ -2452,43 +2452,43 @@
         <v>2.26</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN4" t="n">
         <v>1.7</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
         <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.16</v>
@@ -2500,40 +2500,40 @@
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="DE4" t="n">
         <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.42</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.63</v>
+        <v>34</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
         <v>1.95</v>
@@ -2542,43 +2542,43 @@
         <v>13.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.74</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49</v>
+        <v>49.45</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.31</v>
+        <v>10.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.31</v>
+        <v>6.65</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.58</v>
+        <v>18.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
@@ -2678,139 +2678,139 @@
         <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.56</v>
+        <v>89.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>43.78</v>
+        <v>42.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.56</v>
+        <v>13.3</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.78</v>
+        <v>10.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.89</v>
+        <v>18.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.58</v>
+        <v>4.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
         <v>2.52</v>
@@ -2822,28 +2822,28 @@
         <v>3.15</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="CE5" t="n">
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH5" t="n">
         <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.9</v>
@@ -2864,37 +2864,37 @@
         <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
         <v>1.61</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
         <v>1.79</v>
@@ -2903,85 +2903,85 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.37</v>
+        <v>45.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.74</v>
+        <v>13.6</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.37</v>
+        <v>15.3</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.84</v>
+        <v>7.95</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.11</v>
+        <v>49.7</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.58</v>
+        <v>18.35</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>90.67</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.22</v>
+        <v>39.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.22</v>
+        <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>57.44</v>
+        <v>54.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.89</v>
+        <v>11.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.84</v>
+        <v>8.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.74</v>
+        <v>4.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BR6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
         <v>2.46</v>
@@ -3222,28 +3222,28 @@
         <v>2.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.97</v>
+        <v>4.24</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI6" t="n">
         <v>1.85</v>
@@ -3255,22 +3255,22 @@
         <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3291,64 +3291,64 @@
         <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.42</v>
+        <v>81</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.52</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.63</v>
+        <v>37.45</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.68</v>
+        <v>11.85</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.89</v>
+        <v>18</v>
       </c>
       <c r="DR6" t="n">
         <v>7.9</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.73</v>
+        <v>53.6</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.21</v>
+        <v>12.8</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.050000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.58</v>
+        <v>15.4</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AI7" t="n">
-        <v>91</v>
+        <v>92.27</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.6</v>
+        <v>46.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.4</v>
+        <v>15.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.6</v>
+        <v>12.45</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.7</v>
+        <v>8.09</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>48.7</v>
+        <v>49.36</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>11.27</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
         <v>1.33</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
         <v>2.15</v>
@@ -3625,31 +3625,31 @@
         <v>2.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
         <v>3.14</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.95</v>
@@ -3658,7 +3658,7 @@
         <v>1.78</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM7" t="n">
         <v>1.96</v>
@@ -3673,16 +3673,16 @@
         <v>2.28</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DH7" t="n">
-        <v>92.53</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.31</v>
+        <v>49.1</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.58</v>
+        <v>14.55</v>
       </c>
       <c r="DQ7" t="n">
         <v>11.1</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.42</v>
+        <v>7.65</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.74</v>
+        <v>49.1</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.53</v>
+        <v>12.35</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.789999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.84</v>
+        <v>18.35</v>
       </c>
       <c r="EB7" t="n">
         <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="H8" t="n">
-        <v>80.90000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>38.7</v>
+        <v>40.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.5</v>
+        <v>15.18</v>
       </c>
       <c r="R8" t="n">
-        <v>8.300000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>45.6</v>
+        <v>47.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.5</v>
+        <v>12.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.1</v>
+        <v>21.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,34 +3968,34 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.95</v>
@@ -4004,28 +4004,28 @@
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CA8" t="n">
         <v>3.04</v>
@@ -4040,13 +4040,13 @@
         <v>3.61</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
         <v>3.15</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4076,7 +4076,7 @@
         <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CR8" t="n">
         <v>1.5</v>
@@ -4094,19 +4094,19 @@
         <v>1.92</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
@@ -4121,43 +4121,43 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>80.84</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM8" t="n">
-        <v>38.79</v>
+        <v>39.55</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.68</v>
+        <v>15.65</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.37</v>
+        <v>14.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.050000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46</v>
+        <v>47.15</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="EB8" t="n">
         <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.33</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.59999999999999</v>
+        <v>77.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.8</v>
+        <v>41.73</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.3</v>
+        <v>18.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.8</v>
+        <v>14.91</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.6</v>
+        <v>46.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.9</v>
+        <v>15.27</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="BD9" t="n">
-        <v>18</v>
+        <v>17.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.37</v>
+        <v>4.55</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.32</v>
@@ -4431,16 +4431,16 @@
         <v>2.43</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -4464,7 +4464,7 @@
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
         <v>2.23</v>
@@ -4479,16 +4479,16 @@
         <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CU9" t="n">
         <v>1.4</v>
@@ -4497,7 +4497,7 @@
         <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
         <v>1.61</v>
@@ -4515,52 +4515,52 @@
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.84</v>
+        <v>80.75</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DK9" t="n">
         <v>4.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.58</v>
+        <v>42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.63</v>
+        <v>16.85</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.32</v>
+        <v>15.35</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DS9" t="n">
         <v>0.1</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.74</v>
+        <v>47.5</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.47</v>
+        <v>16.1</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.16</v>
+        <v>17.7</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -4693,130 +4693,130 @@
         <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>91.22</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.67</v>
+        <v>35.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.22</v>
+        <v>17.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.67</v>
+        <v>12.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.78</v>
+        <v>51.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.22</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.44</v>
+        <v>19.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.529999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT10" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
         <v>2.38</v>
@@ -4834,40 +4834,40 @@
         <v>2.47</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF10" t="n">
         <v>3.24</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK10" t="n">
         <v>1.67</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM10" t="n">
         <v>2.12</v>
@@ -4879,10 +4879,10 @@
         <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="CR10" t="n">
         <v>1.52</v>
@@ -4900,13 +4900,13 @@
         <v>1.85</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX10" t="n">
         <v>1.7</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.14</v>
@@ -4927,76 +4927,76 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.58</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.05</v>
+        <v>39.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.16</v>
+        <v>17.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.63</v>
+        <v>13.9</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54</v>
+        <v>53.45</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.79</v>
+        <v>12.05</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.26</v>
+        <v>8.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.53</v>
+        <v>3.65</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.26</v>
+        <v>20.15</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>87.89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>38.67</v>
+        <v>39.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.11</v>
+        <v>13.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.67</v>
+        <v>18.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>56.78</v>
+        <v>55.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.56</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.44</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.11</v>
+        <v>16.4</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BN11" t="n">
         <v>1.3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
         <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>2.6</v>
@@ -5237,25 +5237,25 @@
         <v>2.86</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CH11" t="n">
         <v>1.38</v>
@@ -5270,49 +5270,49 @@
         <v>1.67</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
         <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY11" t="n">
         <v>2.1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA11" t="n">
         <v>1.73</v>
@@ -5324,82 +5324,82 @@
         <v>2.02</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.68000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.63</v>
+        <v>42.85</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.95</v>
+        <v>13.3</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.26</v>
+        <v>18.05</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.32</v>
+        <v>7.2</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.05</v>
+        <v>60.1</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.69</v>
+        <v>14.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.58</v>
+        <v>9.65</v>
       </c>
       <c r="DZ11" t="n">
         <v>5.1</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.26</v>
+        <v>16.9</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>106.56</v>
+        <v>105</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.22</v>
+        <v>58.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.67</v>
+        <v>16.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.78</v>
+        <v>14.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54.11</v>
+        <v>53</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>15.22</v>
+        <v>14.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.44</v>
+        <v>18.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.68</v>
+        <v>9.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.58</v>
+        <v>5.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY12" t="n">
         <v>1.96</v>
@@ -5640,106 +5640,106 @@
         <v>2.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CW12" t="n">
         <v>1.97</v>
       </c>
-      <c r="CK12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1.98</v>
-      </c>
       <c r="CX12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="DB12" t="n">
         <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="DH12" t="n">
-        <v>103</v>
+        <v>102.4</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
@@ -5748,58 +5748,58 @@
         <v>2.05</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.16</v>
+        <v>6.3</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>59.74</v>
+        <v>58.7</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.84</v>
+        <v>15.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.21</v>
+        <v>14.35</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.79</v>
+        <v>52.3</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>17.58</v>
+        <v>17.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>12.47</v>
+        <v>12.1</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.89</v>
+        <v>18.85</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="EC12" t="n">
         <v>2.05</v>
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>111</v>
+        <v>109.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="M13" t="n">
-        <v>53.67</v>
+        <v>54.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>13.89</v>
+        <v>14.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.11</v>
+        <v>14.8</v>
       </c>
       <c r="R13" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.78</v>
+        <v>14.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.22</v>
+        <v>16.6</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1</v>
@@ -5983,67 +5983,67 @@
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.68</v>
+        <v>8.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT13" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CB13" t="n">
         <v>3.38</v>
@@ -6058,19 +6058,19 @@
         <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
         <v>1.7</v>
@@ -6079,7 +6079,7 @@
         <v>2.28</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN13" t="n">
         <v>1.64</v>
@@ -6088,28 +6088,28 @@
         <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX13" t="n">
         <v>1.75</v>
@@ -6124,55 +6124,55 @@
         <v>1.65</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.95</v>
+        <v>100.5</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.32</v>
+        <v>46.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.16</v>
+        <v>15.2</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.53</v>
+        <v>13.9</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.21</v>
+        <v>53.4</v>
       </c>
       <c r="DW13" t="n">
         <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.369999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.89</v>
+        <v>16.1</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="H14" t="n">
-        <v>91.7</v>
+        <v>92.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M14" t="n">
-        <v>44.8</v>
+        <v>45.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>12.9</v>
+        <v>13.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.7</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
         <v>0.33</v>
@@ -6386,70 +6386,70 @@
         <v>2.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO14" t="n">
         <v>0.95</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="BR14" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
         <v>2.33</v>
@@ -6461,7 +6461,7 @@
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG14" t="n">
         <v>2.7</v>
@@ -6473,28 +6473,28 @@
         <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL14" t="n">
         <v>2.01</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO14" t="n">
         <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6509,22 +6509,22 @@
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.37</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
@@ -6536,46 +6536,46 @@
         <v>3.74</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.20999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.79</v>
+        <v>45.9</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.37</v>
+        <v>15.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.58</v>
+        <v>13.75</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="DS14" t="n">
         <v>0.1</v>
@@ -6590,19 +6590,19 @@
         <v>48</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.47</v>
+        <v>14.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.42</v>
+        <v>19.2</v>
       </c>
       <c r="EB14" t="n">
         <v>1.56</v>
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="H15" t="n">
-        <v>81.5</v>
+        <v>85.55</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="K15" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M15" t="n">
-        <v>37.8</v>
+        <v>38.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P15" t="n">
-        <v>14.2</v>
+        <v>14.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.8</v>
+        <v>16.18</v>
       </c>
       <c r="R15" t="n">
-        <v>6.7</v>
+        <v>6.82</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.4</v>
+        <v>50.09</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>16.64</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.7</v>
+        <v>19.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
         <v>0.22</v>
@@ -6789,70 +6789,70 @@
         <v>2.56</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.37</v>
+        <v>11.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.89</v>
+        <v>5.95</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT15" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU15" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="CA15" t="n">
         <v>3.46</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>3.45</v>
-      </c>
       <c r="CB15" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CC15" t="n">
         <v>4.86</v>
@@ -6864,121 +6864,121 @@
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CH15" t="n">
         <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO15" t="n">
         <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CU15" t="n">
         <v>1.39</v>
       </c>
       <c r="CV15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DJ15" t="n">
         <v>1.95</v>
       </c>
-      <c r="CW15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>75.42</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>2.05</v>
-      </c>
       <c r="DK15" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM15" t="n">
-        <v>33.21</v>
+        <v>33.8</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.31</v>
+        <v>14.45</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.16</v>
+        <v>15.4</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48</v>
+        <v>48.45</v>
       </c>
       <c r="DW15" t="n">
         <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>14</v>
+        <v>13.95</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.16</v>
+        <v>9.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.63</v>
+        <v>18.7</v>
       </c>
       <c r="EB15" t="n">
         <v>1.42</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>79.44</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>13.78</v>
+        <v>13.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.78</v>
+        <v>13.8</v>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.56</v>
+        <v>45.4</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.33</v>
+        <v>12.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.22</v>
+        <v>15.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.789999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="BR16" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT16" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU16" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
         <v>4.46</v>
@@ -7267,67 +7267,67 @@
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.93</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL16" t="n">
         <v>2.24</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO16" t="n">
         <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW16" t="n">
         <v>1.95</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA16" t="n">
         <v>1.74</v>
@@ -7336,52 +7336,52 @@
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>77.47</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.84</v>
+        <v>35.3</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.21</v>
+        <v>15.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.42</v>
+        <v>14.4</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="DS16" t="n">
         <v>0.05</v>
@@ -7396,22 +7396,22 @@
         <v>44.05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.52</v>
+        <v>10.9</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.74</v>
+        <v>7.05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.31</v>
+        <v>16.25</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
         <v>2.05</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.2</v>
@@ -7917,139 +7917,139 @@
         <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>88.67</v>
+        <v>87.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.89</v>
+        <v>39.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.78</v>
+        <v>15.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.33</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.89</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.44</v>
+        <v>45.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.22</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.44</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.22</v>
+        <v>19.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.32</v>
+        <v>10.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BV18" t="n">
         <v>5</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
         <v>2.11</v>
@@ -8058,136 +8058,136 @@
         <v>2.26</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="CE18" t="n">
         <v>1.47</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH18" t="n">
         <v>1.31</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.95</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL18" t="n">
         <v>2.13</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="CR18" t="n">
         <v>1.5</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV18" t="n">
         <v>1.88</v>
       </c>
       <c r="CW18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB18" t="n">
         <v>1.42</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DH18" t="n">
-        <v>91.05</v>
+        <v>90.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.74</v>
+        <v>4.9</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="DN18" t="n">
         <v>0.95</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.63</v>
+        <v>15.7</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.79</v>
+        <v>16.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="DS18" t="n">
         <v>0.05</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.73</v>
+        <v>47</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.21</v>
+        <v>10.4</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.31</v>
+        <v>6.55</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.89</v>
+        <v>17.95</v>
       </c>
       <c r="EB18" t="n">
         <v>1.23</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.11</v>
@@ -8323,127 +8323,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>95.3</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.4</v>
+        <v>49.82</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.3</v>
+        <v>19.55</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.2</v>
+        <v>13.36</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>37.2</v>
+        <v>36.64</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.7</v>
+        <v>10.27</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>6.91</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.5</v>
+        <v>23.18</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.16</v>
+        <v>8.35</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN19" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BR19" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT19" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU19" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
         <v>2.41</v>
@@ -8461,25 +8461,25 @@
         <v>2.44</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
         <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8488,7 +8488,7 @@
         <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK19" t="n">
         <v>1.63</v>
@@ -8497,19 +8497,19 @@
         <v>2.24</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
@@ -8524,73 +8524,73 @@
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="DH19" t="n">
-        <v>97</v>
+        <v>96.3</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM19" t="n">
-        <v>57.58</v>
+        <v>55.9</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.47</v>
+        <v>17.7</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.79</v>
+        <v>13.85</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.05</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>38.21</v>
+        <v>37.85</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.37</v>
+        <v>12.05</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.789999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.63</v>
+        <v>24.4</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
-        <v>105.89</v>
+        <v>106.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>46.44</v>
+        <v>49.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>15.33</v>
+        <v>15.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.67</v>
+        <v>16.4</v>
       </c>
       <c r="R20" t="n">
-        <v>6.78</v>
+        <v>6.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>63.11</v>
+        <v>63.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.33</v>
+        <v>17.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.78</v>
+        <v>12.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.67</v>
+        <v>14.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
         <v>0.1</v>
@@ -8804,70 +8804,70 @@
         <v>2.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.050000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="BR20" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS20" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT20" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="CC20" t="n">
         <v>2.26</v>
@@ -8876,19 +8876,19 @@
         <v>2.34</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH20" t="n">
         <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.89</v>
@@ -8897,7 +8897,7 @@
         <v>1.57</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM20" t="n">
         <v>2.26</v>
@@ -8906,13 +8906,13 @@
         <v>1.78</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CR20" t="n">
         <v>1.43</v>
@@ -8942,91 +8942,91 @@
         <v>2.27</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH20" t="n">
-        <v>109.37</v>
+        <v>109.4</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM20" t="n">
-        <v>50.47</v>
+        <v>51.6</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.84</v>
+        <v>15.1</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.11</v>
+        <v>15.05</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.16</v>
+        <v>5.95</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>61.95</v>
+        <v>62.25</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX20" t="n">
-        <v>16.63</v>
+        <v>16.95</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.21</v>
+        <v>11.5</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.53</v>
+        <v>16.4</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H5" t="n">
-        <v>87.3</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>5.36</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M5" t="n">
-        <v>48.7</v>
+        <v>47.73</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P5" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.2</v>
+        <v>50.55</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.9</v>
+        <v>14.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.8</v>
+        <v>10.27</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.3</v>
+        <v>18.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.7</v>
+        <v>4.57</v>
       </c>
       <c r="BQ5" t="n">
         <v>5.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="BZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC5" t="n">
         <v>3.88</v>
@@ -2834,7 +2834,7 @@
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG5" t="n">
         <v>2.61</v>
@@ -2846,7 +2846,7 @@
         <v>1.84</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK5" t="n">
         <v>1.57</v>
@@ -2855,10 +2855,10 @@
         <v>2.12</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO5" t="n">
         <v>1.35</v>
@@ -2867,13 +2867,13 @@
         <v>2.15</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT5" t="n">
         <v>2.83</v>
@@ -2885,7 +2885,7 @@
         <v>1.97</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
         <v>1.61</v>
@@ -2906,82 +2906,82 @@
         <v>2.22</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.3</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.3</v>
+        <v>5.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.8</v>
+        <v>45.43</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.3</v>
+        <v>15.05</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.95</v>
+        <v>7.86</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.7</v>
+        <v>49.91</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.35</v>
+        <v>18.57</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="6">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.78</v>
+        <v>82.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.89</v>
+        <v>39.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>15.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.22</v>
+        <v>13.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,58 +3944,58 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.44</v>
+        <v>46.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.109999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.56</v>
+        <v>17.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO8" t="n">
         <v>1.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.65</v>
+        <v>4.52</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.95</v>
@@ -4004,22 +4004,22 @@
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT8" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU8" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4028,7 +4028,7 @@
         <v>2.76</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CB8" t="n">
         <v>3.06</v>
@@ -4037,7 +4037,7 @@
         <v>3.27</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
@@ -4055,7 +4055,7 @@
         <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
         <v>1.61</v>
@@ -4064,7 +4064,7 @@
         <v>2.12</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN8" t="n">
         <v>1.73</v>
@@ -4073,25 +4073,25 @@
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CU8" t="n">
         <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW8" t="n">
         <v>1.94</v>
@@ -4109,55 +4109,55 @@
         <v>1.76</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>81.65000000000001</v>
+        <v>82.28</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.55</v>
+        <v>39.81</v>
       </c>
       <c r="DN8" t="n">
         <v>0.95</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.65</v>
+        <v>15.38</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.75</v>
+        <v>14.57</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.15</v>
+        <v>47.1</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DY8" t="n">
         <v>6.95</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.2</v>
+        <v>19.71</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,52 +1469,52 @@
         <v>2.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>88.5</v>
+        <v>87.91</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>34.7</v>
+        <v>35.82</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.6</v>
+        <v>13.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.8</v>
+        <v>17.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.3</v>
+        <v>51.91</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.1</v>
+        <v>10.18</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>7.45</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.9</v>
+        <v>19.73</v>
       </c>
       <c r="BE2" t="n">
         <v>1.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY2" t="n">
         <v>2.93</v>
@@ -1616,7 +1616,7 @@
         <v>3.19</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CD2" t="n">
         <v>3.97</v>
@@ -1625,10 +1625,10 @@
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH2" t="n">
         <v>1.32</v>
@@ -1640,37 +1640,37 @@
         <v>1.93</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO2" t="n">
         <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV2" t="n">
         <v>1.92</v>
@@ -1679,67 +1679,67 @@
         <v>1.94</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC2" t="n">
         <v>2.28</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.34999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.75</v>
+        <v>35.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.7</v>
+        <v>17.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.45</v>
+        <v>6.62</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.4</v>
+        <v>18.86</v>
       </c>
       <c r="EB2" t="n">
         <v>1.14</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>82.91</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>2.55</v>
@@ -2013,16 +2013,16 @@
         <v>2.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.58</v>
+        <v>4.72</v>
       </c>
       <c r="CE3" t="n">
         <v>1.46</v>
@@ -2031,7 +2031,7 @@
         <v>3.09</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
@@ -2046,13 +2046,13 @@
         <v>1.63</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM3" t="n">
         <v>2.2</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
@@ -2061,16 +2061,16 @@
         <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2097,52 +2097,52 @@
         <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>81.05</v>
+        <v>81.19</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="DL3" t="n">
         <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>35.75</v>
+        <v>35.05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.15</v>
+        <v>14.95</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.15</v>
+        <v>14.91</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.95</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.1</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.95</v>
+        <v>49.33</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.8</v>
+        <v>7.52</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.6</v>
+        <v>17.62</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.09999999999999</v>
+        <v>86.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.5</v>
+        <v>32.82</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>15.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,73 +2332,73 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.4</v>
+        <v>47.82</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.4</v>
+        <v>10.64</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>6.64</v>
       </c>
       <c r="BC4" t="n">
         <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>19.91</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.9</v>
+        <v>9.81</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
         <v>1.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BR4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY4" t="n">
         <v>2.9</v>
@@ -2419,13 +2419,13 @@
         <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
@@ -2434,7 +2434,7 @@
         <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CH4" t="n">
         <v>1.3</v>
@@ -2446,16 +2446,16 @@
         <v>1.97</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL4" t="n">
         <v>2.26</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO4" t="n">
         <v>1.41</v>
@@ -2485,13 +2485,13 @@
         <v>2.02</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
         <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA4" t="n">
         <v>1.72</v>
@@ -2500,85 +2500,85 @@
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="DE4" t="n">
         <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.84999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.95</v>
+        <v>14.1</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>14.76</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.949999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.45</v>
+        <v>49.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.65</v>
+        <v>6.76</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.4</v>
+        <v>18.67</v>
       </c>
       <c r="EB4" t="n">
         <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -2822,7 +2822,7 @@
         <v>3.14</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CC5" t="n">
         <v>3.88</v>
@@ -2876,37 +2876,37 @@
         <v>3.18</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU5" t="n">
         <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW5" t="n">
         <v>1.89</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY5" t="n">
         <v>2.01</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>76.90000000000001</v>
+        <v>81.91</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>35.4</v>
+        <v>35.73</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P6" t="n">
-        <v>11.4</v>
+        <v>11.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.5</v>
+        <v>18.64</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.3</v>
+        <v>52.45</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="AA6" t="n">
         <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.9</v>
+        <v>17.64</v>
       </c>
       <c r="AD6" t="n">
         <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AF6" t="n">
         <v>0.2</v>
@@ -3162,70 +3162,70 @@
         <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.6</v>
+        <v>8.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.05</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU6" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CA6" t="n">
         <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC6" t="n">
         <v>3.98</v>
@@ -3234,7 +3234,7 @@
         <v>4.24</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
         <v>3.06</v>
@@ -3258,7 +3258,7 @@
         <v>2.23</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.67</v>
@@ -3276,10 +3276,10 @@
         <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU6" t="n">
         <v>1.36</v>
@@ -3291,100 +3291,100 @@
         <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="DE6" t="n">
         <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DG6" t="n">
         <v>1.95</v>
       </c>
       <c r="DH6" t="n">
-        <v>81</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.45</v>
+        <v>37.53</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.85</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.9</v>
+        <v>7.76</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.6</v>
+        <v>53.62</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.8</v>
+        <v>12.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.4</v>
+        <v>15.38</v>
       </c>
       <c r="EB6" t="n">
         <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3406,79 +3406,79 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="H7" t="n">
-        <v>94.22</v>
+        <v>96.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K7" t="n">
-        <v>5.67</v>
+        <v>6.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52.33</v>
+        <v>55.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>13.67</v>
+        <v>13.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.44</v>
+        <v>9.6</v>
       </c>
       <c r="R7" t="n">
-        <v>7.11</v>
+        <v>6.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.78</v>
+        <v>50.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.67</v>
+        <v>13.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.56</v>
+        <v>18.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.449999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.85</v>
+        <v>4.19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV7" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CC7" t="n">
         <v>2.9</v>
@@ -3640,10 +3640,10 @@
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3655,10 +3655,10 @@
         <v>1.95</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM7" t="n">
         <v>1.96</v>
@@ -3670,19 +3670,19 @@
         <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
@@ -3694,97 +3694,97 @@
         <v>1.97</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.15000000000001</v>
+        <v>94.14</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.85</v>
+        <v>5.38</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.1</v>
+        <v>50.57</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.55</v>
+        <v>14.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.65</v>
+        <v>7.38</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.1</v>
+        <v>49.76</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.35</v>
+        <v>12.52</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.35</v>
+        <v>18.57</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
         <v>2</v>
@@ -4037,7 +4037,7 @@
         <v>3.27</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
@@ -4082,7 +4082,7 @@
         <v>1.49</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CT8" t="n">
         <v>2.72</v>
@@ -4094,19 +4094,19 @@
         <v>1.93</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB8" t="n">
         <v>1.41</v>
@@ -4115,7 +4115,7 @@
         <v>2.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
@@ -4200,91 +4200,91 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>84.44</v>
+        <v>88.2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>42.33</v>
+        <v>44.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>14.78</v>
+        <v>15.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.89</v>
+        <v>15.8</v>
       </c>
       <c r="R9" t="n">
-        <v>8.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.11</v>
+        <v>16.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.33</v>
+        <v>18.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -4371,70 +4371,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CC9" t="n">
         <v>3.16</v>
@@ -4446,28 +4446,28 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI9" t="n">
         <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN9" t="n">
         <v>1.79</v>
@@ -4476,22 +4476,22 @@
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV9" t="n">
         <v>2.11</v>
@@ -4500,100 +4500,100 @@
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF9" t="n">
         <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.75</v>
+        <v>82.72</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>42</v>
+        <v>43.24</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.85</v>
+        <v>16.91</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.35</v>
+        <v>15.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.5</v>
+        <v>48.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.1</v>
+        <v>16.05</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.6</v>
+        <v>10.67</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.7</v>
+        <v>17.95</v>
       </c>
       <c r="EB9" t="n">
         <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="H10" t="n">
-        <v>91.90000000000001</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>42.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>17.1</v>
+        <v>16.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.4</v>
+        <v>15.18</v>
       </c>
       <c r="R10" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.1</v>
+        <v>55.27</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>21</v>
+        <v>21.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,49 +4774,49 @@
         <v>3.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.6</v>
+        <v>8.52</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BO10" t="n">
         <v>1.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BR10" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT10" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
         <v>3.23</v>
@@ -4852,7 +4852,7 @@
         <v>3.24</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH10" t="n">
         <v>1.29</v>
@@ -4864,25 +4864,25 @@
         <v>1.99</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.52</v>
@@ -4909,94 +4909,94 @@
         <v>2.13</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.40000000000001</v>
+        <v>92.09</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.25</v>
+        <v>39.19</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.1</v>
+        <v>16.86</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.6</v>
+        <v>6.52</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.45</v>
+        <v>53.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.05</v>
+        <v>12.14</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.4</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.15</v>
+        <v>20.28</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H11" t="n">
-        <v>93.2</v>
+        <v>91.64</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K11" t="n">
-        <v>6.1</v>
+        <v>5.82</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="P11" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>17.9</v>
+        <v>17.45</v>
       </c>
       <c r="R11" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>64.90000000000001</v>
+        <v>62.82</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.5</v>
+        <v>16.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.5</v>
+        <v>10.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.4</v>
+        <v>17.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.3</v>
+        <v>10.38</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.86</v>
+        <v>3.11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="CC11" t="n">
         <v>4.24</v>
@@ -5249,13 +5249,13 @@
         <v>4.78</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CH11" t="n">
         <v>1.38</v>
@@ -5267,139 +5267,139 @@
         <v>1.79</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
         <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX11" t="n">
         <v>1.67</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.18</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.15000000000001</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.85</v>
+        <v>42.9</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.3</v>
+        <v>13.29</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.05</v>
+        <v>17.81</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.2</v>
+        <v>7.14</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.1</v>
+        <v>59.24</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.75</v>
+        <v>14.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.9</v>
+        <v>16.86</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5424,79 +5424,79 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="H12" t="n">
-        <v>99.8</v>
+        <v>98.45</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="K12" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="AB12" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AC12" t="n">
-        <v>19.3</v>
+        <v>20.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5580,49 +5580,49 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.85</v>
+        <v>9.67</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.6</v>
+        <v>5.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC12" t="n">
         <v>2.42</v>
@@ -5658,37 +5658,37 @@
         <v>3.09</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN12" t="n">
         <v>1.68</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP12" t="n">
         <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
@@ -5703,106 +5703,106 @@
         <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC12" t="n">
         <v>2.28</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="DH12" t="n">
-        <v>102.4</v>
+        <v>101.57</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.7</v>
+        <v>57.57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.1</v>
+        <v>15.19</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.35</v>
+        <v>14.48</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>17.25</v>
+        <v>16.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>12.1</v>
+        <v>11.91</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.85</v>
+        <v>19.43</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>109.1</v>
+        <v>106</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
-        <v>54.1</v>
+        <v>52.91</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>14.1</v>
+        <v>13.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.1</v>
+        <v>55.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.2</v>
+        <v>13.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.6</v>
+        <v>17.27</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1</v>
@@ -5983,70 +5983,70 @@
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.9</v>
+        <v>9.24</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
         <v>1.05</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.45</v>
+        <v>4.76</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>1.73</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CA13" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="CC13" t="n">
         <v>2.41</v>
@@ -6055,55 +6055,55 @@
         <v>2.62</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="CR13" t="n">
         <v>1.47</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV13" t="n">
         <v>1.85</v>
@@ -6115,64 +6115,64 @@
         <v>1.75</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.07</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.5</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.9</v>
+        <v>46.62</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.2</v>
+        <v>15.05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.9</v>
+        <v>14.05</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.85</v>
+        <v>6.14</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.4</v>
+        <v>53.24</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.1</v>
+        <v>13.81</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.65</v>
+        <v>9.33</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.1</v>
+        <v>16.47</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6305,139 +6305,139 @@
         <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>94.89</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.89</v>
+        <v>46.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18.11</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.44</v>
+        <v>13.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.109999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AV14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT14" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY14" t="n">
         <v>1.78</v>
@@ -6446,31 +6446,31 @@
         <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH14" t="n">
         <v>1.36</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.87</v>
@@ -6485,7 +6485,7 @@
         <v>2.38</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
         <v>1.32</v>
@@ -6494,7 +6494,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6509,13 +6509,13 @@
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
         <v>1.95</v>
@@ -6536,76 +6536,76 @@
         <v>3.74</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.7</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.9</v>
+        <v>45.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.5</v>
+        <v>15.57</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.75</v>
+        <v>13.9</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48</v>
+        <v>48.29</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.5</v>
+        <v>13.95</v>
       </c>
       <c r="DY14" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.2</v>
+        <v>19.28</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="EC14" t="n">
         <v>2.05</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.18</v>
@@ -6708,139 +6708,139 @@
         <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>68.67</v>
+        <v>71.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>28.11</v>
+        <v>30.3</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.44</v>
+        <v>14.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.44</v>
+        <v>14.2</v>
       </c>
       <c r="AS15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BB15" t="n">
         <v>8</v>
       </c>
-      <c r="AT15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.22</v>
-      </c>
       <c r="BC15" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.44</v>
+        <v>17.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.45</v>
+        <v>11.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
         <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.45</v>
+        <v>5.71</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
         <v>3.53</v>
@@ -6849,28 +6849,28 @@
         <v>3.94</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.86</v>
+        <v>4.97</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.56</v>
+        <v>5.82</v>
       </c>
       <c r="CE15" t="n">
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
         <v>1.84</v>
@@ -6879,106 +6879,106 @@
         <v>1.9</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX15" t="n">
         <v>1.62</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.27</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="DH15" t="n">
-        <v>77.95</v>
+        <v>79</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
         <v>1.95</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM15" t="n">
-        <v>33.8</v>
+        <v>34.57</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.45</v>
+        <v>14.57</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.4</v>
+        <v>15.24</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.35</v>
+        <v>7.14</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.45</v>
+        <v>48.52</v>
       </c>
       <c r="DW15" t="n">
         <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.95</v>
+        <v>14.24</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.25</v>
+        <v>9.52</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.7</v>
+        <v>18.76</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>75.7</v>
+        <v>74.91</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.2</v>
+        <v>30.55</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.5</v>
+        <v>16.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.2</v>
+        <v>10.45</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.7</v>
+        <v>42.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.9</v>
+        <v>9.09</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.9</v>
+        <v>6.09</v>
       </c>
       <c r="BC16" t="n">
         <v>3</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.3</v>
+        <v>17.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.35</v>
+        <v>5.24</v>
       </c>
       <c r="BR16" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>3.37</v>
@@ -7252,136 +7252,136 @@
         <v>3.73</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="CD16" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CM16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP16" t="n">
         <v>2.13</v>
       </c>
-      <c r="CN16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="CQ16" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DD16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG16" t="n">
         <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>78.65000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.3</v>
+        <v>35.24</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DP16" t="n">
         <v>15.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.4</v>
+        <v>14.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.9</v>
+        <v>10.05</v>
       </c>
       <c r="DS16" t="n">
         <v>0.05</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.05</v>
+        <v>43.91</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
         <v>10.9</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.25</v>
+        <v>16.43</v>
       </c>
       <c r="EB16" t="n">
         <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AI17" t="n">
-        <v>98</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.7</v>
+        <v>44.09</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.9</v>
+        <v>7.64</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.8</v>
+        <v>12.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.3</v>
+        <v>20.55</v>
       </c>
       <c r="BE17" t="n">
         <v>1.39</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS17" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY17" t="n">
         <v>2.18</v>
@@ -7655,16 +7655,16 @@
         <v>2.29</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CB17" t="n">
         <v>3.12</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="CE17" t="n">
         <v>1.47</v>
@@ -7679,16 +7679,16 @@
         <v>1.31</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK17" t="n">
         <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM17" t="n">
         <v>2.07</v>
@@ -7700,16 +7700,16 @@
         <v>1.41</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT17" t="n">
         <v>2.66</v>
@@ -7724,7 +7724,7 @@
         <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY17" t="n">
         <v>2.21</v>
@@ -7736,88 +7736,88 @@
         <v>1.64</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DH17" t="n">
-        <v>99.8</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.15</v>
+        <v>44.81</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.75</v>
+        <v>16.9</v>
       </c>
       <c r="DQ17" t="n">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.95</v>
+        <v>7.34</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.35</v>
+        <v>50.14</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.9</v>
+        <v>9.81</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.15</v>
+        <v>18.86</v>
       </c>
       <c r="EB17" t="n">
         <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>93.2</v>
+        <v>93.73</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M18" t="n">
-        <v>44.6</v>
+        <v>43.91</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
-        <v>15.5</v>
+        <v>15.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.2</v>
+        <v>16.91</v>
       </c>
       <c r="R18" t="n">
-        <v>6.2</v>
+        <v>6.27</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.8</v>
+        <v>48.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.3</v>
+        <v>5.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.7</v>
+        <v>16.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AF18" t="n">
         <v>0.1</v>
@@ -7998,67 +7998,67 @@
         <v>2.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.65</v>
+        <v>10.71</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BO18" t="n">
         <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU18" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB18" t="n">
         <v>3.21</v>
@@ -8076,46 +8076,46 @@
         <v>3.16</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI18" t="n">
         <v>1.79</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO18" t="n">
         <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU18" t="n">
         <v>1.36</v>
@@ -8127,67 +8127,67 @@
         <v>1.99</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.5</v>
+        <v>90.91</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM18" t="n">
-        <v>42</v>
+        <v>41.76</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="DP18" t="n">
-        <v>15.7</v>
+        <v>15.76</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.85</v>
+        <v>16.71</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="DS18" t="n">
         <v>0.05</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.4</v>
+        <v>10.48</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.55</v>
+        <v>6.76</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.95</v>
+        <v>17.76</v>
       </c>
       <c r="EB18" t="n">
         <v>1.23</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>98.89</v>
+        <v>100.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="M19" t="n">
-        <v>63.33</v>
+        <v>64.5</v>
       </c>
       <c r="N19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P19" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="R19" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.11</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>39.33</v>
+        <v>40.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.22</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>25.89</v>
+        <v>25.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.35</v>
+        <v>8.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN19" t="n">
         <v>0.95</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,19 +8452,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CA19" t="n">
         <v>3.16</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC19" t="n">
         <v>3.74</v>
@@ -8476,28 +8476,28 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI19" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL19" t="n">
         <v>2.24</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN19" t="n">
         <v>1.75</v>
@@ -8509,7 +8509,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
@@ -8524,10 +8524,10 @@
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.65</v>
@@ -8542,88 +8542,88 @@
         <v>1.76</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.3</v>
+        <v>97.28</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.9</v>
+        <v>56.81</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.7</v>
+        <v>17.34</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>37.85</v>
+        <v>38.34</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.05</v>
+        <v>12.52</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.4</v>
+        <v>24.24</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0.2</v>
@@ -8723,139 +8723,139 @@
         <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AI20" t="n">
-        <v>112.5</v>
+        <v>110.27</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL20" t="n">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AN20" t="n">
-        <v>54.1</v>
+        <v>52.18</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.6</v>
+        <v>5.73</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.9</v>
+        <v>60.64</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>16.45</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.3</v>
+        <v>5.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.2</v>
+        <v>17.91</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
         <v>0.9</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="BR20" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS20" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV20" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="BX20" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
         <v>1.81</v>
@@ -8864,70 +8864,70 @@
         <v>1.81</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="CE20" t="n">
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL20" t="n">
         <v>2.09</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO20" t="n">
         <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW20" t="n">
         <v>1.91</v>
@@ -8948,82 +8948,82 @@
         <v>1.34</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH20" t="n">
-        <v>109.4</v>
+        <v>108.38</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.4</v>
+        <v>4.62</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM20" t="n">
-        <v>51.6</v>
+        <v>50.71</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.05</v>
+        <v>14.95</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>62.25</v>
+        <v>62.05</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>16.95</v>
+        <v>17.14</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.45</v>
+        <v>5.72</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.4</v>
+        <v>16.33</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="EC20" t="n">
         <v>1.9</v>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0.1</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AI21" t="n">
-        <v>83.40000000000001</v>
+        <v>83.45</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.4</v>
+        <v>39.45</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>13.82</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>7.36</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>48.8</v>
+        <v>48.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.1</v>
+        <v>10.91</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.45</v>
+        <v>11.24</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.55</v>
+        <v>4.38</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
       <c r="BR21" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS21" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV21" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY21" t="n">
         <v>2.48</v>
@@ -9267,16 +9267,16 @@
         <v>2.61</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="CD21" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CE21" t="n">
         <v>1.49</v>
@@ -9285,7 +9285,7 @@
         <v>3.3</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
@@ -9294,19 +9294,19 @@
         <v>1.75</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK21" t="n">
         <v>1.63</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
@@ -9315,7 +9315,7 @@
         <v>2.34</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
@@ -9342,13 +9342,13 @@
         <v>2.02</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA21" t="n">
         <v>1.81</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="DC21" t="n">
         <v>2.46</v>
@@ -9360,76 +9360,76 @@
         <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.09999999999999</v>
+        <v>83.14</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DK21" t="n">
-        <v>5.95</v>
+        <v>5.81</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM21" t="n">
-        <v>43.9</v>
+        <v>42.76</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.75</v>
+        <v>16.57</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.1</v>
+        <v>13.05</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.35</v>
+        <v>7.14</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.75</v>
+        <v>46.57</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.9</v>
+        <v>12.71</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.550000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.25</v>
+        <v>20.1</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1541,7 +1541,7 @@
         <v>2.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.73</v>
+        <v>19.82</v>
       </c>
       <c r="BE2" t="n">
         <v>1.1</v>
@@ -1766,7 +1766,7 @@
         <v>3.43</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.86</v>
+        <v>18.91</v>
       </c>
       <c r="EB2" t="n">
         <v>1.14</v>
@@ -5893,7 +5893,7 @@
         <v>4.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.27</v>
+        <v>17.36</v>
       </c>
       <c r="AD13" t="n">
         <v>1.57</v>
@@ -6199,7 +6199,7 @@
         <v>4.48</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.47</v>
+        <v>16.52</v>
       </c>
       <c r="EB13" t="n">
         <v>1.52</v>
@@ -6780,7 +6780,7 @@
         <v>3.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="BE15" t="n">
         <v>1.13</v>
@@ -7005,7 +7005,7 @@
         <v>4.72</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.76</v>
+        <v>18.72</v>
       </c>
       <c r="EB15" t="n">
         <v>1.44</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H3" t="n">
-        <v>79.3</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>36.64</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>16.3</v>
+        <v>15.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>16.27</v>
       </c>
       <c r="R3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.5</v>
+        <v>47.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.1</v>
+        <v>10.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.6</v>
+        <v>7.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.6</v>
+        <v>15.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>1.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1</v>
       </c>
-      <c r="BM3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BP3" t="n">
-        <v>4.57</v>
+        <v>4.73</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="CA3" t="n">
         <v>3.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
         <v>3.8</v>
@@ -2028,22 +2028,22 @@
         <v>1.46</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL3" t="n">
         <v>2.13</v>
@@ -2052,7 +2052,7 @@
         <v>2.2</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
@@ -2061,121 +2061,121 @@
         <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH3" t="n">
-        <v>81.19</v>
+        <v>81.86</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>35.05</v>
+        <v>35.41</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.95</v>
+        <v>14.82</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.91</v>
+        <v>15.09</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.33</v>
+        <v>49.32</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.29</v>
+        <v>10.14</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.52</v>
+        <v>7.45</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.62</v>
+        <v>17.64</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6305,139 +6305,139 @@
         <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>93.90000000000001</v>
+        <v>94.27</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.3</v>
+        <v>47.64</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>18.09</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.8</v>
+        <v>13.55</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.1</v>
+        <v>49.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.1</v>
+        <v>9.73</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.2</v>
+        <v>18.82</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.71</v>
+        <v>4.59</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS14" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU14" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY14" t="n">
         <v>1.78</v>
@@ -6446,16 +6446,16 @@
         <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
@@ -6470,7 +6470,7 @@
         <v>1.36</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.87</v>
@@ -6479,43 +6479,43 @@
         <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY14" t="n">
         <v>1.95</v>
@@ -6530,85 +6530,85 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.29000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.09</v>
+        <v>5.18</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.67</v>
+        <v>46.36</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.57</v>
+        <v>15.72</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.9</v>
+        <v>13.78</v>
       </c>
       <c r="DR14" t="n">
         <v>6.91</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.29</v>
+        <v>48.41</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.95</v>
+        <v>14.28</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.28</v>
+        <v>19.55</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>80.2</v>
+        <v>81.91</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>34.8</v>
+        <v>35.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>13.7</v>
+        <v>13.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.6</v>
+        <v>17.27</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.9</v>
+        <v>17.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.81</v>
+        <v>3.59</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.62</v>
+        <v>5.32</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC2" t="n">
         <v>3.44</v>
@@ -1628,7 +1628,7 @@
         <v>3.11</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CH2" t="n">
         <v>1.32</v>
@@ -1637,7 +1637,7 @@
         <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK2" t="n">
         <v>1.65</v>
@@ -1646,7 +1646,7 @@
         <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN2" t="n">
         <v>1.72</v>
@@ -1658,7 +1658,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,7 +1673,7 @@
         <v>1.37</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW2" t="n">
         <v>1.94</v>
@@ -1682,97 +1682,97 @@
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DG2" t="n">
         <v>2.28</v>
       </c>
-      <c r="DD2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.43</v>
-      </c>
       <c r="DH2" t="n">
-        <v>84.23999999999999</v>
+        <v>84.91</v>
       </c>
       <c r="DI2" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="DK2" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.33</v>
+        <v>35.68</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.67</v>
+        <v>13.46</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.67</v>
+        <v>17.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50</v>
+        <v>49.96</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.05</v>
+        <v>10.09</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.62</v>
+        <v>6.59</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.91</v>
+        <v>18.73</v>
       </c>
       <c r="EB2" t="n">
         <v>1.14</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1824,10 +1824,10 @@
         <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>15.91</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.27</v>
+        <v>16.18</v>
       </c>
       <c r="R3" t="n">
         <v>8.449999999999999</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.64</v>
+        <v>47.73</v>
       </c>
       <c r="Y3" t="n">
         <v>0.09</v>
@@ -2010,7 +2010,7 @@
         <v>2.71</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CA3" t="n">
         <v>3.15</v>
@@ -2136,10 +2136,10 @@
         <v>1.41</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.82</v>
+        <v>14.86</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="DR3" t="n">
         <v>8.27</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.32</v>
+        <v>49.36</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H4" t="n">
-        <v>91.59999999999999</v>
+        <v>85.64</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>35.5</v>
+        <v>35.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>12.4</v>
+        <v>12.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.5</v>
+        <v>15.73</v>
       </c>
       <c r="R4" t="n">
-        <v>8.4</v>
+        <v>8.27</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.5</v>
+        <v>50.27</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.2</v>
+        <v>11.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.9</v>
+        <v>7.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.3</v>
+        <v>16.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>2.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.81</v>
+        <v>9.91</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="CA4" t="n">
         <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CC4" t="n">
         <v>3.76</v>
@@ -2443,16 +2443,16 @@
         <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
         <v>1.65</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN4" t="n">
         <v>1.71</v>
@@ -2464,7 +2464,7 @@
         <v>2.3</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
@@ -2494,91 +2494,91 @@
         <v>2.17</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB4" t="n">
         <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.70999999999999</v>
+        <v>85.86</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.1</v>
+        <v>34.09</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.1</v>
+        <v>14.19</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.76</v>
+        <v>14.46</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.57</v>
+        <v>49.04</v>
       </c>
       <c r="DW4" t="n">
         <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.91</v>
+        <v>11.28</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.76</v>
+        <v>7.28</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.67</v>
+        <v>18.32</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>89.3</v>
+        <v>86.45</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>42.9</v>
+        <v>41.27</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.3</v>
+        <v>13.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.45</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.2</v>
+        <v>47.45</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.9</v>
+        <v>10.55</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.4</v>
+        <v>18.09</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG5" t="n">
         <v>2.86</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.67</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO5" t="n">
         <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV5" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>2.51</v>
@@ -2819,28 +2819,28 @@
         <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.88</v>
+        <v>4.18</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.21</v>
+        <v>4.57</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI5" t="n">
         <v>1.84</v>
@@ -2849,37 +2849,37 @@
         <v>1.89</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN5" t="n">
         <v>1.79</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV5" t="n">
         <v>1.98</v>
@@ -2903,85 +2903,85 @@
         <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.70999999999999</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.43</v>
+        <v>44.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.48</v>
+        <v>13.54</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.05</v>
+        <v>15.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.86</v>
+        <v>8.1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.91</v>
+        <v>49</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.81</v>
+        <v>12.55</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AI6" t="n">
-        <v>85.09999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>39.5</v>
+        <v>42.18</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>17.27</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>54.9</v>
+        <v>55.91</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.2</v>
+        <v>12.09</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="BD6" t="n">
-        <v>12.9</v>
+        <v>13.73</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.52</v>
+        <v>8.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.48</v>
+        <v>4.23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY6" t="n">
         <v>2.45</v>
@@ -3222,25 +3222,25 @@
         <v>2.62</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CE6" t="n">
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
@@ -3264,13 +3264,13 @@
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP6" t="n">
         <v>2.16</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3297,7 +3297,7 @@
         <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA6" t="n">
         <v>1.69</v>
@@ -3309,49 +3309,49 @@
         <v>2.25</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.43000000000001</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.53</v>
+        <v>38.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.1</v>
+        <v>17.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
       <c r="DS6" t="n">
         <v>0.09</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.62</v>
+        <v>54.18</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.81</v>
+        <v>13.18</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.76</v>
+        <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.38</v>
+        <v>15.69</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,16 +3484,16 @@
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
-        <v>92.27</v>
+        <v>94.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3502,121 +3502,121 @@
         <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.45</v>
+        <v>47</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.27</v>
+        <v>15.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.45</v>
+        <v>12.17</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49.36</v>
+        <v>49.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.36</v>
+        <v>7.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>19</v>
+        <v>18.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.19</v>
+        <v>3.95</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.67</v>
+        <v>4.41</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY7" t="n">
         <v>2.09</v>
@@ -3628,13 +3628,13 @@
         <v>3.15</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
@@ -3643,7 +3643,7 @@
         <v>3.16</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3652,13 +3652,13 @@
         <v>1.78</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK7" t="n">
         <v>1.77</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM7" t="n">
         <v>1.96</v>
@@ -3673,7 +3673,7 @@
         <v>2.27</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3691,7 +3691,7 @@
         <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX7" t="n">
         <v>1.79</v>
@@ -3700,7 +3700,7 @@
         <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DA7" t="n">
         <v>1.62</v>
@@ -3712,19 +3712,19 @@
         <v>2.33</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.14</v>
+        <v>95.27</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
@@ -3733,55 +3733,55 @@
         <v>2.14</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.57</v>
+        <v>50.68</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.33</v>
+        <v>14.32</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.09</v>
+        <v>11</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.76</v>
+        <v>49.82</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.52</v>
+        <v>12.45</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.52</v>
+        <v>8.41</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.57</v>
+        <v>18.27</v>
       </c>
       <c r="EB7" t="n">
         <v>1.44</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>82.36</v>
+        <v>81.67</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>40.09</v>
+        <v>39.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="P8" t="n">
-        <v>15.36</v>
+        <v>14.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.18</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>7.82</v>
+        <v>8.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>47.73</v>
+        <v>47.58</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.18</v>
+        <v>11.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.36</v>
+        <v>20.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,67 +3968,67 @@
         <v>2.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.48</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.05</v>
       </c>
-      <c r="BM8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.95</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CB8" t="n">
         <v>3.06</v>
@@ -4040,7 +4040,7 @@
         <v>3.58</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
         <v>3.15</v>
@@ -4058,16 +4058,16 @@
         <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL8" t="n">
         <v>2.12</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.39</v>
@@ -4076,7 +4076,7 @@
         <v>2.25</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4091,19 +4091,19 @@
         <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW8" t="n">
         <v>1.93</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA8" t="n">
         <v>1.77</v>
@@ -4112,85 +4112,85 @@
         <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>82.28</v>
+        <v>81.91</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.81</v>
+        <v>39.68</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.38</v>
+        <v>15.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.76</v>
+        <v>7.91</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.81</v>
+        <v>10.73</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.71</v>
+        <v>19.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.73</v>
+        <v>78.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.27</v>
+        <v>4.58</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.73</v>
+        <v>41.33</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.55</v>
+        <v>18.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.91</v>
+        <v>15.17</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.27</v>
+        <v>47.33</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.27</v>
+        <v>14.92</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.67</v>
+        <v>9.73</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.25</v>
@@ -4431,16 +4431,16 @@
         <v>2.36</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -4449,7 +4449,7 @@
         <v>2.92</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH9" t="n">
         <v>1.37</v>
@@ -4473,13 +4473,13 @@
         <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
@@ -4506,7 +4506,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
         <v>1.84</v>
@@ -4521,46 +4521,46 @@
         <v>3.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.72</v>
+        <v>82.77</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.05</v>
+        <v>5.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.24</v>
+        <v>42.95</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.91</v>
+        <v>17.05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.33</v>
+        <v>15.46</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.050000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DS9" t="n">
         <v>0.09</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.05</v>
+        <v>48.54</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.05</v>
+        <v>15.82</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.67</v>
+        <v>10.54</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.95</v>
+        <v>17.86</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.09</v>
@@ -4693,130 +4693,130 @@
         <v>2.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>90.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.5</v>
+        <v>35.55</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.1</v>
+        <v>16.64</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.4</v>
+        <v>12.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.7</v>
+        <v>6.45</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.8</v>
+        <v>52.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA10" t="n">
         <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.6</v>
+        <v>7.45</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.3</v>
+        <v>19.27</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="BG10" t="n">
         <v>2.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.52</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="BR10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS10" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT10" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY10" t="n">
         <v>2.35</v>
@@ -4834,16 +4834,16 @@
         <v>2.45</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB10" t="n">
         <v>3.09</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="CE10" t="n">
         <v>1.51</v>
@@ -4852,13 +4852,13 @@
         <v>3.24</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CH10" t="n">
         <v>1.29</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.99</v>
@@ -4867,7 +4867,7 @@
         <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CM10" t="n">
         <v>2.13</v>
@@ -4882,7 +4882,7 @@
         <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="CR10" t="n">
         <v>1.52</v>
@@ -4897,7 +4897,7 @@
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW10" t="n">
         <v>2.02</v>
@@ -4909,94 +4909,94 @@
         <v>2.13</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="DH10" t="n">
-        <v>92.09</v>
+        <v>91.09</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.19</v>
+        <v>39.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.86</v>
+        <v>16.64</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.86</v>
+        <v>13.91</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.52</v>
+        <v>6.41</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.62</v>
+        <v>53.91</v>
       </c>
       <c r="DW10" t="n">
         <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.14</v>
+        <v>12.09</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.28</v>
+        <v>20.22</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.5</v>
+        <v>39.91</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.2</v>
+        <v>18.73</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.3</v>
+        <v>54.36</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>12.18</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.4</v>
+        <v>16.64</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.76</v>
+        <v>5.59</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY11" t="n">
         <v>2.81</v>
@@ -5243,10 +5243,10 @@
         <v>3.41</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.24</v>
+        <v>4.12</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.78</v>
+        <v>4.69</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5258,148 +5258,148 @@
         <v>2.79</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.43000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.9</v>
+        <v>42.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.29</v>
+        <v>13.41</v>
       </c>
       <c r="DQ11" t="n">
-        <v>17.81</v>
+        <v>18.09</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.14</v>
+        <v>7.18</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.24</v>
+        <v>58.59</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.43</v>
+        <v>14.41</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.86</v>
+        <v>16.95</v>
       </c>
       <c r="EB11" t="n">
         <v>1.58</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>105</v>
+        <v>106.18</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL12" t="n">
-        <v>7.6</v>
+        <v>7.27</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.1</v>
+        <v>58.09</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.1</v>
+        <v>13.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>53</v>
+        <v>53.09</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>19.1</v>
+        <v>18.55</v>
       </c>
       <c r="BB12" t="n">
-        <v>14.2</v>
+        <v>13.82</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.4</v>
+        <v>18.09</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.67</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="BR12" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY12" t="n">
         <v>1.99</v>
@@ -5643,13 +5643,13 @@
         <v>3.24</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
@@ -5667,28 +5667,28 @@
         <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
         <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
@@ -5706,100 +5706,100 @@
         <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB12" t="n">
         <v>1.39</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="DH12" t="n">
-        <v>101.57</v>
+        <v>102.32</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.57</v>
+        <v>57.59</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.19</v>
+        <v>15.09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.48</v>
+        <v>14.28</v>
       </c>
       <c r="DR12" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="DZ12" t="n">
         <v>4.86</v>
       </c>
-      <c r="DS12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>52</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX12" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="DY12" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="DZ12" t="n">
-        <v>4.95</v>
-      </c>
       <c r="EA12" t="n">
-        <v>19.43</v>
+        <v>19.22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.18</v>
@@ -5902,52 +5902,52 @@
         <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.90000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.7</v>
+        <v>39.82</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16.3</v>
+        <v>15.64</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>13.27</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>50.7</v>
+        <v>51.73</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>14.45</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.6</v>
+        <v>16.18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.24</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>1.7</v>
@@ -6049,10 +6049,10 @@
         <v>3.46</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="CE13" t="n">
         <v>1.45</v>
@@ -6061,7 +6061,7 @@
         <v>3.1</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -6070,19 +6070,19 @@
         <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
         <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CM13" t="n">
         <v>2.1</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO13" t="n">
         <v>1.37</v>
@@ -6112,16 +6112,16 @@
         <v>2.03</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
@@ -6133,46 +6133,46 @@
         <v>4.11</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.29000000000001</v>
+        <v>95.72</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.67</v>
+        <v>5.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.62</v>
+        <v>46.36</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.05</v>
+        <v>14.78</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.05</v>
+        <v>14.14</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.14</v>
+        <v>6.22</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.24</v>
+        <v>53.64</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.81</v>
+        <v>14.04</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.33</v>
+        <v>9.41</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.48</v>
+        <v>4.64</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.52</v>
+        <v>16.77</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="14">
@@ -6338,10 +6338,10 @@
         <v>2.73</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18.09</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.55</v>
+        <v>13.64</v>
       </c>
       <c r="AS14" t="n">
         <v>8.09</v>
@@ -6362,16 +6362,16 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>13</v>
+        <v>13.09</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.73</v>
+        <v>9.82</v>
       </c>
       <c r="BC14" t="n">
         <v>3.27</v>
@@ -6455,7 +6455,7 @@
         <v>2.39</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
@@ -6569,10 +6569,10 @@
         <v>2.82</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.72</v>
+        <v>15.68</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.78</v>
+        <v>13.82</v>
       </c>
       <c r="DR14" t="n">
         <v>6.91</v>
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.41</v>
+        <v>48.36</v>
       </c>
       <c r="DW14" t="n">
         <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.28</v>
+        <v>14.32</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.41</v>
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="H15" t="n">
-        <v>85.55</v>
+        <v>84.42</v>
       </c>
       <c r="I15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="K15" t="n">
-        <v>6.55</v>
+        <v>6.33</v>
       </c>
       <c r="L15" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="M15" t="n">
-        <v>38.45</v>
+        <v>37.67</v>
       </c>
       <c r="N15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>14.45</v>
+        <v>15.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.18</v>
+        <v>16.25</v>
       </c>
       <c r="R15" t="n">
-        <v>6.82</v>
+        <v>6.67</v>
       </c>
       <c r="S15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.09</v>
+        <v>50.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.64</v>
+        <v>16.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.91</v>
+        <v>10.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.73</v>
+        <v>19.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6789,70 +6789,70 @@
         <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.67</v>
+        <v>11.59</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
         <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.71</v>
+        <v>5.55</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC15" t="n">
         <v>4.97</v>
@@ -6861,10 +6861,10 @@
         <v>5.82</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG15" t="n">
         <v>2.77</v>
@@ -6873,10 +6873,10 @@
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK15" t="n">
         <v>1.57</v>
@@ -6885,7 +6885,7 @@
         <v>2.09</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN15" t="n">
         <v>1.81</v>
@@ -6894,91 +6894,91 @@
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="DH15" t="n">
-        <v>79</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.57</v>
+        <v>34.32</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.57</v>
+        <v>15.04</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.24</v>
+        <v>15.32</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.14</v>
+        <v>7.05</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.52</v>
+        <v>48.82</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.24</v>
+        <v>14.14</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.72</v>
+        <v>18.64</v>
       </c>
       <c r="EB15" t="n">
         <v>1.44</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>81.59999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M16" t="n">
-        <v>40.4</v>
+        <v>39.64</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
-        <v>13.6</v>
+        <v>13.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.8</v>
+        <v>13.64</v>
       </c>
       <c r="R16" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.4</v>
+        <v>44.91</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.2</v>
+        <v>15.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.710000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="BZ16" t="n">
         <v>3.73</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
         <v>4.49</v>
@@ -7270,7 +7270,7 @@
         <v>3.07</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
@@ -7285,7 +7285,7 @@
         <v>1.66</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CM16" t="n">
         <v>2.14</v>
@@ -7294,13 +7294,13 @@
         <v>1.69</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
@@ -7309,7 +7309,7 @@
         <v>3.21</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7318,100 +7318,100 @@
         <v>1.92</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX16" t="n">
         <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA16" t="n">
         <v>1.75</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>78.09999999999999</v>
+        <v>77.77</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.24</v>
+        <v>35.1</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.05</v>
+        <v>15.04</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.57</v>
+        <v>14.46</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.91</v>
+        <v>43.73</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="DY16" t="n">
         <v>7.09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.43</v>
+        <v>16.55</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
         <v>2.09</v>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H17" t="n">
-        <v>101.6</v>
+        <v>101.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>45.6</v>
+        <v>45.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P17" t="n">
-        <v>17.9</v>
+        <v>17.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>16.9</v>
+        <v>17.45</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.3</v>
+        <v>50.82</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.5</v>
+        <v>14.09</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AC17" t="n">
         <v>17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.48</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>4.91</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="BZ17" t="n">
         <v>2.29</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CC17" t="n">
         <v>3.42</v>
@@ -7667,52 +7667,52 @@
         <v>3.83</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF17" t="n">
         <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK17" t="n">
         <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM17" t="n">
         <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO17" t="n">
         <v>1.41</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7736,88 +7736,88 @@
         <v>1.64</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.70999999999999</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.81</v>
+        <v>44.77</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.9</v>
+        <v>16.78</v>
       </c>
       <c r="DQ17" t="n">
-        <v>15.62</v>
+        <v>15.95</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.14</v>
+        <v>50.41</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.81</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.86</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.86</v>
+        <v>18.78</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.18</v>
@@ -7917,139 +7917,139 @@
         <v>2.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>87.8</v>
+        <v>86.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.1</v>
+        <v>5.64</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.4</v>
+        <v>39.09</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AP18" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.9</v>
+        <v>16.55</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>16.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45.2</v>
+        <v>45.09</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>11.45</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.2</v>
+        <v>18.64</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
         <v>1.14</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.62</v>
+        <v>5.82</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS18" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
         <v>2.1</v>
@@ -8058,25 +8058,25 @@
         <v>2.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH18" t="n">
         <v>1.32</v>
@@ -8085,13 +8085,13 @@
         <v>1.79</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK18" t="n">
         <v>1.6</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM18" t="n">
         <v>2.21</v>
@@ -8103,16 +8103,16 @@
         <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT18" t="n">
         <v>2.71</v>
@@ -8127,100 +8127,100 @@
         <v>1.99</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA18" t="n">
         <v>1.8</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DO18" t="n">
         <v>2.32</v>
       </c>
-      <c r="DD18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>90.91</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>2.24</v>
-      </c>
       <c r="DP18" t="n">
-        <v>15.76</v>
+        <v>16.1</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.71</v>
+        <v>16.59</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.76</v>
+        <v>46.64</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.76</v>
+        <v>6.82</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.76</v>
+        <v>17.55</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="H19" t="n">
-        <v>100.7</v>
+        <v>97.91</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>4.73</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="M19" t="n">
-        <v>64.5</v>
+        <v>62.91</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P19" t="n">
-        <v>14.9</v>
+        <v>14.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.6</v>
+        <v>14.09</v>
       </c>
       <c r="R19" t="n">
-        <v>8.5</v>
+        <v>9.27</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>40.2</v>
+        <v>39.64</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>14.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>10.36</v>
       </c>
       <c r="AB19" t="n">
         <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>25.4</v>
+        <v>24.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.19</v>
+        <v>3.95</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.14</v>
+        <v>3.91</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT19" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU19" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,16 +8452,16 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB19" t="n">
         <v>3.19</v>
@@ -8479,7 +8479,7 @@
         <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH19" t="n">
         <v>1.32</v>
@@ -8488,19 +8488,19 @@
         <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL19" t="n">
         <v>2.24</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
@@ -8524,73 +8524,73 @@
         <v>1.35</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW19" t="n">
         <v>1.97</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="DH19" t="n">
-        <v>97.28</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.38</v>
+        <v>4.23</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>56.81</v>
+        <v>56.36</v>
       </c>
       <c r="DN19" t="n">
         <v>0.91</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.34</v>
+        <v>17.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.95</v>
+        <v>13.72</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>38.34</v>
+        <v>38.14</v>
       </c>
       <c r="DW19" t="n">
         <v>0.14</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.52</v>
+        <v>12.31</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.859999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="EA19" t="n">
-        <v>24.24</v>
+        <v>23.96</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H20" t="n">
-        <v>106.3</v>
+        <v>108.64</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>49.1</v>
+        <v>51.36</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>15.8</v>
+        <v>16.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.4</v>
+        <v>16.27</v>
       </c>
       <c r="R20" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>63.6</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.9</v>
+        <v>17.82</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.6</v>
+        <v>14.73</v>
       </c>
       <c r="AD20" t="n">
         <v>1.88</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
         <v>0.09</v>
@@ -8813,61 +8813,61 @@
         <v>2.86</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="BR20" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS20" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT20" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU20" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV20" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CC20" t="n">
         <v>2.19</v>
@@ -8876,16 +8876,16 @@
         <v>2.27</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI20" t="n">
         <v>1.86</v>
@@ -8897,40 +8897,40 @@
         <v>1.56</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN20" t="n">
         <v>1.79</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="CR20" t="n">
         <v>1.42</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CV20" t="n">
         <v>1.96</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX20" t="n">
         <v>1.61</v>
@@ -8945,88 +8945,88 @@
         <v>1.8</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG20" t="n">
         <v>2.05</v>
       </c>
       <c r="DH20" t="n">
-        <v>108.38</v>
+        <v>109.46</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ20" t="n">
         <v>2.19</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM20" t="n">
-        <v>50.71</v>
+        <v>51.77</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP20" t="n">
-        <v>15</v>
+        <v>15.18</v>
       </c>
       <c r="DQ20" t="n">
-        <v>14.95</v>
+        <v>14.96</v>
       </c>
       <c r="DR20" t="n">
         <v>6</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>62.05</v>
+        <v>62.41</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX20" t="n">
         <v>17.14</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.43</v>
+        <v>11.46</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.33</v>
+        <v>16.32</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="H21" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K21" t="n">
-        <v>6.8</v>
+        <v>6.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M21" t="n">
-        <v>46.4</v>
+        <v>46.18</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="P21" t="n">
-        <v>16.1</v>
+        <v>16.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.2</v>
+        <v>12.91</v>
       </c>
       <c r="R21" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44.7</v>
+        <v>44.36</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.7</v>
+        <v>14.82</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.3</v>
+        <v>10.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.7</v>
+        <v>21.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,64 +9207,64 @@
         <v>2.09</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.24</v>
+        <v>11.23</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL21" t="n">
         <v>0.95</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.76</v>
+        <v>6.73</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS21" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV21" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CA21" t="n">
         <v>3.11</v>
@@ -9282,7 +9282,7 @@
         <v>1.49</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CG21" t="n">
         <v>2.5</v>
@@ -9291,19 +9291,19 @@
         <v>1.3</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN21" t="n">
         <v>1.73</v>
@@ -9312,28 +9312,28 @@
         <v>1.41</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX21" t="n">
         <v>1.62</v>
@@ -9342,94 +9342,94 @@
         <v>2.02</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA21" t="n">
         <v>1.81</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.14</v>
+        <v>82.72</v>
       </c>
       <c r="DI21" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DK21" t="n">
-        <v>5.81</v>
+        <v>5.68</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.76</v>
+        <v>42.82</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.57</v>
+        <v>16.64</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.05</v>
+        <v>13.36</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.14</v>
+        <v>7.18</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.57</v>
+        <v>46.32</v>
       </c>
       <c r="DW21" t="n">
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.71</v>
+        <v>12.87</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.1</v>
+        <v>20.23</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.27</v>
+        <v>50.36</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.04</v>
+        <v>49.09</v>
       </c>
       <c r="DW4" t="n">
         <v>0.09</v>
@@ -3165,7 +3165,7 @@
         <v>2.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.32</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI6" t="n">
         <v>2.45</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.33</v>
+        <v>47.25</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.17</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.54</v>
+        <v>48.5</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
@@ -5159,19 +5159,19 @@
         <v>0.09</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.18</v>
+        <v>12.27</v>
       </c>
       <c r="BB11" t="n">
         <v>7.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.36</v>
+        <v>4.45</v>
       </c>
       <c r="BD11" t="n">
         <v>16.64</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BF11" t="n">
         <v>2.27</v>
@@ -5384,19 +5384,19 @@
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.41</v>
+        <v>14.46</v>
       </c>
       <c r="DY11" t="n">
         <v>9.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="EA11" t="n">
         <v>16.95</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC11" t="n">
         <v>2.31</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51.73</v>
+        <v>51.64</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.64</v>
+        <v>53.6</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
@@ -6663,10 +6663,10 @@
         <v>15.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.25</v>
+        <v>16.17</v>
       </c>
       <c r="R15" t="n">
-        <v>6.67</v>
+        <v>6.75</v>
       </c>
       <c r="S15" t="n">
         <v>1.58</v>
@@ -6975,10 +6975,10 @@
         <v>15.04</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.32</v>
+        <v>15.27</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>2.73</v>
       </c>
       <c r="K19" t="n">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="L19" t="n">
         <v>0.18</v>
@@ -8404,7 +8404,7 @@
         <v>2.14</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="BI19" t="n">
         <v>2.14</v>
@@ -8569,7 +8569,7 @@
         <v>2.54</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.23</v>
+        <v>4.28</v>
       </c>
       <c r="DL19" t="n">
         <v>0.32</v>
@@ -9102,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44.36</v>
+        <v>44.45</v>
       </c>
       <c r="Y21" t="n">
         <v>0.09</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.32</v>
+        <v>46.36</v>
       </c>
       <c r="DW21" t="n">
         <v>0.09</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,52 +1872,52 @@
         <v>2.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>82.91</v>
+        <v>80.08</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>34.18</v>
+        <v>32.17</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.73</v>
+        <v>14.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.91</v>
+        <v>14.42</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.09</v>
+        <v>8.17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51</v>
+        <v>49.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.45</v>
+        <v>6.92</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.45</v>
+        <v>18.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.949999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
         <v>2.71</v>
@@ -2019,25 +2019,25 @@
         <v>3.17</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.92</v>
@@ -2049,7 +2049,7 @@
         <v>2.13</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN3" t="n">
         <v>1.74</v>
@@ -2058,25 +2058,25 @@
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
         <v>1.95</v>
@@ -2085,34 +2085,34 @@
         <v>1.65</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DH3" t="n">
-        <v>81.86</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
@@ -2121,28 +2121,28 @@
         <v>2.13</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DM3" t="n">
-        <v>35.41</v>
+        <v>34.31</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.86</v>
+        <v>15.26</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.04</v>
+        <v>15.26</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.14</v>
+        <v>9.83</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.45</v>
+        <v>7.17</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.64</v>
+        <v>17.26</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="EC3" t="n">
         <v>2</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.09</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.09</v>
+        <v>84.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.82</v>
+        <v>31.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.64</v>
+        <v>15.17</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.18</v>
+        <v>14.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.73</v>
+        <v>9.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.82</v>
+        <v>48.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.64</v>
+        <v>10.42</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.64</v>
+        <v>6.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.91</v>
+        <v>20.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.91</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="BO4" t="n">
         <v>1.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU4" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY4" t="n">
         <v>3.04</v>
@@ -2416,16 +2416,16 @@
         <v>3.4</v>
       </c>
       <c r="CA4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CB4" t="n">
         <v>3.15</v>
       </c>
-      <c r="CB4" t="n">
-        <v>3.14</v>
-      </c>
       <c r="CC4" t="n">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.23</v>
+        <v>4.35</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
@@ -2434,13 +2434,13 @@
         <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH4" t="n">
         <v>1.3</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.98</v>
@@ -2455,7 +2455,7 @@
         <v>2.15</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO4" t="n">
         <v>1.41</v>
@@ -2470,19 +2470,19 @@
         <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CT4" t="n">
         <v>2.67</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
@@ -2497,88 +2497,88 @@
         <v>1.73</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0.04</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.86</v>
+        <v>85.05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DK4" t="n">
         <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.09</v>
+        <v>33.43</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.19</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.46</v>
+        <v>14.87</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.09</v>
+        <v>49.26</v>
       </c>
       <c r="DW4" t="n">
         <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.28</v>
+        <v>11.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.28</v>
+        <v>7.04</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.32</v>
+        <v>18.92</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>88.18000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K5" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>47.73</v>
+        <v>45.83</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>13.64</v>
+        <v>12.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="R5" t="n">
-        <v>8.640000000000001</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.55</v>
+        <v>51.58</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.55</v>
+        <v>14.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.73</v>
+        <v>18.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF5" t="n">
         <v>0.18</v>
@@ -2759,70 +2759,70 @@
         <v>2.64</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.09</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="BR5" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT5" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC5" t="n">
         <v>4.18</v>
@@ -2831,19 +2831,19 @@
         <v>4.57</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
         <v>2.99</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.89</v>
@@ -2855,7 +2855,7 @@
         <v>2.11</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN5" t="n">
         <v>1.79</v>
@@ -2864,16 +2864,16 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
         <v>2.86</v>
@@ -2888,100 +2888,100 @@
         <v>1.89</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY5" t="n">
         <v>2.01</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
         <v>2.18</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="DE5" t="n">
         <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.31999999999999</v>
+        <v>86</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.5</v>
+        <v>43.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.54</v>
+        <v>13.13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.22</v>
+        <v>15.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.1</v>
+        <v>8.31</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.55</v>
+        <v>12.65</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.41</v>
+        <v>8.48</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>81.91</v>
+        <v>79.92</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>35.73</v>
+        <v>34.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="O6" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="P6" t="n">
-        <v>11.73</v>
+        <v>11.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.64</v>
+        <v>18.75</v>
       </c>
       <c r="R6" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.45</v>
+        <v>52.83</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.27</v>
+        <v>14.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.64</v>
+        <v>17.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AF6" t="n">
         <v>0.27</v>
@@ -3162,70 +3162,70 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.359999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.23</v>
+        <v>4.43</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BR6" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX6" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CC6" t="n">
         <v>3.95</v>
@@ -3249,28 +3249,28 @@
         <v>1.85</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK6" t="n">
         <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP6" t="n">
         <v>2.16</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3294,97 +3294,97 @@
         <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.12</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.81999999999999</v>
+        <v>83.66</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.23</v>
+        <v>4.13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.96</v>
+        <v>38.04</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.86</v>
+        <v>11.7</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.95</v>
+        <v>18.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.64</v>
+        <v>7.74</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.18</v>
+        <v>54.3</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.18</v>
+        <v>13.22</v>
       </c>
       <c r="DY6" t="n">
         <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.69</v>
+        <v>15.7</v>
       </c>
       <c r="EB6" t="n">
         <v>1.33</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>96.2</v>
+        <v>94.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="K7" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>55.1</v>
+        <v>53</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>13.3</v>
+        <v>13.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>6.6</v>
+        <v>6.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.2</v>
+        <v>48.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.1</v>
+        <v>17.91</v>
       </c>
       <c r="AD7" t="n">
         <v>1.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.949999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.41</v>
+        <v>4.52</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CC7" t="n">
         <v>2.86</v>
@@ -3637,43 +3637,43 @@
         <v>3.1</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.94</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3688,7 +3688,7 @@
         <v>1.35</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW7" t="n">
         <v>1.96</v>
@@ -3709,85 +3709,85 @@
         <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.27</v>
+        <v>94.39</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.68</v>
+        <v>49.87</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.32</v>
+        <v>14.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11</v>
+        <v>10.96</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.36</v>
+        <v>7.48</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.82</v>
+        <v>49.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.45</v>
+        <v>12.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.41</v>
+        <v>8.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.27</v>
+        <v>18.18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>1.92</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.2</v>
+        <v>80.27</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.5</v>
+        <v>39.73</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.4</v>
+        <v>14.91</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.9</v>
+        <v>14.36</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.4</v>
+        <v>46</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.3</v>
+        <v>6.55</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.9</v>
+        <v>17.73</v>
       </c>
       <c r="BE8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.09</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY8" t="n">
         <v>2.59</v>
@@ -4028,25 +4028,25 @@
         <v>2.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4064,100 +4064,100 @@
         <v>2.12</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW8" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>1.93</v>
       </c>
       <c r="CX8" t="n">
         <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB8" t="n">
         <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DH8" t="n">
-        <v>81.91</v>
+        <v>81</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.68</v>
+        <v>39.78</v>
       </c>
       <c r="DN8" t="n">
         <v>0.91</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.14</v>
+        <v>14.92</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.5</v>
+        <v>14.69</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.91</v>
+        <v>7.74</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.04</v>
+        <v>46.82</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.73</v>
+        <v>11</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.5</v>
+        <v>19.35</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="H9" t="n">
-        <v>88.2</v>
+        <v>85.91</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>44.9</v>
+        <v>45.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>15.1</v>
+        <v>15.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.8</v>
+        <v>15.73</v>
       </c>
       <c r="R9" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50</v>
+        <v>49.36</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.9</v>
+        <v>17.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.8</v>
+        <v>19.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
         <v>0.25</v>
@@ -4371,70 +4371,70 @@
         <v>2.92</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.73</v>
+        <v>9.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.64</v>
+        <v>4.39</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC9" t="n">
         <v>3.11</v>
@@ -4446,25 +4446,25 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK9" t="n">
         <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
         <v>2.24</v>
@@ -4476,28 +4476,28 @@
         <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX9" t="n">
         <v>1.6</v>
@@ -4509,91 +4509,91 @@
         <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.77</v>
+        <v>81.91</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.95</v>
+        <v>43.3</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="DP9" t="n">
-        <v>17.05</v>
+        <v>17.09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.46</v>
+        <v>15.44</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.5</v>
+        <v>48.26</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.82</v>
+        <v>16</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.54</v>
+        <v>10.48</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.27</v>
+        <v>5.52</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.86</v>
+        <v>18.21</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="H10" t="n">
-        <v>93.18000000000001</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="K10" t="n">
-        <v>5.45</v>
+        <v>5.08</v>
       </c>
       <c r="L10" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M10" t="n">
-        <v>42.55</v>
+        <v>40.83</v>
       </c>
       <c r="N10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>16.64</v>
+        <v>16.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.18</v>
+        <v>14.83</v>
       </c>
       <c r="R10" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.27</v>
+        <v>54.58</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.18</v>
+        <v>21.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0.18</v>
@@ -4774,70 +4774,70 @@
         <v>2.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="BR10" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT10" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="CA10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CB10" t="n">
         <v>3.1</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
         <v>3.15</v>
@@ -4861,7 +4861,7 @@
         <v>1.74</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK10" t="n">
         <v>1.66</v>
@@ -4882,13 +4882,13 @@
         <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="CR10" t="n">
         <v>1.52</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CT10" t="n">
         <v>2.63</v>
@@ -4900,7 +4900,7 @@
         <v>1.84</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX10" t="n">
         <v>1.7</v>
@@ -4921,82 +4921,82 @@
         <v>2.42</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="DE10" t="n">
         <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.09</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.68</v>
+        <v>4.52</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.05</v>
+        <v>38.3</v>
       </c>
       <c r="DN10" t="n">
         <v>0.87</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.64</v>
+        <v>16.7</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.91</v>
+        <v>13.78</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="DS10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="DW10" t="n">
         <v>0.13</v>
       </c>
-      <c r="DT10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>53.91</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DX10" t="n">
-        <v>12.09</v>
+        <v>12.13</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.18</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.22</v>
+        <v>20.65</v>
       </c>
       <c r="EB10" t="n">
         <v>1.32</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="H11" t="n">
-        <v>91.64</v>
+        <v>91.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="L11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>47.58</v>
       </c>
       <c r="N11" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="O11" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P11" t="n">
-        <v>12.82</v>
+        <v>13.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>17.45</v>
+        <v>18.33</v>
       </c>
       <c r="R11" t="n">
-        <v>6.64</v>
+        <v>6.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.82</v>
+        <v>62.92</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.64</v>
+        <v>16.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.82</v>
+        <v>10.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.27</v>
+        <v>17.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.36</v>
+        <v>10.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.59</v>
+        <v>5.57</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="CA11" t="n">
         <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC11" t="n">
         <v>4.12</v>
@@ -5249,16 +5249,16 @@
         <v>4.69</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF11" t="n">
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI11" t="n">
         <v>1.94</v>
@@ -5270,19 +5270,19 @@
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
         <v>3.32</v>
@@ -5291,10 +5291,10 @@
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CU11" t="n">
         <v>1.43</v>
@@ -5306,16 +5306,16 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
@@ -5330,76 +5330,76 @@
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.81999999999999</v>
+        <v>89.91</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.96</v>
+        <v>43.91</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.41</v>
+        <v>13.61</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.09</v>
+        <v>18.52</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.18</v>
+        <v>6.96</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>58.59</v>
+        <v>58.83</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.46</v>
+        <v>14.52</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.95</v>
+        <v>17.31</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5424,79 +5424,79 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H12" t="n">
-        <v>98.45</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M12" t="n">
-        <v>57.09</v>
+        <v>55.92</v>
       </c>
       <c r="N12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P12" t="n">
-        <v>14.36</v>
+        <v>14.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.82</v>
+        <v>15.08</v>
       </c>
       <c r="R12" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="S12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="V12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.09</v>
+        <v>51.42</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.82</v>
+        <v>15.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.82</v>
+        <v>10.17</v>
       </c>
       <c r="AB12" t="n">
         <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.36</v>
+        <v>20.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.18</v>
@@ -5580,49 +5580,49 @@
         <v>2.45</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,16 +5631,16 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB12" t="n">
         <v>3.24</v>
@@ -5658,22 +5658,22 @@
         <v>3.09</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK12" t="n">
         <v>1.67</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CM12" t="n">
         <v>2.11</v>
@@ -5682,19 +5682,19 @@
         <v>1.69</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP12" t="n">
         <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT12" t="n">
         <v>2.76</v>
@@ -5706,13 +5706,13 @@
         <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.15</v>
@@ -5733,76 +5733,76 @@
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DH12" t="n">
-        <v>102.32</v>
+        <v>101.91</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.59</v>
+        <v>56.96</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.09</v>
+        <v>15.26</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.28</v>
+        <v>14.43</v>
       </c>
       <c r="DR12" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.09</v>
+        <v>52.22</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.82</v>
+        <v>11.92</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.22</v>
+        <v>19.31</v>
       </c>
       <c r="EB12" t="n">
         <v>1.81</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>92.73</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="K14" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M14" t="n">
-        <v>45.09</v>
+        <v>44.83</v>
       </c>
       <c r="N14" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>13.36</v>
+        <v>13.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="R14" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="S14" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.55</v>
+        <v>48.42</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.55</v>
+        <v>15.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.27</v>
+        <v>20.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF14" t="n">
         <v>0.27</v>
@@ -6386,70 +6386,70 @@
         <v>2.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.640000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CC14" t="n">
         <v>2.39</v>
@@ -6461,7 +6461,7 @@
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG14" t="n">
         <v>2.69</v>
@@ -6473,7 +6473,7 @@
         <v>1.85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK14" t="n">
         <v>1.52</v>
@@ -6482,7 +6482,7 @@
         <v>2.02</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
@@ -6491,10 +6491,10 @@
         <v>1.33</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6509,10 +6509,10 @@
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX14" t="n">
         <v>1.55</v>
@@ -6533,82 +6533,82 @@
         <v>2.13</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.5</v>
+        <v>93.09</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.36</v>
+        <v>46.17</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.68</v>
+        <v>15.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.82</v>
+        <v>13.87</v>
       </c>
       <c r="DR14" t="n">
         <v>6.91</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.36</v>
+        <v>48.78</v>
       </c>
       <c r="DW14" t="n">
         <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.32</v>
+        <v>14.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.55</v>
+        <v>19.79</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6708,52 +6708,52 @@
         <v>1.42</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>71.8</v>
+        <v>74.64</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>30.3</v>
+        <v>33.18</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.7</v>
+        <v>14.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.2</v>
+        <v>14.27</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.8</v>
+        <v>48.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.6</v>
+        <v>12.36</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>8.73</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.6</v>
+        <v>17.64</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.59</v>
+        <v>11.57</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP15" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.55</v>
+        <v>5.61</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU15" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY15" t="n">
         <v>3.43</v>
@@ -6855,19 +6855,19 @@
         <v>3.62</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.97</v>
+        <v>4.95</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="CE15" t="n">
         <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
@@ -6876,28 +6876,28 @@
         <v>1.86</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6915,7 +6915,7 @@
         <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.61</v>
@@ -6933,52 +6933,52 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="DH15" t="n">
-        <v>78.68000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.32</v>
+        <v>35.52</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.04</v>
+        <v>14.87</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.27</v>
+        <v>15.26</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.82</v>
+        <v>49.48</v>
       </c>
       <c r="DW15" t="n">
         <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.14</v>
+        <v>14.39</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.460000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.64</v>
+        <v>18.61</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" t="n">
-        <v>74.91</v>
+        <v>74.08</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.27</v>
+        <v>3.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.55</v>
+        <v>30.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.27</v>
+        <v>14.92</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.45</v>
+        <v>10.58</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.55</v>
+        <v>42.58</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.09</v>
+        <v>9.58</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.55</v>
+        <v>17.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.68</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY16" t="n">
         <v>3.36</v>
@@ -7255,19 +7255,19 @@
         <v>3.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="CE16" t="n">
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG16" t="n">
         <v>2.62</v>
@@ -7285,10 +7285,10 @@
         <v>1.66</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN16" t="n">
         <v>1.69</v>
@@ -7297,10 +7297,10 @@
         <v>1.36</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CR16" t="n">
         <v>1.46</v>
@@ -7330,58 +7330,58 @@
         <v>2.2</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DO16" t="n">
         <v>2</v>
       </c>
-      <c r="DH16" t="n">
-        <v>77.77</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.68</v>
-      </c>
       <c r="DP16" t="n">
-        <v>15.04</v>
+        <v>15.13</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.46</v>
+        <v>14.31</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.04</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.73</v>
+        <v>43.69</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.87</v>
+        <v>11.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.55</v>
+        <v>16.7</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.18000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.09</v>
+        <v>42.58</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.45</v>
+        <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50</v>
+        <v>49.58</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.91</v>
+        <v>12.58</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.27</v>
+        <v>8.92</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.55</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.859999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY17" t="n">
         <v>2.19</v>
@@ -7661,10 +7661,10 @@
         <v>3.11</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="CE17" t="n">
         <v>1.48</v>
@@ -7673,7 +7673,7 @@
         <v>3.23</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7688,13 +7688,13 @@
         <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM17" t="n">
         <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO17" t="n">
         <v>1.41</v>
@@ -7703,7 +7703,7 @@
         <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7712,7 +7712,7 @@
         <v>3.32</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CU17" t="n">
         <v>1.35</v>
@@ -7727,7 +7727,7 @@
         <v>1.76</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.06</v>
@@ -7742,82 +7742,82 @@
         <v>2.4</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.68000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.91</v>
+        <v>4.74</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.77</v>
+        <v>43.95</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.78</v>
+        <v>16.74</v>
       </c>
       <c r="DQ17" t="n">
-        <v>15.95</v>
+        <v>16.17</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.41</v>
+        <v>50.17</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.78</v>
+        <v>18.57</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>93.73</v>
+        <v>94.67</v>
       </c>
       <c r="I18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="K18" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="L18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M18" t="n">
-        <v>43.91</v>
+        <v>45.08</v>
       </c>
       <c r="N18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>15.64</v>
+        <v>15.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.91</v>
+        <v>16.42</v>
       </c>
       <c r="R18" t="n">
-        <v>6.27</v>
+        <v>6.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.18</v>
+        <v>49.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.550000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.45</v>
+        <v>17.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AF18" t="n">
         <v>0.09</v>
@@ -7998,70 +7998,70 @@
         <v>2.45</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH18" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.82</v>
+        <v>5.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="BZ18" t="n">
         <v>2.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC18" t="n">
         <v>3.23</v>
@@ -8076,7 +8076,7 @@
         <v>3.17</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH18" t="n">
         <v>1.32</v>
@@ -8094,7 +8094,7 @@
         <v>2.1</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN18" t="n">
         <v>1.78</v>
@@ -8106,7 +8106,7 @@
         <v>2.26</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CR18" t="n">
         <v>1.5</v>
@@ -8127,13 +8127,13 @@
         <v>1.99</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA18" t="n">
         <v>1.8</v>
@@ -8151,43 +8151,43 @@
         <v>0.13</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG18" t="n">
         <v>2.78</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.23</v>
+        <v>90.87</v>
       </c>
       <c r="DI18" t="n">
         <v>0.22</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.5</v>
+        <v>42.22</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.1</v>
+        <v>16.13</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.59</v>
+        <v>16.35</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="DS18" t="n">
         <v>0.04</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.64</v>
+        <v>47.3</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.55</v>
+        <v>18.05</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.18</v>
@@ -8323,127 +8323,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>94.18000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>49.82</v>
+        <v>49.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.55</v>
+        <v>19.42</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.36</v>
+        <v>12.67</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>36.64</v>
+        <v>36.67</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.18</v>
+        <v>23.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.18</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU19" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY19" t="n">
         <v>2.35</v>
@@ -8461,25 +8461,25 @@
         <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
         <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH19" t="n">
         <v>1.32</v>
@@ -8494,7 +8494,7 @@
         <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM19" t="n">
         <v>2.2</v>
@@ -8509,16 +8509,16 @@
         <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
@@ -8527,103 +8527,103 @@
         <v>1.9</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
         <v>1.66</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA19" t="n">
         <v>1.75</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
         <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.04000000000001</v>
+        <v>95.05</v>
       </c>
       <c r="DI19" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM19" t="n">
-        <v>56.36</v>
+        <v>55.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.23</v>
+        <v>17.26</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.72</v>
+        <v>13.35</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>38.14</v>
+        <v>38.09</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.31</v>
+        <v>12.22</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="EA19" t="n">
-        <v>23.96</v>
+        <v>24</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
         <v>0.18</v>
@@ -8723,139 +8723,139 @@
         <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>110.27</v>
+        <v>105.92</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.36</v>
+        <v>5.08</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.18</v>
+        <v>50.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.27</v>
+        <v>14.42</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.64</v>
+        <v>13.92</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.73</v>
+        <v>6.08</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.64</v>
+        <v>60.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.45</v>
+        <v>16.25</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.64</v>
+        <v>10.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.82</v>
+        <v>5.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.91</v>
+        <v>18.67</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.32</v>
+        <v>4.09</v>
       </c>
       <c r="BR20" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS20" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV20" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX20" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY20" t="n">
         <v>1.77</v>
@@ -8864,43 +8864,43 @@
         <v>1.77</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB20" t="n">
         <v>3.64</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CE20" t="n">
         <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH20" t="n">
         <v>1.38</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK20" t="n">
         <v>1.56</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN20" t="n">
         <v>1.79</v>
@@ -8909,28 +8909,28 @@
         <v>1.31</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU20" t="n">
         <v>1.42</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX20" t="n">
         <v>1.61</v>
@@ -8948,85 +8948,85 @@
         <v>1.33</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="DE20" t="n">
         <v>0.13</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="DH20" t="n">
-        <v>109.46</v>
+        <v>107.22</v>
       </c>
       <c r="DI20" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="DM20" t="n">
-        <v>51.77</v>
+        <v>50.78</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.18</v>
+        <v>15.22</v>
       </c>
       <c r="DQ20" t="n">
-        <v>14.96</v>
+        <v>15.04</v>
       </c>
       <c r="DR20" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>62.41</v>
+        <v>62.17</v>
       </c>
       <c r="DW20" t="n">
         <v>0.13</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.14</v>
+        <v>17</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.46</v>
+        <v>11.35</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.32</v>
+        <v>16.79</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0.09</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AI21" t="n">
-        <v>83.45</v>
+        <v>84.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.45</v>
+        <v>38.67</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.82</v>
+        <v>13.83</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>48.27</v>
+        <v>47.42</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.64</v>
+        <v>18.92</v>
       </c>
       <c r="BE21" t="n">
         <v>1.14</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.73</v>
+        <v>6.78</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS21" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BU21" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV21" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY21" t="n">
         <v>2.52</v>
@@ -9267,25 +9267,25 @@
         <v>2.65</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CD21" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF21" t="n">
         <v>3.28</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
@@ -9306,7 +9306,7 @@
         <v>2.19</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
@@ -9315,7 +9315,7 @@
         <v>2.32</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
@@ -9330,73 +9330,73 @@
         <v>1.35</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW21" t="n">
         <v>2.03</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB21" t="n">
         <v>1.45</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="DE21" t="n">
         <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="DH21" t="n">
-        <v>82.72</v>
+        <v>83.3</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="DK21" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.82</v>
+        <v>42.26</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.64</v>
+        <v>16.48</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.36</v>
+        <v>13.39</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="DS21" t="n">
         <v>0.13</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.36</v>
+        <v>46</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.87</v>
+        <v>12.79</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.23</v>
+        <v>20.31</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>87.91</v>
+        <v>86.42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.82</v>
+        <v>34.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.64</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.73</v>
+        <v>17.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.91</v>
       </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>51.91</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY2" t="n">
         <v>2.96</v>
@@ -1610,34 +1610,34 @@
         <v>3.16</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.97</v>
+        <v>4.19</v>
       </c>
       <c r="CE2" t="n">
         <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI2" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK2" t="n">
         <v>1.65</v>
@@ -1646,100 +1646,100 @@
         <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN2" t="n">
         <v>1.72</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU2" t="n">
         <v>1.37</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW2" t="n">
         <v>1.94</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.91</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="DL2" t="n">
         <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.68</v>
+        <v>34.87</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.46</v>
+        <v>13.13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.5</v>
+        <v>17.17</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.27</v>
+        <v>9.43</v>
       </c>
       <c r="DS2" t="n">
         <v>0.04</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.96</v>
+        <v>49.61</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.09</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.59</v>
+        <v>6.35</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.73</v>
+        <v>18.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46</v>
+        <v>46.09</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.18</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.82</v>
+        <v>46.87</v>
       </c>
       <c r="DW8" t="n">
         <v>0.17</v>
@@ -5457,7 +5457,7 @@
         <v>15.08</v>
       </c>
       <c r="R12" t="n">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="S12" t="n">
         <v>0.92</v>
@@ -5769,7 +5769,7 @@
         <v>14.43</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="DS12" t="n">
         <v>0.3</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>3.33</v>
       </c>
       <c r="H13" t="n">
-        <v>106</v>
+        <v>105.67</v>
       </c>
       <c r="I13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>6.18</v>
+        <v>6.92</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="M13" t="n">
-        <v>52.91</v>
+        <v>53.08</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>13.91</v>
+        <v>13.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>14.83</v>
       </c>
       <c r="R13" t="n">
-        <v>5.45</v>
+        <v>5.08</v>
       </c>
       <c r="S13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>55.55</v>
+        <v>55.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.64</v>
+        <v>15.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.36</v>
+        <v>17.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -5983,70 +5983,70 @@
         <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CC13" t="n">
         <v>2.36</v>
@@ -6061,25 +6061,25 @@
         <v>3.1</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
         <v>2</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN13" t="n">
         <v>1.68</v>
@@ -6088,19 +6088,19 @@
         <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6112,100 +6112,100 @@
         <v>2.03</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="DE13" t="n">
         <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.72</v>
+        <v>96</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.82</v>
+        <v>6.22</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.36</v>
+        <v>46.74</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.78</v>
+        <v>14.43</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.14</v>
+        <v>14.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.6</v>
+        <v>53.78</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.04</v>
+        <v>14.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.41</v>
+        <v>10.04</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.77</v>
+        <v>16.83</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.42</v>
+        <v>48.33</v>
       </c>
       <c r="Y14" t="n">
         <v>0.08</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.78</v>
+        <v>48.74</v>
       </c>
       <c r="DW14" t="n">
         <v>0.13</v>
@@ -7177,16 +7177,16 @@
         <v>9.58</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="BD16" t="n">
         <v>17.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BF16" t="n">
         <v>2.42</v>
@@ -7402,10 +7402,10 @@
         <v>11.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.17</v>
+        <v>7.22</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="EA16" t="n">
         <v>16.7</v>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -1379,91 +1379,91 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>81.91</v>
+        <v>83.17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K2" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>35.55</v>
+        <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>13.27</v>
+        <v>13.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.27</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>10.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.64</v>
+        <v>18.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -1550,67 +1550,67 @@
         <v>2.58</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BH2" t="n">
         <v>9.83</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY2" t="n">
         <v>2.96</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB2" t="n">
         <v>3.23</v>
@@ -1622,43 +1622,43 @@
         <v>4.19</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO2" t="n">
         <v>1.36</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,73 +1673,73 @@
         <v>1.37</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DG2" t="n">
         <v>2.21</v>
       </c>
-      <c r="DA2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DD2" t="n">
+      <c r="DH2" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DK2" t="n">
         <v>4.12</v>
       </c>
-      <c r="DE2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>84.26000000000001</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>4.04</v>
-      </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.87</v>
+        <v>35.62</v>
       </c>
       <c r="DN2" t="n">
         <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.13</v>
+        <v>13.04</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.17</v>
+        <v>17.04</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.43</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS2" t="n">
         <v>0.04</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.61</v>
+        <v>50.04</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.35</v>
+        <v>6.46</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.48</v>
+        <v>19.04</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>80.81999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>36.64</v>
+        <v>36.83</v>
       </c>
       <c r="N3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>15.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.18</v>
+        <v>15.67</v>
       </c>
       <c r="R3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.73</v>
+        <v>48.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.73</v>
+        <v>11.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.45</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.82</v>
+        <v>16.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.91</v>
+        <v>9.17</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
         <v>3.76</v>
@@ -2028,10 +2028,10 @@
         <v>1.47</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH3" t="n">
         <v>1.32</v>
@@ -2043,34 +2043,34 @@
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL3" t="n">
         <v>2.13</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS3" t="n">
         <v>3.23</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2082,100 +2082,100 @@
         <v>1.95</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="DH3" t="n">
-        <v>80.43000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>34.31</v>
+        <v>34.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.26</v>
+        <v>15.2</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.26</v>
+        <v>15.04</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.78</v>
+        <v>48.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.83</v>
+        <v>10.29</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.17</v>
+        <v>7.46</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.26</v>
+        <v>17.38</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H4" t="n">
-        <v>85.64</v>
+        <v>84.42</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>35.36</v>
+        <v>33.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>12.73</v>
+        <v>13.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.73</v>
+        <v>15.25</v>
       </c>
       <c r="R4" t="n">
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.36</v>
+        <v>49.17</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.91</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.73</v>
+        <v>16.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP4" t="n">
         <v>4.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC4" t="n">
         <v>3.92</v>
@@ -2440,19 +2440,19 @@
         <v>1.3</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN4" t="n">
         <v>1.72</v>
@@ -2461,34 +2461,34 @@
         <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.17</v>
@@ -2503,7 +2503,7 @@
         <v>2.39</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="DE4" t="n">
         <v>0.04</v>
@@ -2512,73 +2512,73 @@
         <v>1.96</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.05</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="DK4" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>33.43</v>
+        <v>32.71</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO4" t="n">
         <v>1.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.87</v>
+        <v>14.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.869999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.26</v>
+        <v>48.71</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.13</v>
+        <v>11.21</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.04</v>
+        <v>7.21</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.92</v>
+        <v>18.71</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,139 +2678,139 @@
         <v>2.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL5" t="n">
         <v>1</v>
       </c>
-      <c r="AH5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>86.45</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>47.45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BM5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BR5" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.5</v>
@@ -2819,25 +2819,25 @@
         <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.18</v>
+        <v>4.07</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.57</v>
+        <v>4.42</v>
       </c>
       <c r="CE5" t="n">
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
@@ -2846,7 +2846,7 @@
         <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK5" t="n">
         <v>1.56</v>
@@ -2885,70 +2885,70 @@
         <v>1.98</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY5" t="n">
         <v>2.01</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD5" t="n">
         <v>3.91</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="DH5" t="n">
-        <v>86</v>
+        <v>87.38</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM5" t="n">
-        <v>43.65</v>
+        <v>45.04</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.13</v>
+        <v>13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.39</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.31</v>
+        <v>8.33</v>
       </c>
       <c r="DS5" t="n">
         <v>0.17</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.6</v>
+        <v>50.21</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.65</v>
+        <v>13.04</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.48</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.26</v>
+        <v>18.58</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>87.73</v>
+        <v>86.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.18</v>
+        <v>41</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>12.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.27</v>
+        <v>17.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.55</v>
+        <v>8.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>55.91</v>
+        <v>54.83</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.09</v>
+        <v>12.25</v>
       </c>
       <c r="BB6" t="n">
         <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>13.73</v>
+        <v>13.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="BR6" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX6" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY6" t="n">
         <v>2.39</v>
@@ -3222,55 +3222,55 @@
         <v>2.55</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.21</v>
+        <v>4.08</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CN6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.66</v>
       </c>
       <c r="CO6" t="n">
         <v>1.35</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3285,73 +3285,73 @@
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.93</v>
       </c>
-      <c r="CW6" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CX6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DB6" t="n">
         <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.66</v>
+        <v>83.12</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.04</v>
+        <v>37.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.04</v>
+        <v>18.21</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.74</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.3</v>
+        <v>53.83</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.22</v>
+        <v>13.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.7</v>
+        <v>15.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,49 +3487,49 @@
         <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>94.5</v>
+        <v>96.31</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>47</v>
+        <v>47.69</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.17</v>
+        <v>15.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AV7" t="n">
         <v>0.08</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49.5</v>
+        <v>50.77</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.25</v>
+        <v>11.69</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.25</v>
+        <v>7.85</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.42</v>
+        <v>18.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP7" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.05</v>
@@ -3628,10 +3628,10 @@
         <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CD7" t="n">
         <v>3.1</v>
@@ -3640,10 +3640,10 @@
         <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH7" t="n">
         <v>1.31</v>
@@ -3652,16 +3652,16 @@
         <v>1.79</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN7" t="n">
         <v>1.62</v>
@@ -3691,19 +3691,19 @@
         <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
@@ -3712,49 +3712,49 @@
         <v>2.31</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.39</v>
+        <v>95.38</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.87</v>
+        <v>50.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.35</v>
+        <v>14.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.48</v>
+        <v>7.38</v>
       </c>
       <c r="DS7" t="n">
         <v>0.17</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.22</v>
+        <v>49.92</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.57</v>
+        <v>12.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.48</v>
+        <v>8.75</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.18</v>
+        <v>18.25</v>
       </c>
       <c r="EB7" t="n">
         <v>1.45</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>81.67</v>
+        <v>82.77</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>39.83</v>
+        <v>40.46</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>14.92</v>
+        <v>14.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="R8" t="n">
-        <v>8.08</v>
+        <v>7.69</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U8" t="n">
         <v>0.08</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>47.58</v>
+        <v>47.31</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z8" t="n">
         <v>11.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.42</v>
+        <v>7.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.83</v>
+        <v>20.69</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>2.27</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.390000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC8" t="n">
         <v>3.38</v>
@@ -4040,13 +4040,13 @@
         <v>3.79</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4055,28 +4055,28 @@
         <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP8" t="n">
         <v>2.24</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4091,73 +4091,73 @@
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW8" t="n">
         <v>1.94</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB8" t="n">
         <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>81</v>
+        <v>81.62</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.78</v>
+        <v>40.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.92</v>
+        <v>14.88</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.69</v>
+        <v>14.46</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.74</v>
+        <v>7.54</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.87</v>
+        <v>46.75</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.35</v>
+        <v>19.33</v>
       </c>
       <c r="EB8" t="n">
         <v>1.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.27</v>
@@ -4290,52 +4290,52 @@
         <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.25</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.33</v>
+        <v>40.85</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.67</v>
+        <v>18.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AV9" t="n">
         <v>0.08</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.25</v>
+        <v>46.69</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.92</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="BC9" t="n">
         <v>5.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.08</v>
+        <v>17.31</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.65</v>
+        <v>9.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.38</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY9" t="n">
         <v>2.35</v>
@@ -4431,22 +4431,22 @@
         <v>2.48</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB9" t="n">
         <v>3.26</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG9" t="n">
         <v>2.73</v>
@@ -4455,31 +4455,31 @@
         <v>1.38</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK9" t="n">
         <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
@@ -4500,67 +4500,67 @@
         <v>1.77</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY9" t="n">
         <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DH9" t="n">
-        <v>81.91</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.3</v>
+        <v>42.96</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DP9" t="n">
-        <v>17.09</v>
+        <v>16.83</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.44</v>
+        <v>15.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DS9" t="n">
         <v>0.08</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.26</v>
+        <v>47.91</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
         <v>16</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.52</v>
+        <v>5.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.08</v>
@@ -4693,139 +4693,139 @@
         <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>89</v>
+        <v>89.92</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.55</v>
+        <v>35.17</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.64</v>
+        <v>16.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.64</v>
+        <v>13.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.55</v>
+        <v>52.83</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.27</v>
+        <v>19.58</v>
       </c>
       <c r="BE10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.21</v>
       </c>
-      <c r="BF10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.48</v>
+        <v>4.54</v>
       </c>
       <c r="BR10" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY10" t="n">
         <v>2.3</v>
@@ -4834,22 +4834,22 @@
         <v>2.39</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CE10" t="n">
         <v>1.51</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CG10" t="n">
         <v>2.48</v>
@@ -4864,16 +4864,16 @@
         <v>2</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
@@ -4903,13 +4903,13 @@
         <v>2.03</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CZ10" t="n">
         <v>2.13</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.14</v>
       </c>
       <c r="DA10" t="n">
         <v>1.7</v>
@@ -4918,52 +4918,52 @@
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.56999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.78</v>
+        <v>14.08</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
       <c r="DS10" t="n">
         <v>0.17</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.61</v>
+        <v>53.71</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.65</v>
+        <v>20.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI11" t="n">
-        <v>88</v>
+        <v>91.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.91</v>
+        <v>42.92</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.73</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>54.36</v>
+        <v>55.67</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.27</v>
+        <v>12.17</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.82</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.64</v>
+        <v>17.08</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN11" t="n">
         <v>1.38</v>
       </c>
-      <c r="BF11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BO11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY11" t="n">
         <v>2.75</v>
@@ -5237,16 +5237,16 @@
         <v>3.03</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.69</v>
+        <v>4.55</v>
       </c>
       <c r="CE11" t="n">
         <v>1.39</v>
@@ -5255,7 +5255,7 @@
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.38</v>
@@ -5270,13 +5270,13 @@
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM11" t="n">
         <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
@@ -5285,88 +5285,88 @@
         <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX11" t="n">
         <v>1.65</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.21</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="DE11" t="n">
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.91</v>
+        <v>91.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.91</v>
+        <v>45.25</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.61</v>
+        <v>13.54</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.52</v>
+        <v>18.42</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
       </c>
       <c r="DS11" t="n">
         <v>0.17</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>58.83</v>
+        <v>59.29</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.52</v>
+        <v>14.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.31</v>
+        <v>9.33</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.22</v>
+        <v>5.04</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.31</v>
+        <v>17.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>106.18</v>
+        <v>103.83</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AL12" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.09</v>
+        <v>56.08</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.82</v>
+        <v>15.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.73</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.27</v>
+        <v>5.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>53.09</v>
+        <v>51.58</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>18.55</v>
+        <v>18.08</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.82</v>
+        <v>13.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.73</v>
+        <v>4.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.09</v>
+        <v>17.92</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY12" t="n">
         <v>1.97</v>
@@ -5643,52 +5643,52 @@
         <v>3.23</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK12" t="n">
         <v>1.67</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN12" t="n">
         <v>1.69</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
@@ -5706,16 +5706,16 @@
         <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA12" t="n">
         <v>1.73</v>
@@ -5724,85 +5724,85 @@
         <v>1.39</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>101.91</v>
+        <v>100.92</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.91</v>
+        <v>5.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>56.96</v>
+        <v>56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.26</v>
+        <v>15.21</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.43</v>
+        <v>14.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.22</v>
+        <v>51.5</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.79</v>
+        <v>16.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.92</v>
+        <v>11.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.31</v>
+        <v>19.17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5902,139 +5902,139 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.45</v>
+        <v>86.58</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.82</v>
+        <v>38.92</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.64</v>
+        <v>16.08</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.27</v>
+        <v>13.58</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="AT13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1</v>
       </c>
-      <c r="AU13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU13" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>1.69</v>
@@ -6043,16 +6043,16 @@
         <v>1.71</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CE13" t="n">
         <v>1.45</v>
@@ -6070,7 +6070,7 @@
         <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
         <v>1.67</v>
@@ -6094,10 +6094,10 @@
         <v>3.92</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT13" t="n">
         <v>2.82</v>
@@ -6115,7 +6115,7 @@
         <v>1.73</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.1</v>
@@ -6127,52 +6127,52 @@
         <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>96</v>
+        <v>96.12</v>
       </c>
       <c r="DI13" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.22</v>
+        <v>6.08</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.74</v>
+        <v>46</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.43</v>
+        <v>14.7</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.08</v>
+        <v>14.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.78</v>
+        <v>53.96</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.87</v>
+        <v>14.54</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.04</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.83</v>
+        <v>4.66</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.83</v>
+        <v>17.12</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.08</v>
@@ -6305,139 +6305,139 @@
         <v>1.58</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>94.27</v>
+        <v>93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>47.64</v>
+        <v>47.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>17.08</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.09</v>
+        <v>8.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.18</v>
+        <v>49.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.82</v>
+        <v>18.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.57</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.77</v>
@@ -6446,25 +6446,25 @@
         <v>1.81</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC14" t="n">
         <v>2.39</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH14" t="n">
         <v>1.36</v>
@@ -6476,16 +6476,16 @@
         <v>1.88</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO14" t="n">
         <v>1.33</v>
@@ -6494,13 +6494,13 @@
         <v>2.08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT14" t="n">
         <v>2.93</v>
@@ -6515,67 +6515,67 @@
         <v>1.92</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.09</v>
+        <v>92.5</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.17</v>
+        <v>46.25</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.52</v>
+        <v>15.16</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.87</v>
+        <v>13.79</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="DS14" t="n">
         <v>0.17</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.74</v>
+        <v>48.92</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.22</v>
+        <v>14.25</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.869999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.79</v>
+        <v>19.58</v>
       </c>
       <c r="EB14" t="n">
         <v>1.54</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G15" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="H15" t="n">
-        <v>84.42</v>
+        <v>86</v>
       </c>
       <c r="I15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="K15" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>37.67</v>
+        <v>39.69</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>15.33</v>
+        <v>15.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.17</v>
+        <v>16.38</v>
       </c>
       <c r="R15" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="S15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.25</v>
+        <v>16.54</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.67</v>
+        <v>11.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.58</v>
+        <v>5.31</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.5</v>
+        <v>18.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6789,70 +6789,70 @@
         <v>2.36</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.91</v>
+        <v>5.96</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.61</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT15" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC15" t="n">
         <v>4.95</v>
@@ -6864,7 +6864,7 @@
         <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG15" t="n">
         <v>2.78</v>
@@ -6873,10 +6873,10 @@
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK15" t="n">
         <v>1.56</v>
@@ -6885,19 +6885,19 @@
         <v>2.08</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6912,19 +6912,19 @@
         <v>1.41</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW15" t="n">
         <v>1.89</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA15" t="n">
         <v>1.87</v>
@@ -6933,52 +6933,52 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DH15" t="n">
-        <v>79.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM15" t="n">
-        <v>35.52</v>
+        <v>36.71</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.87</v>
+        <v>15.12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.26</v>
+        <v>15.41</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.13</v>
+        <v>7.05</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.48</v>
+        <v>49.79</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.39</v>
+        <v>14.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.74</v>
+        <v>10.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.61</v>
+        <v>18.3</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H16" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>80.64</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="K16" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="L16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>39.64</v>
+        <v>39.17</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>13.73</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="R16" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>44.91</v>
+        <v>43.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.55</v>
+        <v>15.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.42</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX16" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
         <v>4.5</v>
@@ -7267,7 +7267,7 @@
         <v>1.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG16" t="n">
         <v>2.62</v>
@@ -7279,31 +7279,31 @@
         <v>1.83</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM16" t="n">
         <v>2.13</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP16" t="n">
         <v>2.14</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS16" t="n">
         <v>3.21</v>
@@ -7321,13 +7321,13 @@
         <v>1.95</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA16" t="n">
         <v>1.74</v>
@@ -7336,52 +7336,52 @@
         <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
         <v>4</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>77.22</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.87</v>
+        <v>34.84</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DO16" t="n">
         <v>2</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.13</v>
+        <v>15.21</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.31</v>
+        <v>14.21</v>
       </c>
       <c r="DR16" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="DS16" t="n">
         <v>0.04</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.69</v>
+        <v>43.12</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
         <v>11.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.22</v>
+        <v>7.25</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="EB16" t="n">
         <v>1.22</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>101.18</v>
+        <v>98.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J17" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="K17" t="n">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="M17" t="n">
-        <v>45.45</v>
+        <v>44.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>17.55</v>
+        <v>16.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.45</v>
+        <v>17.75</v>
       </c>
       <c r="R17" t="n">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.82</v>
+        <v>50.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>17</v>
+        <v>15.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BO17" t="n">
         <v>0.96</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="BX17" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="CA17" t="n">
         <v>3.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CC17" t="n">
         <v>3.53</v>
@@ -7682,16 +7682,16 @@
         <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK17" t="n">
         <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN17" t="n">
         <v>1.66</v>
@@ -7700,10 +7700,10 @@
         <v>1.41</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7721,7 +7721,7 @@
         <v>1.86</v>
       </c>
       <c r="CW17" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CX17" t="n">
         <v>1.76</v>
@@ -7742,82 +7742,82 @@
         <v>2.4</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.7</v>
+        <v>94.67</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.95</v>
+        <v>43.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.74</v>
+        <v>16.25</v>
       </c>
       <c r="DQ17" t="n">
-        <v>16.17</v>
+        <v>16.38</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.22</v>
+        <v>7.21</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.17</v>
+        <v>50.04</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.3</v>
+        <v>13.29</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.44</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.57</v>
+        <v>17.96</v>
       </c>
       <c r="EB17" t="n">
         <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7917,139 +7917,139 @@
         <v>2.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>86.73</v>
+        <v>88.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.64</v>
+        <v>6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.09</v>
+        <v>39.83</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.55</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.27</v>
+        <v>15.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.09</v>
+        <v>8.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45.09</v>
+        <v>45.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.45</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.82</v>
+        <v>8.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.64</v>
+        <v>19.08</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>11.04</v>
+        <v>11.21</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>5.04</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.91</v>
+        <v>6.08</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
         <v>2.11</v>
@@ -8058,43 +8058,43 @@
         <v>2.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC18" t="n">
         <v>3.18</v>
       </c>
-      <c r="CC18" t="n">
-        <v>3.23</v>
-      </c>
       <c r="CD18" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="CE18" t="n">
         <v>1.48</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH18" t="n">
         <v>1.32</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.95</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL18" t="n">
         <v>2.1</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN18" t="n">
         <v>1.78</v>
@@ -8103,7 +8103,7 @@
         <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ18" t="n">
         <v>4.17</v>
@@ -8115,7 +8115,7 @@
         <v>3.28</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CU18" t="n">
         <v>1.36</v>
@@ -8127,67 +8127,67 @@
         <v>1.99</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB18" t="n">
         <v>1.42</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.87</v>
+        <v>91.58</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.13</v>
+        <v>5.34</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.22</v>
+        <v>42.46</v>
       </c>
       <c r="DN18" t="n">
         <v>1.08</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.13</v>
+        <v>15.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.35</v>
+        <v>16.17</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.22</v>
+        <v>7.34</v>
       </c>
       <c r="DS18" t="n">
         <v>0.04</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.3</v>
+        <v>47.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.52</v>
+        <v>10.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.83</v>
+        <v>7.04</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.05</v>
+        <v>18.29</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>97.91</v>
+        <v>98.75</v>
       </c>
       <c r="I19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J19" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M19" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="N19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="P19" t="n">
-        <v>14.91</v>
+        <v>14.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.09</v>
+        <v>14.5</v>
       </c>
       <c r="R19" t="n">
-        <v>9.27</v>
+        <v>9.08</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>39.64</v>
+        <v>39.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.36</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.36</v>
+        <v>10.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>24.73</v>
+        <v>24.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,49 +8401,49 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BR19" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8452,19 +8452,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC19" t="n">
         <v>3.66</v>
@@ -8479,7 +8479,7 @@
         <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH19" t="n">
         <v>1.32</v>
@@ -8506,7 +8506,7 @@
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.98</v>
@@ -8515,10 +8515,10 @@
         <v>1.49</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
@@ -8548,49 +8548,49 @@
         <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DH19" t="n">
-        <v>95.05</v>
+        <v>95.58</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.91</v>
+        <v>56.04</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP19" t="n">
-        <v>17.26</v>
+        <v>17.05</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.35</v>
+        <v>13.58</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS19" t="n">
         <v>0.08</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>38.09</v>
+        <v>38.25</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.22</v>
+        <v>12.12</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>24</v>
+        <v>24.08</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
-        <v>108.64</v>
+        <v>108.42</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>51.36</v>
+        <v>51.83</v>
       </c>
       <c r="N20" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="P20" t="n">
-        <v>16.09</v>
+        <v>16.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.27</v>
+        <v>16.17</v>
       </c>
       <c r="R20" t="n">
-        <v>6.27</v>
+        <v>6.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>64.18000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.82</v>
+        <v>17.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.27</v>
+        <v>12.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.73</v>
+        <v>14.58</v>
       </c>
       <c r="AD20" t="n">
         <v>1.88</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF20" t="n">
         <v>0.08</v>
@@ -8804,70 +8804,70 @@
         <v>2.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.91</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BJ20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL20" t="n">
         <v>0.83</v>
       </c>
-      <c r="BK20" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.87</v>
-      </c>
       <c r="BM20" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BR20" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS20" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX20" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY20" t="n">
         <v>1.77</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC20" t="n">
         <v>2.17</v>
@@ -8897,10 +8897,10 @@
         <v>1.56</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN20" t="n">
         <v>1.79</v>
@@ -8912,7 +8912,7 @@
         <v>1.99</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CR20" t="n">
         <v>1.41</v>
@@ -8933,13 +8933,13 @@
         <v>1.89</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA20" t="n">
         <v>1.8</v>
@@ -8954,73 +8954,73 @@
         <v>3.6</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DH20" t="n">
-        <v>107.22</v>
+        <v>107.17</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM20" t="n">
-        <v>50.78</v>
+        <v>51.04</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DP20" t="n">
-        <v>15.22</v>
+        <v>15.5</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.04</v>
+        <v>15.05</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>62.17</v>
+        <v>62.29</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX20" t="n">
         <v>17</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.35</v>
+        <v>11.38</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.79</v>
+        <v>16.62</v>
       </c>
       <c r="EB20" t="n">
         <v>1.84</v>
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="H21" t="n">
-        <v>82</v>
+        <v>82.17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J21" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="K21" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="L21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="M21" t="n">
-        <v>46.18</v>
+        <v>44.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="P21" t="n">
-        <v>16.27</v>
+        <v>15.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.91</v>
+        <v>12.92</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>7.58</v>
       </c>
       <c r="S21" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T21" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44.45</v>
+        <v>43.58</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.82</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.36</v>
+        <v>10</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.82</v>
+        <v>21.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.17</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BH21" t="n">
-        <v>11.26</v>
+        <v>11.21</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS21" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT21" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BU21" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CA21" t="n">
         <v>3.09</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC21" t="n">
         <v>3.58</v>
@@ -9279,13 +9279,13 @@
         <v>4.08</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF21" t="n">
         <v>3.28</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH21" t="n">
         <v>1.3</v>
@@ -9300,13 +9300,13 @@
         <v>1.62</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM21" t="n">
         <v>2.19</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO21" t="n">
         <v>1.41</v>
@@ -9315,16 +9315,16 @@
         <v>2.32</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
@@ -9333,7 +9333,7 @@
         <v>1.85</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX21" t="n">
         <v>1.61</v>
@@ -9345,7 +9345,7 @@
         <v>2.29</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB21" t="n">
         <v>1.45</v>
@@ -9354,82 +9354,82 @@
         <v>2.43</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="DE21" t="n">
         <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.3</v>
+        <v>83.34</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>5.69</v>
+        <v>5.66</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.26</v>
+        <v>41.75</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP21" t="n">
-        <v>16.48</v>
+        <v>16.3</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.17</v>
+        <v>7.46</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.79</v>
+        <v>12.71</v>
       </c>
       <c r="DY21" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.31</v>
+        <v>20.17</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_B_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.5</v>
+        <v>86.38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.17</v>
+        <v>3.92</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.67</v>
+        <v>31.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.17</v>
+        <v>15.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.08</v>
+        <v>13.92</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.42</v>
+        <v>9.15</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.25</v>
+        <v>48.31</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.42</v>
+        <v>9.92</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.17</v>
+        <v>3.92</v>
       </c>
       <c r="BD4" t="n">
         <v>20.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BO4" t="n">
         <v>1.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.96</v>
+        <v>4.8</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY4" t="n">
         <v>3.02</v>
@@ -2419,19 +2419,19 @@
         <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG4" t="n">
         <v>2.54</v>
@@ -2464,7 +2464,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2500,52 +2500,52 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="DE4" t="n">
         <v>0.04</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>84.45999999999999</v>
+        <v>85.44</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.96</v>
+        <v>3.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.71</v>
+        <v>32.52</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.17</v>
+        <v>14.32</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.66</v>
+        <v>14.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DS4" t="n">
         <v>0.16</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.71</v>
+        <v>48.72</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.21</v>
+        <v>10.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.21</v>
+        <v>7.04</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.71</v>
+        <v>18.8</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,139 +2678,139 @@
         <v>2.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AI5" t="n">
-        <v>89.17</v>
+        <v>89.08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.25</v>
+        <v>42.69</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.17</v>
+        <v>13.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.75</v>
+        <v>14.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.67</v>
+        <v>7.77</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.83</v>
+        <v>48.92</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.5</v>
+        <v>11.62</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.75</v>
+        <v>7.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.75</v>
+        <v>18.92</v>
       </c>
       <c r="BE5" t="n">
         <v>1.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BO5" t="n">
         <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="BR5" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV5" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY5" t="n">
         <v>2.5</v>
@@ -2819,25 +2819,25 @@
         <v>2.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CB5" t="n">
         <v>3.26</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.42</v>
+        <v>4.57</v>
       </c>
       <c r="CE5" t="n">
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
@@ -2852,7 +2852,7 @@
         <v>1.56</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM5" t="n">
         <v>2.27</v>
@@ -2864,10 +2864,10 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
@@ -2885,7 +2885,7 @@
         <v>1.98</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
         <v>1.6</v>
@@ -2903,64 +2903,64 @@
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="DE5" t="n">
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.38</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.04</v>
+        <v>44.2</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>13</v>
+        <v>13.04</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>15.52</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.21</v>
+        <v>50.2</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
@@ -2975,13 +2975,13 @@
         <v>4.04</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.58</v>
+        <v>18.68</v>
       </c>
       <c r="EB5" t="n">
         <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
-        <v>79.92</v>
+        <v>77.77</v>
       </c>
       <c r="I6" t="n">
         <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>34.25</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="P6" t="n">
-        <v>11.42</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.75</v>
+        <v>18.69</v>
       </c>
       <c r="R6" t="n">
-        <v>7.92</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U6" t="n">
         <v>0.08</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.83</v>
+        <v>52.08</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.25</v>
+        <v>13.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.92</v>
+        <v>9.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.5</v>
+        <v>17.31</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
         <v>0.25</v>
@@ -3162,70 +3162,70 @@
         <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.58</v>
+        <v>8.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT6" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CC6" t="n">
         <v>3.82</v>
@@ -3237,7 +3237,7 @@
         <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CG6" t="n">
         <v>2.62</v>
@@ -3246,16 +3246,16 @@
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK6" t="n">
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM6" t="n">
         <v>2.11</v>
@@ -3264,31 +3264,31 @@
         <v>1.68</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CU6" t="n">
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX6" t="n">
         <v>1.7</v>
@@ -3303,55 +3303,55 @@
         <v>1.7</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.12</v>
+        <v>81.88</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.62</v>
+        <v>36.32</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DO6" t="n">
         <v>2.12</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>11.76</v>
       </c>
       <c r="DQ6" t="n">
-        <v>18.21</v>
+        <v>18.2</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>8.32</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.83</v>
+        <v>53.4</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.25</v>
+        <v>12.88</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.71</v>
+        <v>15.68</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="H7" t="n">
-        <v>94.27</v>
+        <v>91.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="K7" t="n">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="L7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>53</v>
+        <v>50.58</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>13.45</v>
+        <v>13.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.640000000000001</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="U7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.91</v>
+        <v>47.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.82</v>
+        <v>9.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.91</v>
+        <v>17.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,64 +3565,64 @@
         <v>2.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.08</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU7" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="CA7" t="n">
         <v>3.16</v>
@@ -3640,25 +3640,25 @@
         <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG7" t="n">
         <v>2.55</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
         <v>1.75</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CM7" t="n">
         <v>2</v>
@@ -3670,124 +3670,124 @@
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA7" t="n">
         <v>1.63</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.38</v>
+        <v>93.8</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.12</v>
+        <v>49.08</v>
       </c>
       <c r="DN7" t="n">
         <v>0.88</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11</v>
+        <v>11.12</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.38</v>
+        <v>7.32</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.92</v>
+        <v>49.24</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.75</v>
+        <v>12.68</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.75</v>
+        <v>8.68</v>
       </c>
       <c r="DZ7" t="n">
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.25</v>
+        <v>18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="AI11" t="n">
-        <v>91.33</v>
+        <v>93.77</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.92</v>
+        <v>44.54</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.83</v>
+        <v>13.62</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.5</v>
+        <v>18.31</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.58</v>
+        <v>7.15</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.67</v>
+        <v>55.77</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.17</v>
+        <v>12.62</v>
       </c>
       <c r="BB11" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>92</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>60</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW11" t="n">
         <v>8</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>50</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>8.33</v>
-      </c>
       <c r="BX11" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY11" t="n">
         <v>2.75</v>
@@ -5237,22 +5237,22 @@
         <v>3.03</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="CE11" t="n">
         <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG11" t="n">
         <v>2.76</v>
@@ -5261,7 +5261,7 @@
         <v>1.38</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.78</v>
@@ -5270,7 +5270,7 @@
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM11" t="n">
         <v>2.12</v>
@@ -5282,37 +5282,37 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV11" t="n">
         <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA11" t="n">
         <v>1.76</v>
@@ -5324,82 +5324,82 @@
         <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="DE11" t="n">
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.5</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.25</v>
+        <v>46</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO11" t="n">
         <v>2.12</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.54</v>
+        <v>13.44</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.42</v>
+        <v>18.32</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.92</v>
+        <v>6.72</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.29</v>
+        <v>59.2</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.38</v>
+        <v>14.52</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.33</v>
+        <v>9.56</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.5</v>
+        <v>17.56</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="G12" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>55.92</v>
+        <v>54.92</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O12" t="n">
         <v>1.92</v>
       </c>
       <c r="P12" t="n">
-        <v>14.75</v>
+        <v>14.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.08</v>
+        <v>14.92</v>
       </c>
       <c r="R12" t="n">
-        <v>4.67</v>
+        <v>4.85</v>
       </c>
       <c r="S12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.42</v>
+        <v>51.31</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.17</v>
+        <v>9.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.42</v>
+        <v>20.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5583,25 +5583,25 @@
         <v>2.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.289999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI12" t="n">
         <v>2.08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO12" t="n">
         <v>0.88</v>
@@ -5610,19 +5610,19 @@
         <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.29</v>
+        <v>5.36</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT12" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
         <v>2.55</v>
@@ -5658,7 +5658,7 @@
         <v>3.08</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5673,22 +5673,22 @@
         <v>1.67</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM12" t="n">
         <v>2.12</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO12" t="n">
         <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CR12" t="n">
         <v>1.48</v>
@@ -5709,7 +5709,7 @@
         <v>1.95</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
         <v>2.1</v>
@@ -5718,91 +5718,91 @@
         <v>2.16</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB12" t="n">
         <v>1.39</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>100.92</v>
+        <v>100.88</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="DK12" t="n">
         <v>5.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM12" t="n">
-        <v>56</v>
+        <v>55.48</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.21</v>
+        <v>15.16</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.79</v>
+        <v>14.72</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.5</v>
+        <v>51.44</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.62</v>
+        <v>16.48</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.67</v>
+        <v>11.48</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.17</v>
+        <v>19.24</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>92</v>
+        <v>91.69</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="J14" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="K14" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="L14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>44.83</v>
+        <v>45</v>
       </c>
       <c r="N14" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.08</v>
+        <v>13.92</v>
       </c>
       <c r="R14" t="n">
-        <v>5.83</v>
+        <v>6.08</v>
       </c>
       <c r="S14" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.33</v>
+        <v>48.15</v>
       </c>
       <c r="Y14" t="n">
         <v>0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.25</v>
+        <v>14.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.92</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.67</v>
+        <v>20.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6386,70 +6386,70 @@
         <v>2.83</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.460000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="CC14" t="n">
         <v>2.39</v>
@@ -6461,10 +6461,10 @@
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH14" t="n">
         <v>1.36</v>
@@ -6476,7 +6476,7 @@
         <v>1.88</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL14" t="n">
         <v>2.04</v>
@@ -6485,7 +6485,7 @@
         <v>2.36</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
         <v>1.33</v>
@@ -6494,7 +6494,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6509,10 +6509,10 @@
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
@@ -6533,82 +6533,82 @@
         <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="DE14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>46.28</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="DS14" t="n">
         <v>0.16</v>
       </c>
-      <c r="DF14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>7</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DT14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.92</v>
+        <v>48.8</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.25</v>
+        <v>13.96</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.960000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.58</v>
+        <v>19.64</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="H17" t="n">
-        <v>98.67</v>
+        <v>99.23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J17" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="L17" t="n">
         <v>0.92</v>
       </c>
       <c r="M17" t="n">
-        <v>44.17</v>
+        <v>44.62</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
-        <v>16.5</v>
+        <v>16.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.75</v>
+        <v>17.85</v>
       </c>
       <c r="R17" t="n">
-        <v>6.75</v>
+        <v>6.46</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.5</v>
+        <v>50.54</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>13.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.83</v>
+        <v>9.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>15.92</v>
+        <v>16.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BO17" t="n">
         <v>0.96</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="CA17" t="n">
         <v>3.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CC17" t="n">
         <v>3.53</v>
@@ -7670,10 +7670,10 @@
         <v>1.48</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH17" t="n">
         <v>1.31</v>
@@ -7685,16 +7685,16 @@
         <v>1.97</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO17" t="n">
         <v>1.41</v>
@@ -7703,7 +7703,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CR17" t="n">
         <v>1.51</v>
@@ -7718,16 +7718,16 @@
         <v>1.35</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
         <v>2.01</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.06</v>
@@ -7736,88 +7736,88 @@
         <v>1.64</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.67</v>
+        <v>95.12</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.38</v>
+        <v>43.64</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP17" t="n">
-        <v>16.25</v>
+        <v>16.04</v>
       </c>
       <c r="DQ17" t="n">
-        <v>16.38</v>
+        <v>16.48</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.21</v>
+        <v>7.04</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.04</v>
+        <v>50.08</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.29</v>
+        <v>13.24</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.380000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.96</v>
+        <v>18.08</v>
       </c>
       <c r="EB17" t="n">
         <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="18">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
         <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>0.17</v>
@@ -8726,136 +8726,136 @@
         <v>0.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AI20" t="n">
-        <v>105.92</v>
+        <v>106.62</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AL20" t="n">
         <v>5.08</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN20" t="n">
-        <v>50.25</v>
+        <v>50.38</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.92</v>
+        <v>13.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>60.33</v>
+        <v>60.85</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.25</v>
+        <v>16.08</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.67</v>
+        <v>18.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.789999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS20" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT20" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV20" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY20" t="n">
         <v>1.77</v>
@@ -8864,25 +8864,25 @@
         <v>1.78</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC20" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CD20" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CE20" t="n">
         <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH20" t="n">
         <v>1.38</v>
@@ -8891,16 +8891,16 @@
         <v>1.88</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL20" t="n">
         <v>2.1</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN20" t="n">
         <v>1.79</v>
@@ -8909,28 +8909,28 @@
         <v>1.31</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CR20" t="n">
         <v>1.41</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU20" t="n">
         <v>1.42</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
 